--- a/database/SBFG3.xlsx
+++ b/database/SBFG3.xlsx
@@ -452,16 +452,16 @@
         <v>43572</v>
       </c>
       <c r="B2" t="n">
-        <v>10.75700092315674</v>
+        <v>10.75700283050537</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14180383526864</v>
+        <v>11.14180581084757</v>
       </c>
       <c r="D2" t="n">
-        <v>10.55585332084199</v>
+        <v>10.55585519252467</v>
       </c>
       <c r="E2" t="n">
-        <v>10.66954529883926</v>
+        <v>10.66954719068093</v>
       </c>
       <c r="F2" t="n">
         <v>10338900</v>
@@ -512,16 +512,16 @@
         <v>43578</v>
       </c>
       <c r="B5" t="n">
-        <v>10.43341732025146</v>
+        <v>10.43341827392578</v>
       </c>
       <c r="C5" t="n">
-        <v>10.52961784781559</v>
+        <v>10.52961881028319</v>
       </c>
       <c r="D5" t="n">
-        <v>10.36345314856142</v>
+        <v>10.36345409584061</v>
       </c>
       <c r="E5" t="n">
-        <v>10.49463576197057</v>
+        <v>10.4946367212406</v>
       </c>
       <c r="F5" t="n">
         <v>1919200</v>
@@ -612,16 +612,16 @@
         <v>43585</v>
       </c>
       <c r="B10" t="n">
-        <v>10.23227119445801</v>
+        <v>10.23226928710938</v>
       </c>
       <c r="C10" t="n">
-        <v>10.58209293800151</v>
+        <v>10.58209096544428</v>
       </c>
       <c r="D10" t="n">
-        <v>9.760012549607294</v>
+        <v>9.760010730290132</v>
       </c>
       <c r="E10" t="n">
-        <v>10.40718164921034</v>
+        <v>10.40717970925749</v>
       </c>
       <c r="F10" t="n">
         <v>3631900</v>
@@ -672,16 +672,16 @@
         <v>43591</v>
       </c>
       <c r="B13" t="n">
-        <v>10.20603370666504</v>
+        <v>10.20603275299072</v>
       </c>
       <c r="C13" t="n">
-        <v>10.27599788083272</v>
+        <v>10.27599692062079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.926177009994333</v>
+        <v>9.926176082470445</v>
       </c>
       <c r="E13" t="n">
-        <v>10.04861389776839</v>
+        <v>10.04861295880373</v>
       </c>
       <c r="F13" t="n">
         <v>180200</v>
@@ -732,16 +732,16 @@
         <v>43594</v>
       </c>
       <c r="B16" t="n">
-        <v>10.43341732025146</v>
+        <v>10.43341827392578</v>
       </c>
       <c r="C16" t="n">
-        <v>10.44216221618368</v>
+        <v>10.44216317065733</v>
       </c>
       <c r="D16" t="n">
-        <v>9.97864937022749</v>
+        <v>9.978650282333401</v>
       </c>
       <c r="E16" t="n">
-        <v>10.31972533274547</v>
+        <v>10.31972627602769</v>
       </c>
       <c r="F16" t="n">
         <v>237700</v>
@@ -752,16 +752,16 @@
         <v>43595</v>
       </c>
       <c r="B17" t="n">
-        <v>10.58209228515625</v>
+        <v>10.58209133148193</v>
       </c>
       <c r="C17" t="n">
-        <v>10.70452917890991</v>
+        <v>10.7045282142014</v>
       </c>
       <c r="D17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="E17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="F17" t="n">
         <v>669000</v>
@@ -872,16 +872,16 @@
         <v>43605</v>
       </c>
       <c r="B23" t="n">
-        <v>9.707539558410645</v>
+        <v>9.707537651062012</v>
       </c>
       <c r="C23" t="n">
-        <v>9.873704277263393</v>
+        <v>9.873702337266524</v>
       </c>
       <c r="D23" t="n">
-        <v>9.602592454458703</v>
+        <v>9.6025905677302</v>
       </c>
       <c r="E23" t="n">
-        <v>9.873704277263393</v>
+        <v>9.873702337266524</v>
       </c>
       <c r="F23" t="n">
         <v>117200</v>
@@ -892,16 +892,16 @@
         <v>43606</v>
       </c>
       <c r="B24" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C24" t="n">
-        <v>9.961159054194923</v>
+        <v>9.961158092924956</v>
       </c>
       <c r="D24" t="n">
-        <v>9.725029341866504</v>
+        <v>9.725028403383487</v>
       </c>
       <c r="E24" t="n">
-        <v>9.794993515732981</v>
+        <v>9.794992570498295</v>
       </c>
       <c r="F24" t="n">
         <v>253500</v>
@@ -932,16 +932,16 @@
         <v>43608</v>
       </c>
       <c r="B26" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C26" t="n">
-        <v>10.67829225334568</v>
+        <v>10.67829122287106</v>
       </c>
       <c r="D26" t="n">
-        <v>9.873703419842455</v>
+        <v>9.873702467012118</v>
       </c>
       <c r="E26" t="n">
-        <v>10.35470774070354</v>
+        <v>10.35470674145541</v>
       </c>
       <c r="F26" t="n">
         <v>1121200</v>
@@ -952,16 +952,16 @@
         <v>43609</v>
       </c>
       <c r="B27" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01363176757541</v>
+        <v>10.01363080124173</v>
       </c>
       <c r="D27" t="n">
-        <v>9.794993515732981</v>
+        <v>9.794992570498295</v>
       </c>
       <c r="E27" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="F27" t="n">
         <v>207200</v>
@@ -1012,16 +1012,16 @@
         <v>43614</v>
       </c>
       <c r="B30" t="n">
-        <v>10.23227119445801</v>
+        <v>10.23226928710938</v>
       </c>
       <c r="C30" t="n">
-        <v>10.30223537635894</v>
+        <v>10.30223345596862</v>
       </c>
       <c r="D30" t="n">
-        <v>9.978650826557418</v>
+        <v>9.978648966484943</v>
       </c>
       <c r="E30" t="n">
-        <v>10.22352546321068</v>
+        <v>10.2235235574923</v>
       </c>
       <c r="F30" t="n">
         <v>497500</v>
@@ -1032,16 +1032,16 @@
         <v>43615</v>
       </c>
       <c r="B31" t="n">
-        <v>10.25850582122803</v>
+        <v>10.25850677490234</v>
       </c>
       <c r="C31" t="n">
-        <v>10.36345291038992</v>
+        <v>10.36345387382057</v>
       </c>
       <c r="D31" t="n">
-        <v>10.14481467037358</v>
+        <v>10.14481561347869</v>
       </c>
       <c r="E31" t="n">
-        <v>10.25850582122803</v>
+        <v>10.25850677490234</v>
       </c>
       <c r="F31" t="n">
         <v>445800</v>
@@ -1052,16 +1052,16 @@
         <v>43616</v>
       </c>
       <c r="B32" t="n">
-        <v>10.44216346740723</v>
+        <v>10.44216251373291</v>
       </c>
       <c r="C32" t="n">
-        <v>10.44216346740723</v>
+        <v>10.44216251373291</v>
       </c>
       <c r="D32" t="n">
-        <v>9.98739629692987</v>
+        <v>9.987395384789069</v>
       </c>
       <c r="E32" t="n">
-        <v>10.24101665820579</v>
+        <v>10.24101572290205</v>
       </c>
       <c r="F32" t="n">
         <v>2469900</v>
@@ -1072,16 +1072,16 @@
         <v>43619</v>
       </c>
       <c r="B33" t="n">
-        <v>10.36345386505127</v>
+        <v>10.36345291137695</v>
       </c>
       <c r="C33" t="n">
-        <v>10.58209212520814</v>
+        <v>10.58209115141412</v>
       </c>
       <c r="D33" t="n">
-        <v>10.28474395794859</v>
+        <v>10.28474301151738</v>
       </c>
       <c r="E33" t="n">
-        <v>10.46840012984192</v>
+        <v>10.46839916651015</v>
       </c>
       <c r="F33" t="n">
         <v>341500</v>
@@ -1092,16 +1092,16 @@
         <v>43620</v>
       </c>
       <c r="B34" t="n">
-        <v>10.13607025146484</v>
+        <v>10.13606929779053</v>
       </c>
       <c r="C34" t="n">
-        <v>10.35470851975688</v>
+        <v>10.3547075455115</v>
       </c>
       <c r="D34" t="n">
-        <v>10.01363252096734</v>
+        <v>10.01363157881284</v>
       </c>
       <c r="E34" t="n">
-        <v>10.34596278885588</v>
+        <v>10.34596181543337</v>
       </c>
       <c r="F34" t="n">
         <v>433200</v>
@@ -1112,16 +1112,16 @@
         <v>43621</v>
       </c>
       <c r="B35" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C35" t="n">
-        <v>10.19728815949492</v>
+        <v>10.19728720088784</v>
       </c>
       <c r="D35" t="n">
-        <v>10.0223777209349</v>
+        <v>10.02237677877047</v>
       </c>
       <c r="E35" t="n">
-        <v>10.03986834777152</v>
+        <v>10.03986740396287</v>
       </c>
       <c r="F35" t="n">
         <v>186800</v>
@@ -1132,16 +1132,16 @@
         <v>43622</v>
       </c>
       <c r="B36" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C36" t="n">
-        <v>10.31098015306862</v>
+        <v>10.31097918377381</v>
       </c>
       <c r="D36" t="n">
-        <v>10.0573598086469</v>
+        <v>10.05735886319394</v>
       </c>
       <c r="E36" t="n">
-        <v>10.17979753265829</v>
+        <v>10.17979657569545</v>
       </c>
       <c r="F36" t="n">
         <v>146300</v>
@@ -1172,16 +1172,16 @@
         <v>43626</v>
       </c>
       <c r="B38" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C38" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="D38" t="n">
-        <v>9.89119510052457</v>
+        <v>9.891194170692108</v>
       </c>
       <c r="E38" t="n">
-        <v>10.07485126952228</v>
+        <v>10.07485032242502</v>
       </c>
       <c r="F38" t="n">
         <v>348000</v>
@@ -1192,16 +1192,16 @@
         <v>43627</v>
       </c>
       <c r="B39" t="n">
-        <v>10.02237701416016</v>
+        <v>10.02237796783447</v>
       </c>
       <c r="C39" t="n">
-        <v>10.22352379580968</v>
+        <v>10.22352476862402</v>
       </c>
       <c r="D39" t="n">
-        <v>10.01363128433921</v>
+        <v>10.01363223718133</v>
       </c>
       <c r="E39" t="n">
-        <v>10.09234118465031</v>
+        <v>10.09234214498204</v>
       </c>
       <c r="F39" t="n">
         <v>345200</v>
@@ -1232,16 +1232,16 @@
         <v>43629</v>
       </c>
       <c r="B41" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C41" t="n">
-        <v>10.35470797121831</v>
+        <v>10.35470699781282</v>
       </c>
       <c r="D41" t="n">
-        <v>9.996141363660582</v>
+        <v>9.996140423962533</v>
       </c>
       <c r="E41" t="n">
-        <v>10.08359616592121</v>
+        <v>10.08359521800188</v>
       </c>
       <c r="F41" t="n">
         <v>344300</v>
@@ -1252,16 +1252,16 @@
         <v>43630</v>
       </c>
       <c r="B42" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C42" t="n">
-        <v>10.2497617080823</v>
+        <v>10.2497607445424</v>
       </c>
       <c r="D42" t="n">
-        <v>9.899939996923502</v>
+        <v>9.899939066268965</v>
       </c>
       <c r="E42" t="n">
-        <v>10.22352451676923</v>
+        <v>10.22352355569578</v>
       </c>
       <c r="F42" t="n">
         <v>475700</v>
@@ -1312,16 +1312,16 @@
         <v>43635</v>
       </c>
       <c r="B45" t="n">
-        <v>10.75700092315674</v>
+        <v>10.75700283050537</v>
       </c>
       <c r="C45" t="n">
-        <v>10.78323727683652</v>
+        <v>10.78323918883719</v>
       </c>
       <c r="D45" t="n">
-        <v>10.31972446964662</v>
+        <v>10.31972629946075</v>
       </c>
       <c r="E45" t="n">
-        <v>10.39843436472462</v>
+        <v>10.39843620849499</v>
       </c>
       <c r="F45" t="n">
         <v>221700</v>
@@ -1332,16 +1332,16 @@
         <v>43637</v>
       </c>
       <c r="B46" t="n">
-        <v>11.19427871704102</v>
+        <v>11.1942777633667</v>
       </c>
       <c r="C46" t="n">
-        <v>11.28173351779147</v>
+        <v>11.28173255666661</v>
       </c>
       <c r="D46" t="n">
-        <v>10.75700221117253</v>
+        <v>10.75700129475111</v>
       </c>
       <c r="E46" t="n">
-        <v>10.75700221117253</v>
+        <v>10.75700129475111</v>
       </c>
       <c r="F46" t="n">
         <v>990700</v>
@@ -1372,16 +1372,16 @@
         <v>43641</v>
       </c>
       <c r="B48" t="n">
-        <v>11.35169792175293</v>
+        <v>11.35169696807861</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3604436522166</v>
+        <v>11.36044269780754</v>
       </c>
       <c r="D48" t="n">
-        <v>11.07184121922551</v>
+        <v>11.0718402890624</v>
       </c>
       <c r="E48" t="n">
-        <v>11.14180539485737</v>
+        <v>11.14180445881646</v>
       </c>
       <c r="F48" t="n">
         <v>1743100</v>
@@ -1392,16 +1392,16 @@
         <v>43642</v>
       </c>
       <c r="B49" t="n">
-        <v>12.02510356903076</v>
+        <v>12.02510452270508</v>
       </c>
       <c r="C49" t="n">
-        <v>12.20001399959074</v>
+        <v>12.20001496713667</v>
       </c>
       <c r="D49" t="n">
-        <v>11.24675111049047</v>
+        <v>11.24675200243602</v>
       </c>
       <c r="E49" t="n">
-        <v>11.28173319660246</v>
+        <v>11.28173409132234</v>
       </c>
       <c r="F49" t="n">
         <v>1344300</v>
@@ -1432,16 +1432,16 @@
         <v>43644</v>
       </c>
       <c r="B51" t="n">
-        <v>12.50610733032227</v>
+        <v>12.50610828399658</v>
       </c>
       <c r="C51" t="n">
-        <v>12.68976348286829</v>
+        <v>12.68976445054762</v>
       </c>
       <c r="D51" t="n">
-        <v>12.24374127896527</v>
+        <v>12.24374221263242</v>
       </c>
       <c r="E51" t="n">
-        <v>12.54983514455488</v>
+        <v>12.54983610156373</v>
       </c>
       <c r="F51" t="n">
         <v>1554600</v>
@@ -1452,16 +1452,16 @@
         <v>43647</v>
       </c>
       <c r="B52" t="n">
-        <v>12.24374103546143</v>
+        <v>12.24374389648438</v>
       </c>
       <c r="C52" t="n">
-        <v>12.68101750101362</v>
+        <v>12.68102046421596</v>
       </c>
       <c r="D52" t="n">
-        <v>12.03384853216565</v>
+        <v>12.03385134414254</v>
       </c>
       <c r="E52" t="n">
-        <v>12.61105333324836</v>
+        <v>12.61105628010201</v>
       </c>
       <c r="F52" t="n">
         <v>990900</v>
@@ -1492,16 +1492,16 @@
         <v>43649</v>
       </c>
       <c r="B54" t="n">
-        <v>12.24374103546143</v>
+        <v>12.24374389648438</v>
       </c>
       <c r="C54" t="n">
-        <v>12.27872311934406</v>
+        <v>12.27872598854135</v>
       </c>
       <c r="D54" t="n">
-        <v>11.91141082155712</v>
+        <v>11.91141360492371</v>
       </c>
       <c r="E54" t="n">
-        <v>12.11255842941124</v>
+        <v>12.11256125978044</v>
       </c>
       <c r="F54" t="n">
         <v>2832200</v>
@@ -1512,16 +1512,16 @@
         <v>43650</v>
       </c>
       <c r="B55" t="n">
-        <v>12.20001316070557</v>
+        <v>12.2000150680542</v>
       </c>
       <c r="C55" t="n">
-        <v>12.59356181091439</v>
+        <v>12.59356377979037</v>
       </c>
       <c r="D55" t="n">
-        <v>12.19126743126925</v>
+        <v>12.19126933725058</v>
       </c>
       <c r="E55" t="n">
-        <v>12.19126743126925</v>
+        <v>12.19126933725058</v>
       </c>
       <c r="F55" t="n">
         <v>336300</v>
@@ -1532,16 +1532,16 @@
         <v>43651</v>
       </c>
       <c r="B56" t="n">
-        <v>12.41865253448486</v>
+        <v>12.41865158081055</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56732661242062</v>
+        <v>12.56732564732907</v>
       </c>
       <c r="D56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374115962366</v>
       </c>
       <c r="E56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374115962366</v>
       </c>
       <c r="F56" t="n">
         <v>2415300</v>
@@ -1572,16 +1572,16 @@
         <v>43656</v>
       </c>
       <c r="B58" t="n">
-        <v>13.3806619644165</v>
+        <v>13.38066101074219</v>
       </c>
       <c r="C58" t="n">
-        <v>13.55557240934219</v>
+        <v>13.55557144320156</v>
       </c>
       <c r="D58" t="n">
-        <v>12.95213116583887</v>
+        <v>12.95213024270705</v>
       </c>
       <c r="E58" t="n">
-        <v>12.987113254824</v>
+        <v>12.98711232919892</v>
       </c>
       <c r="F58" t="n">
         <v>1494100</v>
@@ -1612,16 +1612,16 @@
         <v>43658</v>
       </c>
       <c r="B60" t="n">
-        <v>13.12704086303711</v>
+        <v>13.12703990936279</v>
       </c>
       <c r="C60" t="n">
-        <v>13.5030980896971</v>
+        <v>13.50309710870238</v>
       </c>
       <c r="D60" t="n">
-        <v>12.91714834108194</v>
+        <v>12.91714740265623</v>
       </c>
       <c r="E60" t="n">
-        <v>13.35442484550792</v>
+        <v>13.35442387531424</v>
       </c>
       <c r="F60" t="n">
         <v>162300</v>
@@ -1672,16 +1672,16 @@
         <v>43663</v>
       </c>
       <c r="B63" t="n">
-        <v>13.3806619644165</v>
+        <v>13.38066101074219</v>
       </c>
       <c r="C63" t="n">
-        <v>13.55557240934219</v>
+        <v>13.55557144320156</v>
       </c>
       <c r="D63" t="n">
-        <v>13.11829588000857</v>
+        <v>13.11829494503377</v>
       </c>
       <c r="E63" t="n">
-        <v>13.11829588000857</v>
+        <v>13.11829494503377</v>
       </c>
       <c r="F63" t="n">
         <v>155200</v>
@@ -1712,16 +1712,16 @@
         <v>43665</v>
       </c>
       <c r="B65" t="n">
-        <v>13.40689659118652</v>
+        <v>13.40689849853516</v>
       </c>
       <c r="C65" t="n">
-        <v>13.76546316548612</v>
+        <v>13.76546512384667</v>
       </c>
       <c r="D65" t="n">
-        <v>13.3281866926254</v>
+        <v>13.32818858877628</v>
       </c>
       <c r="E65" t="n">
-        <v>13.66051691208419</v>
+        <v>13.66051885551443</v>
       </c>
       <c r="F65" t="n">
         <v>227100</v>
@@ -1832,16 +1832,16 @@
         <v>43675</v>
       </c>
       <c r="B71" t="n">
-        <v>14.65750980377197</v>
+        <v>14.65750789642334</v>
       </c>
       <c r="C71" t="n">
-        <v>14.76245523912537</v>
+        <v>14.76245331812043</v>
       </c>
       <c r="D71" t="n">
-        <v>14.26396025100267</v>
+        <v>14.26395839486575</v>
       </c>
       <c r="E71" t="n">
-        <v>14.27270598196172</v>
+        <v>14.27270412468674</v>
       </c>
       <c r="F71" t="n">
         <v>1345200</v>
@@ -1852,16 +1852,16 @@
         <v>43676</v>
       </c>
       <c r="B72" t="n">
-        <v>14.86740016937256</v>
+        <v>14.86740207672119</v>
       </c>
       <c r="C72" t="n">
-        <v>14.86740016937256</v>
+        <v>14.86740207672119</v>
       </c>
       <c r="D72" t="n">
-        <v>14.56130630285824</v>
+        <v>14.56130817093788</v>
       </c>
       <c r="E72" t="n">
-        <v>14.64876193158767</v>
+        <v>14.64876381088706</v>
       </c>
       <c r="F72" t="n">
         <v>235800</v>
@@ -1872,16 +1872,16 @@
         <v>43677</v>
       </c>
       <c r="B73" t="n">
-        <v>14.94610977172852</v>
+        <v>14.94611072540283</v>
       </c>
       <c r="C73" t="n">
-        <v>15.03356539872188</v>
+        <v>15.03356635797652</v>
       </c>
       <c r="D73" t="n">
-        <v>14.37765069838766</v>
+        <v>14.37765161579001</v>
       </c>
       <c r="E73" t="n">
-        <v>14.89363706276344</v>
+        <v>14.8936380130896</v>
       </c>
       <c r="F73" t="n">
         <v>584400</v>
@@ -1892,16 +1892,16 @@
         <v>43678</v>
       </c>
       <c r="B74" t="n">
-        <v>14.69249057769775</v>
+        <v>14.69248962402344</v>
       </c>
       <c r="C74" t="n">
-        <v>15.16475002553341</v>
+        <v>15.16474904120522</v>
       </c>
       <c r="D74" t="n">
-        <v>14.63127213106963</v>
+        <v>14.63127118136894</v>
       </c>
       <c r="E74" t="n">
-        <v>14.91987457094334</v>
+        <v>14.91987360250977</v>
       </c>
       <c r="F74" t="n">
         <v>1399900</v>
@@ -1912,16 +1912,16 @@
         <v>43679</v>
       </c>
       <c r="B75" t="n">
-        <v>14.69249057769775</v>
+        <v>14.69248962402344</v>
       </c>
       <c r="C75" t="n">
-        <v>14.86740185498745</v>
+        <v>14.86740088995983</v>
       </c>
       <c r="D75" t="n">
-        <v>14.43887106051301</v>
+        <v>14.43887012330087</v>
       </c>
       <c r="E75" t="n">
-        <v>14.69249057769775</v>
+        <v>14.69248962402344</v>
       </c>
       <c r="F75" t="n">
         <v>1710700</v>
@@ -1952,16 +1952,16 @@
         <v>43683</v>
       </c>
       <c r="B77" t="n">
-        <v>14.60503578186035</v>
+        <v>14.60503673553467</v>
       </c>
       <c r="C77" t="n">
-        <v>14.61377984396094</v>
+        <v>14.61378079820622</v>
       </c>
       <c r="D77" t="n">
-        <v>14.29894189793825</v>
+        <v>14.29894283162536</v>
       </c>
       <c r="E77" t="n">
-        <v>14.34266888075106</v>
+        <v>14.34266981729344</v>
       </c>
       <c r="F77" t="n">
         <v>572500</v>
@@ -1972,16 +1972,16 @@
         <v>43684</v>
       </c>
       <c r="B78" t="n">
-        <v>15.40087699890137</v>
+        <v>15.40087795257568</v>
       </c>
       <c r="C78" t="n">
-        <v>15.40087699890137</v>
+        <v>15.40087795257568</v>
       </c>
       <c r="D78" t="n">
-        <v>14.63126951796932</v>
+        <v>14.63127042398694</v>
       </c>
       <c r="E78" t="n">
-        <v>14.64876097618988</v>
+        <v>14.64876188329063</v>
       </c>
       <c r="F78" t="n">
         <v>470300</v>
@@ -1992,16 +1992,16 @@
         <v>43685</v>
       </c>
       <c r="B79" t="n">
-        <v>15.89937496185303</v>
+        <v>15.89937305450439</v>
       </c>
       <c r="C79" t="n">
-        <v>15.89937496185303</v>
+        <v>15.89937305450439</v>
       </c>
       <c r="D79" t="n">
-        <v>15.40087998253381</v>
+        <v>15.4008781349865</v>
       </c>
       <c r="E79" t="n">
-        <v>15.45335269928383</v>
+        <v>15.4533508454417</v>
       </c>
       <c r="F79" t="n">
         <v>301700</v>
@@ -2052,16 +2052,16 @@
         <v>43690</v>
       </c>
       <c r="B82" t="n">
-        <v>15.56704139709473</v>
+        <v>15.56704330444336</v>
       </c>
       <c r="C82" t="n">
-        <v>15.91686390154143</v>
+        <v>15.916865851752</v>
       </c>
       <c r="D82" t="n">
-        <v>15.3484031658542</v>
+        <v>15.34840504641422</v>
       </c>
       <c r="E82" t="n">
-        <v>15.91686390154143</v>
+        <v>15.916865851752</v>
       </c>
       <c r="F82" t="n">
         <v>1028200</v>
@@ -2072,16 +2072,16 @@
         <v>43691</v>
       </c>
       <c r="B83" t="n">
-        <v>15.08603763580322</v>
+        <v>15.08603858947754</v>
       </c>
       <c r="C83" t="n">
-        <v>16.29291991271347</v>
+        <v>16.29292094268169</v>
       </c>
       <c r="D83" t="n">
-        <v>15.05105471886919</v>
+        <v>15.05105567033204</v>
       </c>
       <c r="E83" t="n">
-        <v>15.74195231562075</v>
+        <v>15.74195331075917</v>
       </c>
       <c r="F83" t="n">
         <v>474000</v>
@@ -2092,16 +2092,16 @@
         <v>43692</v>
       </c>
       <c r="B84" t="n">
-        <v>14.47385215759277</v>
+        <v>14.47385120391846</v>
       </c>
       <c r="C84" t="n">
-        <v>15.33966113586812</v>
+        <v>15.33966012514611</v>
       </c>
       <c r="D84" t="n">
-        <v>14.22023264316839</v>
+        <v>14.22023170620493</v>
       </c>
       <c r="E84" t="n">
-        <v>15.3046782135599</v>
+        <v>15.3046772051429</v>
       </c>
       <c r="F84" t="n">
         <v>1402800</v>
@@ -2112,16 +2112,16 @@
         <v>43693</v>
       </c>
       <c r="B85" t="n">
-        <v>15.56704139709473</v>
+        <v>15.56704330444336</v>
       </c>
       <c r="C85" t="n">
-        <v>15.56704139709473</v>
+        <v>15.56704330444336</v>
       </c>
       <c r="D85" t="n">
-        <v>14.29894065674605</v>
+        <v>14.2989424087209</v>
       </c>
       <c r="E85" t="n">
-        <v>14.61377857543983</v>
+        <v>14.61378036599013</v>
       </c>
       <c r="F85" t="n">
         <v>1108600</v>
@@ -2132,16 +2132,16 @@
         <v>43696</v>
       </c>
       <c r="B86" t="n">
-        <v>15.47959041595459</v>
+        <v>15.47958755493164</v>
       </c>
       <c r="C86" t="n">
-        <v>15.7157184833656</v>
+        <v>15.71571557870016</v>
       </c>
       <c r="D86" t="n">
-        <v>15.12976784423318</v>
+        <v>15.12976504786636</v>
       </c>
       <c r="E86" t="n">
-        <v>15.7157184833656</v>
+        <v>15.71571557870016</v>
       </c>
       <c r="F86" t="n">
         <v>399000</v>
@@ -2172,16 +2172,16 @@
         <v>43698</v>
       </c>
       <c r="B88" t="n">
-        <v>15.74195384979248</v>
+        <v>15.74195194244385</v>
       </c>
       <c r="C88" t="n">
-        <v>15.88188219501111</v>
+        <v>15.88188027070828</v>
       </c>
       <c r="D88" t="n">
-        <v>15.13851181848875</v>
+        <v>15.1385099842552</v>
       </c>
       <c r="E88" t="n">
-        <v>15.21722172118391</v>
+        <v>15.2172198774136</v>
       </c>
       <c r="F88" t="n">
         <v>222500</v>
@@ -2192,16 +2192,16 @@
         <v>43699</v>
       </c>
       <c r="B89" t="n">
-        <v>16.04804992675781</v>
+        <v>16.04804801940918</v>
       </c>
       <c r="C89" t="n">
-        <v>16.24919674202804</v>
+        <v>16.24919481077263</v>
       </c>
       <c r="D89" t="n">
-        <v>15.61077337108636</v>
+        <v>15.61077151570908</v>
       </c>
       <c r="E89" t="n">
-        <v>15.82941164892209</v>
+        <v>15.82940976755913</v>
       </c>
       <c r="F89" t="n">
         <v>1339200</v>
@@ -2212,16 +2212,16 @@
         <v>43700</v>
       </c>
       <c r="B90" t="n">
-        <v>16.17923164367676</v>
+        <v>16.17922973632812</v>
       </c>
       <c r="C90" t="n">
-        <v>16.79141945418205</v>
+        <v>16.79141747466339</v>
       </c>
       <c r="D90" t="n">
-        <v>15.71571792040403</v>
+        <v>15.71571606769843</v>
       </c>
       <c r="E90" t="n">
-        <v>15.80317356020159</v>
+        <v>15.80317169718595</v>
       </c>
       <c r="F90" t="n">
         <v>872600</v>
@@ -2252,16 +2252,16 @@
         <v>43704</v>
       </c>
       <c r="B92" t="n">
-        <v>16.52904891967773</v>
+        <v>16.529052734375</v>
       </c>
       <c r="C92" t="n">
-        <v>16.96632535495004</v>
+        <v>16.96632927056523</v>
       </c>
       <c r="D92" t="n">
-        <v>16.17922810507533</v>
+        <v>16.17923183903834</v>
       </c>
       <c r="E92" t="n">
-        <v>16.61650454034764</v>
+        <v>16.61650837522857</v>
       </c>
       <c r="F92" t="n">
         <v>710600</v>
@@ -2312,16 +2312,16 @@
         <v>43707</v>
       </c>
       <c r="B95" t="n">
-        <v>18.14697456359863</v>
+        <v>18.14697265625</v>
       </c>
       <c r="C95" t="n">
-        <v>18.44432271399054</v>
+        <v>18.44432077538895</v>
       </c>
       <c r="D95" t="n">
-        <v>17.90209912560605</v>
+        <v>17.90209724399519</v>
       </c>
       <c r="E95" t="n">
-        <v>17.91959058576497</v>
+        <v>17.91958870231567</v>
       </c>
       <c r="F95" t="n">
         <v>944900</v>
@@ -2332,16 +2332,16 @@
         <v>43710</v>
       </c>
       <c r="B96" t="n">
-        <v>18.36561393737793</v>
+        <v>18.3656120300293</v>
       </c>
       <c r="C96" t="n">
-        <v>18.68045356723209</v>
+        <v>18.68045162718599</v>
       </c>
       <c r="D96" t="n">
-        <v>17.99830159190727</v>
+        <v>17.99829972270562</v>
       </c>
       <c r="E96" t="n">
-        <v>18.14697567621867</v>
+        <v>18.14697379157657</v>
       </c>
       <c r="F96" t="n">
         <v>340500</v>
@@ -2352,16 +2352,16 @@
         <v>43711</v>
       </c>
       <c r="B97" t="n">
-        <v>18.65421485900879</v>
+        <v>18.65421676635742</v>
       </c>
       <c r="C97" t="n">
-        <v>19.19643843656125</v>
+        <v>19.19644039935094</v>
       </c>
       <c r="D97" t="n">
-        <v>18.36561244446177</v>
+        <v>18.3656143223015</v>
       </c>
       <c r="E97" t="n">
-        <v>18.36561244446177</v>
+        <v>18.3656143223015</v>
       </c>
       <c r="F97" t="n">
         <v>924400</v>
@@ -2392,16 +2392,16 @@
         <v>43713</v>
       </c>
       <c r="B99" t="n">
-        <v>18.53177833557129</v>
+        <v>18.53177642822266</v>
       </c>
       <c r="C99" t="n">
-        <v>19.43256684820771</v>
+        <v>19.4325648481471</v>
       </c>
       <c r="D99" t="n">
-        <v>18.53177833557129</v>
+        <v>18.53177642822266</v>
       </c>
       <c r="E99" t="n">
-        <v>18.98654462288788</v>
+        <v>18.98654266873328</v>
       </c>
       <c r="F99" t="n">
         <v>461900</v>
@@ -2412,16 +2412,16 @@
         <v>43714</v>
       </c>
       <c r="B100" t="n">
-        <v>18.23443222045898</v>
+        <v>18.23442840576172</v>
       </c>
       <c r="C100" t="n">
-        <v>18.62798010925651</v>
+        <v>18.62797621222785</v>
       </c>
       <c r="D100" t="n">
-        <v>18.02453967948478</v>
+        <v>18.02453590869765</v>
       </c>
       <c r="E100" t="n">
-        <v>18.53178040385852</v>
+        <v>18.53177652695513</v>
       </c>
       <c r="F100" t="n">
         <v>948300</v>
@@ -2432,16 +2432,16 @@
         <v>43717</v>
       </c>
       <c r="B101" t="n">
-        <v>17.69220733642578</v>
+        <v>17.69220924377441</v>
       </c>
       <c r="C101" t="n">
-        <v>18.76790715933088</v>
+        <v>18.76790918264778</v>
       </c>
       <c r="D101" t="n">
-        <v>17.44733355642772</v>
+        <v>17.44733543737718</v>
       </c>
       <c r="E101" t="n">
-        <v>18.36561356757549</v>
+        <v>18.36561554752221</v>
       </c>
       <c r="F101" t="n">
         <v>611800</v>
@@ -2452,16 +2452,16 @@
         <v>43718</v>
       </c>
       <c r="B102" t="n">
-        <v>17.56976890563965</v>
+        <v>17.56977081298828</v>
       </c>
       <c r="C102" t="n">
-        <v>17.69220578490153</v>
+        <v>17.69220770554174</v>
       </c>
       <c r="D102" t="n">
-        <v>17.10625524145521</v>
+        <v>17.10625709848547</v>
       </c>
       <c r="E102" t="n">
-        <v>17.69220578490153</v>
+        <v>17.69220770554174</v>
       </c>
       <c r="F102" t="n">
         <v>349000</v>
@@ -2492,16 +2492,16 @@
         <v>43720</v>
       </c>
       <c r="B104" t="n">
-        <v>17.4385871887207</v>
+        <v>17.43858528137207</v>
       </c>
       <c r="C104" t="n">
-        <v>17.75342513265257</v>
+        <v>17.75342319086847</v>
       </c>
       <c r="D104" t="n">
-        <v>17.21120320983369</v>
+        <v>17.21120132735522</v>
       </c>
       <c r="E104" t="n">
-        <v>17.68346095977021</v>
+        <v>17.68345902563847</v>
       </c>
       <c r="F104" t="n">
         <v>415900</v>
@@ -2512,16 +2512,16 @@
         <v>43721</v>
       </c>
       <c r="B105" t="n">
-        <v>16.9663257598877</v>
+        <v>16.96632766723633</v>
       </c>
       <c r="C105" t="n">
-        <v>17.73593323845853</v>
+        <v>17.73593523232617</v>
       </c>
       <c r="D105" t="n">
-        <v>16.72145201786019</v>
+        <v>16.7214538976802</v>
       </c>
       <c r="E105" t="n">
-        <v>17.49105782835376</v>
+        <v>17.4910597946926</v>
       </c>
       <c r="F105" t="n">
         <v>2704200</v>
@@ -2632,16 +2632,16 @@
         <v>43731</v>
       </c>
       <c r="B111" t="n">
-        <v>19.35385513305664</v>
+        <v>19.35385704040527</v>
       </c>
       <c r="C111" t="n">
-        <v>19.75615033840645</v>
+        <v>19.75615228540181</v>
       </c>
       <c r="D111" t="n">
-        <v>19.05650867876847</v>
+        <v>19.05651055681321</v>
       </c>
       <c r="E111" t="n">
-        <v>19.73865887989617</v>
+        <v>19.73866082516773</v>
       </c>
       <c r="F111" t="n">
         <v>258600</v>
@@ -2792,16 +2792,16 @@
         <v>43741</v>
       </c>
       <c r="B119" t="n">
-        <v>18.89034652709961</v>
+        <v>18.89034461975098</v>
       </c>
       <c r="C119" t="n">
-        <v>19.23142168847491</v>
+        <v>19.23141974668809</v>
       </c>
       <c r="D119" t="n">
-        <v>18.76790796377501</v>
+        <v>18.76790606878893</v>
       </c>
       <c r="E119" t="n">
-        <v>18.81163661784722</v>
+        <v>18.81163471844589</v>
       </c>
       <c r="F119" t="n">
         <v>610400</v>
@@ -2812,16 +2812,16 @@
         <v>43742</v>
       </c>
       <c r="B120" t="n">
-        <v>19.41507911682129</v>
+        <v>19.41507530212402</v>
       </c>
       <c r="C120" t="n">
-        <v>19.98353828736043</v>
+        <v>19.98353436097165</v>
       </c>
       <c r="D120" t="n">
-        <v>18.82038275327475</v>
+        <v>18.82037905542412</v>
       </c>
       <c r="E120" t="n">
-        <v>18.89034693321684</v>
+        <v>18.89034322161956</v>
       </c>
       <c r="F120" t="n">
         <v>953700</v>
@@ -2852,16 +2852,16 @@
         <v>43746</v>
       </c>
       <c r="B122" t="n">
-        <v>19.10898399353027</v>
+        <v>19.10898208618164</v>
       </c>
       <c r="C122" t="n">
-        <v>19.3276222505087</v>
+        <v>19.32762032133686</v>
       </c>
       <c r="D122" t="n">
-        <v>18.84661708430964</v>
+        <v>18.84661520314896</v>
       </c>
       <c r="E122" t="n">
-        <v>19.3276222505087</v>
+        <v>19.32762032133686</v>
       </c>
       <c r="F122" t="n">
         <v>324000</v>
@@ -2872,16 +2872,16 @@
         <v>43747</v>
       </c>
       <c r="B123" t="n">
-        <v>18.39184761047363</v>
+        <v>18.39184951782227</v>
       </c>
       <c r="C123" t="n">
-        <v>19.31012746442506</v>
+        <v>19.310129467005</v>
       </c>
       <c r="D123" t="n">
-        <v>18.23442782566431</v>
+        <v>18.23442971668753</v>
       </c>
       <c r="E123" t="n">
-        <v>19.1439619506733</v>
+        <v>19.14396393602085</v>
       </c>
       <c r="F123" t="n">
         <v>1216800</v>
@@ -2892,16 +2892,16 @@
         <v>43748</v>
       </c>
       <c r="B124" t="n">
-        <v>18.33937644958496</v>
+        <v>18.3393726348877</v>
       </c>
       <c r="C124" t="n">
-        <v>18.69794305865369</v>
+        <v>18.69793916937248</v>
       </c>
       <c r="D124" t="n">
-        <v>18.33937644958496</v>
+        <v>18.3393726348877</v>
       </c>
       <c r="E124" t="n">
-        <v>18.4093406253038</v>
+        <v>18.40933679605357</v>
       </c>
       <c r="F124" t="n">
         <v>1209500</v>
@@ -2952,16 +2952,16 @@
         <v>43753</v>
       </c>
       <c r="B127" t="n">
-        <v>20.43830680847168</v>
+        <v>20.43830490112305</v>
       </c>
       <c r="C127" t="n">
-        <v>21.19042134487142</v>
+        <v>21.19041936733377</v>
       </c>
       <c r="D127" t="n">
-        <v>20.01852005011355</v>
+        <v>20.01851818194036</v>
       </c>
       <c r="E127" t="n">
-        <v>20.07099443745686</v>
+        <v>20.07099256438664</v>
       </c>
       <c r="F127" t="n">
         <v>1169600</v>
@@ -2972,16 +2972,16 @@
         <v>43754</v>
       </c>
       <c r="B128" t="n">
-        <v>20.72690773010254</v>
+        <v>20.72690582275391</v>
       </c>
       <c r="C128" t="n">
-        <v>20.91056306795709</v>
+        <v>20.91056114370798</v>
       </c>
       <c r="D128" t="n">
-        <v>20.18468411095937</v>
+        <v>20.18468225350769</v>
       </c>
       <c r="E128" t="n">
-        <v>20.46454081706776</v>
+        <v>20.46453893386288</v>
       </c>
       <c r="F128" t="n">
         <v>774000</v>
@@ -2992,16 +2992,16 @@
         <v>43755</v>
       </c>
       <c r="B129" t="n">
-        <v>20.78812408447266</v>
+        <v>20.78812599182129</v>
       </c>
       <c r="C129" t="n">
-        <v>21.11170774282428</v>
+        <v>21.1117096798623</v>
       </c>
       <c r="D129" t="n">
-        <v>20.70066845559368</v>
+        <v>20.7006703549181</v>
       </c>
       <c r="E129" t="n">
-        <v>20.80561554386393</v>
+        <v>20.80561745281743</v>
       </c>
       <c r="F129" t="n">
         <v>493800</v>
@@ -3012,16 +3012,16 @@
         <v>43756</v>
       </c>
       <c r="B130" t="n">
-        <v>20.58697700500488</v>
+        <v>20.58697891235352</v>
       </c>
       <c r="C130" t="n">
-        <v>21.13794462316327</v>
+        <v>21.13794658155813</v>
       </c>
       <c r="D130" t="n">
-        <v>20.49077564783542</v>
+        <v>20.49077754627116</v>
       </c>
       <c r="E130" t="n">
-        <v>20.78812378083435</v>
+        <v>20.78812570681889</v>
       </c>
       <c r="F130" t="n">
         <v>547000</v>
@@ -3072,16 +3072,16 @@
         <v>43761</v>
       </c>
       <c r="B133" t="n">
-        <v>22.03873634338379</v>
+        <v>22.03873443603516</v>
       </c>
       <c r="C133" t="n">
-        <v>22.80834225208901</v>
+        <v>22.80834027813461</v>
       </c>
       <c r="D133" t="n">
-        <v>21.99500769238621</v>
+        <v>21.99500578882208</v>
       </c>
       <c r="E133" t="n">
-        <v>22.37106575057804</v>
+        <v>22.37106381446786</v>
       </c>
       <c r="F133" t="n">
         <v>2305600</v>
@@ -3112,16 +3112,16 @@
         <v>43763</v>
       </c>
       <c r="B135" t="n">
-        <v>22.70339584350586</v>
+        <v>22.70339393615723</v>
       </c>
       <c r="C135" t="n">
-        <v>23.08819964351982</v>
+        <v>23.0881977038432</v>
       </c>
       <c r="D135" t="n">
-        <v>22.13493670798735</v>
+        <v>22.13493484839588</v>
       </c>
       <c r="E135" t="n">
-        <v>22.73837876536055</v>
+        <v>22.73837685507294</v>
       </c>
       <c r="F135" t="n">
         <v>977400</v>
@@ -3132,16 +3132,16 @@
         <v>43766</v>
       </c>
       <c r="B136" t="n">
-        <v>23.61293029785156</v>
+        <v>23.6129322052002</v>
       </c>
       <c r="C136" t="n">
-        <v>24.21637231696944</v>
+        <v>24.21637427306147</v>
       </c>
       <c r="D136" t="n">
-        <v>22.82583295487199</v>
+        <v>22.82583479864237</v>
       </c>
       <c r="E136" t="n">
-        <v>22.87830566624999</v>
+        <v>22.87830751425887</v>
       </c>
       <c r="F136" t="n">
         <v>974800</v>
@@ -3152,16 +3152,16 @@
         <v>43767</v>
       </c>
       <c r="B137" t="n">
-        <v>23.61293029785156</v>
+        <v>23.6129322052002</v>
       </c>
       <c r="C137" t="n">
-        <v>24.92475975884332</v>
+        <v>24.92476177215576</v>
       </c>
       <c r="D137" t="n">
-        <v>23.61293029785156</v>
+        <v>23.6129322052002</v>
       </c>
       <c r="E137" t="n">
-        <v>24.40002764083113</v>
+        <v>24.40002961175803</v>
       </c>
       <c r="F137" t="n">
         <v>3282600</v>
@@ -3172,16 +3172,16 @@
         <v>43768</v>
       </c>
       <c r="B138" t="n">
-        <v>23.63916778564453</v>
+        <v>23.63916969299316</v>
       </c>
       <c r="C138" t="n">
-        <v>24.30382825443032</v>
+        <v>24.30383021540771</v>
       </c>
       <c r="D138" t="n">
-        <v>23.62167632560551</v>
+        <v>23.62167823154283</v>
       </c>
       <c r="E138" t="n">
-        <v>23.78784185982132</v>
+        <v>23.78784377916586</v>
       </c>
       <c r="F138" t="n">
         <v>986800</v>
@@ -3192,16 +3192,16 @@
         <v>43769</v>
       </c>
       <c r="B139" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C139" t="n">
-        <v>23.93651617616393</v>
+        <v>23.93651424196111</v>
       </c>
       <c r="D139" t="n">
-        <v>23.35056560354822</v>
+        <v>23.35056371669345</v>
       </c>
       <c r="E139" t="n">
-        <v>23.66540354704859</v>
+        <v>23.66540163475317</v>
       </c>
       <c r="F139" t="n">
         <v>983900</v>
@@ -3212,16 +3212,16 @@
         <v>43770</v>
       </c>
       <c r="B140" t="n">
-        <v>23.84905815124512</v>
+        <v>23.84906005859375</v>
       </c>
       <c r="C140" t="n">
-        <v>24.40002574817014</v>
+        <v>24.40002769958287</v>
       </c>
       <c r="D140" t="n">
-        <v>23.52547284201295</v>
+        <v>23.52547472348257</v>
       </c>
       <c r="E140" t="n">
-        <v>23.75285679778309</v>
+        <v>23.75285869743794</v>
       </c>
       <c r="F140" t="n">
         <v>793300</v>
@@ -3232,16 +3232,16 @@
         <v>43773</v>
       </c>
       <c r="B141" t="n">
-        <v>24.48748207092285</v>
+        <v>24.48748779296875</v>
       </c>
       <c r="C141" t="n">
-        <v>24.64490186541402</v>
+        <v>24.64490762424456</v>
       </c>
       <c r="D141" t="n">
-        <v>24.03271414641001</v>
+        <v>24.03271976218925</v>
       </c>
       <c r="E141" t="n">
-        <v>24.03271414641001</v>
+        <v>24.03271976218925</v>
       </c>
       <c r="F141" t="n">
         <v>674600</v>
@@ -3252,16 +3252,16 @@
         <v>43774</v>
       </c>
       <c r="B142" t="n">
-        <v>24.46124649047852</v>
+        <v>24.46124839782715</v>
       </c>
       <c r="C142" t="n">
-        <v>25.22210832450975</v>
+        <v>25.22211029118606</v>
       </c>
       <c r="D142" t="n">
-        <v>24.43501096839025</v>
+        <v>24.43501287369319</v>
       </c>
       <c r="E142" t="n">
-        <v>24.8897772547205</v>
+        <v>24.88977919548352</v>
       </c>
       <c r="F142" t="n">
         <v>572300</v>
@@ -3272,16 +3272,16 @@
         <v>43775</v>
       </c>
       <c r="B143" t="n">
-        <v>24.40002632141113</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="C143" t="n">
-        <v>24.83730278476286</v>
+        <v>24.83730666782388</v>
       </c>
       <c r="D143" t="n">
-        <v>24.40002632141113</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="E143" t="n">
-        <v>24.65364747083225</v>
+        <v>24.65365132518062</v>
       </c>
       <c r="F143" t="n">
         <v>511100</v>
@@ -3292,16 +3292,16 @@
         <v>43776</v>
       </c>
       <c r="B144" t="n">
-        <v>24.48748207092285</v>
+        <v>24.48748779296875</v>
       </c>
       <c r="C144" t="n">
-        <v>24.79357593042485</v>
+        <v>24.7935817239964</v>
       </c>
       <c r="D144" t="n">
-        <v>24.21637112934215</v>
+        <v>24.21637678803693</v>
       </c>
       <c r="E144" t="n">
-        <v>24.4699906119622</v>
+        <v>24.46999632992083</v>
       </c>
       <c r="F144" t="n">
         <v>513300</v>
@@ -3312,16 +3312,16 @@
         <v>43777</v>
       </c>
       <c r="B145" t="n">
-        <v>24.05020713806152</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C145" t="n">
-        <v>24.74110479834119</v>
+        <v>24.74110676048281</v>
       </c>
       <c r="D145" t="n">
-        <v>24.04146140802384</v>
+        <v>24.04146331467888</v>
       </c>
       <c r="E145" t="n">
-        <v>24.37379247714588</v>
+        <v>24.37379441015708</v>
       </c>
       <c r="F145" t="n">
         <v>636200</v>
@@ -3352,16 +3352,16 @@
         <v>43781</v>
       </c>
       <c r="B147" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C147" t="n">
-        <v>25.46698462970316</v>
+        <v>25.46698264535181</v>
       </c>
       <c r="D147" t="n">
-        <v>24.17264489473525</v>
+        <v>24.17264301123702</v>
       </c>
       <c r="E147" t="n">
-        <v>24.90726956363575</v>
+        <v>24.9072676228966</v>
       </c>
       <c r="F147" t="n">
         <v>1405000</v>
@@ -3372,16 +3372,16 @@
         <v>43782</v>
       </c>
       <c r="B148" t="n">
-        <v>24.31257057189941</v>
+        <v>24.31257247924805</v>
       </c>
       <c r="C148" t="n">
-        <v>24.67113713658429</v>
+        <v>24.67113907206287</v>
       </c>
       <c r="D148" t="n">
-        <v>24.27758932240879</v>
+        <v>24.2775912270131</v>
       </c>
       <c r="E148" t="n">
-        <v>24.57493744942707</v>
+        <v>24.57493937735868</v>
       </c>
       <c r="F148" t="n">
         <v>593100</v>
@@ -3392,16 +3392,16 @@
         <v>43783</v>
       </c>
       <c r="B149" t="n">
-        <v>24.05020713806152</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C149" t="n">
-        <v>25.04719700927275</v>
+        <v>25.04719899568961</v>
       </c>
       <c r="D149" t="n">
-        <v>23.48174803023192</v>
+        <v>23.4817498924978</v>
       </c>
       <c r="E149" t="n">
-        <v>24.63615770596648</v>
+        <v>24.63615965978507</v>
       </c>
       <c r="F149" t="n">
         <v>1658400</v>
@@ -3412,16 +3412,16 @@
         <v>43787</v>
       </c>
       <c r="B150" t="n">
-        <v>24.05020713806152</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C150" t="n">
-        <v>24.60992051585345</v>
+        <v>24.60992246759124</v>
       </c>
       <c r="D150" t="n">
-        <v>23.91027879361354</v>
+        <v>23.91028068986488</v>
       </c>
       <c r="E150" t="n">
-        <v>24.43501091933219</v>
+        <v>24.43501285719844</v>
       </c>
       <c r="F150" t="n">
         <v>1045200</v>
@@ -3432,16 +3432,16 @@
         <v>43788</v>
       </c>
       <c r="B151" t="n">
-        <v>23.71787643432617</v>
+        <v>23.7178783416748</v>
       </c>
       <c r="C151" t="n">
-        <v>24.31257103152811</v>
+        <v>24.312572986701</v>
       </c>
       <c r="D151" t="n">
-        <v>23.71787643432617</v>
+        <v>23.7178783416748</v>
       </c>
       <c r="E151" t="n">
-        <v>24.24260686314686</v>
+        <v>24.24260881269336</v>
       </c>
       <c r="F151" t="n">
         <v>778500</v>
@@ -3452,16 +3452,16 @@
         <v>43790</v>
       </c>
       <c r="B152" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C152" t="n">
-        <v>23.97149676299973</v>
+        <v>23.97149870651001</v>
       </c>
       <c r="D152" t="n">
-        <v>23.45551037749579</v>
+        <v>23.45551227917201</v>
       </c>
       <c r="E152" t="n">
-        <v>23.87529540256013</v>
+        <v>23.87529733827079</v>
       </c>
       <c r="F152" t="n">
         <v>699200</v>
@@ -3472,16 +3472,16 @@
         <v>43791</v>
       </c>
       <c r="B153" t="n">
-        <v>23.30683708190918</v>
+        <v>23.30683517456055</v>
       </c>
       <c r="C153" t="n">
-        <v>23.66540367793259</v>
+        <v>23.66540174124015</v>
       </c>
       <c r="D153" t="n">
-        <v>23.07070737191987</v>
+        <v>23.07070548389525</v>
       </c>
       <c r="E153" t="n">
-        <v>23.53422106174213</v>
+        <v>23.5342191357852</v>
       </c>
       <c r="F153" t="n">
         <v>919200</v>
@@ -3532,16 +3532,16 @@
         <v>43796</v>
       </c>
       <c r="B156" t="n">
-        <v>22.91328811645508</v>
+        <v>22.91329002380371</v>
       </c>
       <c r="C156" t="n">
-        <v>23.62167554381599</v>
+        <v>23.62167751013223</v>
       </c>
       <c r="D156" t="n">
-        <v>22.70339393908844</v>
+        <v>22.70339582896505</v>
       </c>
       <c r="E156" t="n">
-        <v>23.42927449398685</v>
+        <v>23.42927644428724</v>
       </c>
       <c r="F156" t="n">
         <v>1534800</v>
@@ -3552,16 +3552,16 @@
         <v>43797</v>
       </c>
       <c r="B157" t="n">
-        <v>23.42927742004395</v>
+        <v>23.42927360534668</v>
       </c>
       <c r="C157" t="n">
-        <v>23.58669557061263</v>
+        <v>23.58669173028493</v>
       </c>
       <c r="D157" t="n">
-        <v>22.5459786239224</v>
+        <v>22.54597495304167</v>
       </c>
       <c r="E157" t="n">
-        <v>22.91329097807118</v>
+        <v>22.91328724738556</v>
       </c>
       <c r="F157" t="n">
         <v>1150500</v>
@@ -3572,16 +3572,16 @@
         <v>43798</v>
       </c>
       <c r="B158" t="n">
-        <v>23.63042259216309</v>
+        <v>23.63042068481445</v>
       </c>
       <c r="C158" t="n">
-        <v>24.01522471329396</v>
+        <v>24.01522277488572</v>
       </c>
       <c r="D158" t="n">
-        <v>23.48174851461059</v>
+        <v>23.48174661926231</v>
       </c>
       <c r="E158" t="n">
-        <v>23.56920414871397</v>
+        <v>23.56920224630663</v>
       </c>
       <c r="F158" t="n">
         <v>1630000</v>
@@ -3592,16 +3592,16 @@
         <v>43801</v>
       </c>
       <c r="B159" t="n">
-        <v>25.08217811584473</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C159" t="n">
-        <v>25.44074468107603</v>
+        <v>25.44074661569149</v>
       </c>
       <c r="D159" t="n">
-        <v>23.79658425057789</v>
+        <v>23.79658606016485</v>
       </c>
       <c r="E159" t="n">
-        <v>23.79658425057789</v>
+        <v>23.79658606016485</v>
       </c>
       <c r="F159" t="n">
         <v>1775700</v>
@@ -3612,16 +3612,16 @@
         <v>43802</v>
       </c>
       <c r="B160" t="n">
-        <v>26.34153747558594</v>
+        <v>26.3415355682373</v>
       </c>
       <c r="C160" t="n">
-        <v>26.39401018928447</v>
+        <v>26.39400827813636</v>
       </c>
       <c r="D160" t="n">
-        <v>25.20461755826795</v>
+        <v>25.20461573324187</v>
       </c>
       <c r="E160" t="n">
-        <v>25.44949300232355</v>
+        <v>25.44949115956643</v>
       </c>
       <c r="F160" t="n">
         <v>1627600</v>
@@ -3632,16 +3632,16 @@
         <v>43803</v>
       </c>
       <c r="B161" t="n">
-        <v>25.93049621582031</v>
+        <v>25.93049430847168</v>
       </c>
       <c r="C161" t="n">
-        <v>26.93623183606152</v>
+        <v>26.9362298547348</v>
       </c>
       <c r="D161" t="n">
-        <v>25.68562244245087</v>
+        <v>25.68562055311423</v>
       </c>
       <c r="E161" t="n">
-        <v>26.60390242874122</v>
+        <v>26.60390047185939</v>
       </c>
       <c r="F161" t="n">
         <v>2204100</v>
@@ -3672,16 +3672,16 @@
         <v>43805</v>
       </c>
       <c r="B163" t="n">
-        <v>26.80504989624023</v>
+        <v>26.8050479888916</v>
       </c>
       <c r="C163" t="n">
-        <v>27.46096466532317</v>
+        <v>27.46096271130205</v>
       </c>
       <c r="D163" t="n">
-        <v>26.64763008476793</v>
+        <v>26.64762818862071</v>
       </c>
       <c r="E163" t="n">
-        <v>26.76132291219905</v>
+        <v>26.76132100796186</v>
       </c>
       <c r="F163" t="n">
         <v>1348800</v>
@@ -3712,16 +3712,16 @@
         <v>43809</v>
       </c>
       <c r="B165" t="n">
-        <v>26.00920486450195</v>
+        <v>26.00920677185059</v>
       </c>
       <c r="C165" t="n">
-        <v>26.36777144512823</v>
+        <v>26.36777337877184</v>
       </c>
       <c r="D165" t="n">
-        <v>25.86053079438296</v>
+        <v>25.86053269082878</v>
       </c>
       <c r="E165" t="n">
-        <v>26.36777144512823</v>
+        <v>26.36777337877184</v>
       </c>
       <c r="F165" t="n">
         <v>763900</v>
@@ -3732,16 +3732,16 @@
         <v>43810</v>
       </c>
       <c r="B166" t="n">
-        <v>26.90124893188477</v>
+        <v>26.90125274658203</v>
       </c>
       <c r="C166" t="n">
-        <v>27.02368581105319</v>
+        <v>27.02368964311247</v>
       </c>
       <c r="D166" t="n">
-        <v>26.15787859105349</v>
+        <v>26.15788230033807</v>
       </c>
       <c r="E166" t="n">
-        <v>26.15787859105349</v>
+        <v>26.15788230033807</v>
       </c>
       <c r="F166" t="n">
         <v>1303000</v>
@@ -3752,16 +3752,16 @@
         <v>43811</v>
       </c>
       <c r="B167" t="n">
-        <v>28.2043342590332</v>
+        <v>28.20433616638184</v>
       </c>
       <c r="C167" t="n">
-        <v>28.52791793501346</v>
+        <v>28.52791986424479</v>
       </c>
       <c r="D167" t="n">
-        <v>27.13738019919937</v>
+        <v>27.13738203439408</v>
       </c>
       <c r="E167" t="n">
-        <v>27.16361572163819</v>
+        <v>27.16361755860711</v>
       </c>
       <c r="F167" t="n">
         <v>1320800</v>
@@ -3792,16 +3792,16 @@
         <v>43815</v>
       </c>
       <c r="B169" t="n">
-        <v>29.4811840057373</v>
+        <v>29.48118019104004</v>
       </c>
       <c r="C169" t="n">
-        <v>30.15459028863124</v>
+        <v>30.15458638679904</v>
       </c>
       <c r="D169" t="n">
-        <v>29.21881874470007</v>
+        <v>29.21881496395137</v>
       </c>
       <c r="E169" t="n">
-        <v>29.29752865662677</v>
+        <v>29.29752486569346</v>
       </c>
       <c r="F169" t="n">
         <v>1422400</v>
@@ -3832,16 +3832,16 @@
         <v>43817</v>
       </c>
       <c r="B171" t="n">
-        <v>29.01766777038574</v>
+        <v>29.01766967773438</v>
       </c>
       <c r="C171" t="n">
-        <v>29.19257903136893</v>
+        <v>29.19258095021458</v>
       </c>
       <c r="D171" t="n">
-        <v>28.56289982629139</v>
+        <v>28.56290170374785</v>
       </c>
       <c r="E171" t="n">
-        <v>28.59788274571899</v>
+        <v>28.5978846254749</v>
       </c>
       <c r="F171" t="n">
         <v>1262800</v>
@@ -3852,16 +3852,16 @@
         <v>43818</v>
       </c>
       <c r="B172" t="n">
-        <v>29.16634178161621</v>
+        <v>29.16633987426758</v>
       </c>
       <c r="C172" t="n">
-        <v>29.47243733925006</v>
+        <v>29.47243541188415</v>
       </c>
       <c r="D172" t="n">
-        <v>28.77279559290198</v>
+        <v>28.77279371128951</v>
       </c>
       <c r="E172" t="n">
-        <v>29.03516083076314</v>
+        <v>29.03515893199315</v>
       </c>
       <c r="F172" t="n">
         <v>679700</v>
@@ -3892,16 +3892,16 @@
         <v>43822</v>
       </c>
       <c r="B174" t="n">
-        <v>30.25953102111816</v>
+        <v>30.25952911376953</v>
       </c>
       <c r="C174" t="n">
-        <v>30.60935353888158</v>
+        <v>30.60935160948259</v>
       </c>
       <c r="D174" t="n">
-        <v>29.08762992361194</v>
+        <v>29.08762809013173</v>
       </c>
       <c r="E174" t="n">
-        <v>29.08762992361194</v>
+        <v>29.08762809013173</v>
       </c>
       <c r="F174" t="n">
         <v>827300</v>
@@ -3932,16 +3932,16 @@
         <v>43826</v>
       </c>
       <c r="B176" t="n">
-        <v>30.60935592651367</v>
+        <v>30.6093578338623</v>
       </c>
       <c r="C176" t="n">
-        <v>31.13408640793475</v>
+        <v>31.1340883479807</v>
       </c>
       <c r="D176" t="n">
-        <v>30.4344446539883</v>
+        <v>30.43444655043776</v>
       </c>
       <c r="E176" t="n">
-        <v>30.9154481513168</v>
+        <v>30.91545007773883</v>
       </c>
       <c r="F176" t="n">
         <v>646400</v>
@@ -3952,16 +3952,16 @@
         <v>43829</v>
       </c>
       <c r="B177" t="n">
-        <v>30.76677894592285</v>
+        <v>30.76677322387695</v>
       </c>
       <c r="C177" t="n">
-        <v>30.99416128860425</v>
+        <v>30.99415552426948</v>
       </c>
       <c r="D177" t="n">
-        <v>30.62685058054459</v>
+        <v>30.62684488452276</v>
       </c>
       <c r="E177" t="n">
-        <v>30.62685058054459</v>
+        <v>30.62684488452276</v>
       </c>
       <c r="F177" t="n">
         <v>643600</v>
@@ -3972,16 +3972,16 @@
         <v>43832</v>
       </c>
       <c r="B178" t="n">
-        <v>32.73452377319336</v>
+        <v>32.73451614379883</v>
       </c>
       <c r="C178" t="n">
-        <v>32.73452377319336</v>
+        <v>32.73451614379883</v>
       </c>
       <c r="D178" t="n">
-        <v>30.86298061733131</v>
+        <v>30.86297342413501</v>
       </c>
       <c r="E178" t="n">
-        <v>30.96792605832819</v>
+        <v>30.96791884067237</v>
       </c>
       <c r="F178" t="n">
         <v>1312600</v>
@@ -3992,16 +3992,16 @@
         <v>43833</v>
       </c>
       <c r="B179" t="n">
-        <v>33.20678329467773</v>
+        <v>33.2067756652832</v>
       </c>
       <c r="C179" t="n">
-        <v>33.90642512893957</v>
+        <v>33.90641733879947</v>
       </c>
       <c r="D179" t="n">
-        <v>31.947424656851</v>
+        <v>31.94741731679927</v>
       </c>
       <c r="E179" t="n">
-        <v>32.35846569404783</v>
+        <v>32.35845825955774</v>
       </c>
       <c r="F179" t="n">
         <v>2515300</v>
@@ -4032,16 +4032,16 @@
         <v>43837</v>
       </c>
       <c r="B181" t="n">
-        <v>33.80147171020508</v>
+        <v>33.80147552490234</v>
       </c>
       <c r="C181" t="n">
-        <v>33.80147171020508</v>
+        <v>33.80147552490234</v>
       </c>
       <c r="D181" t="n">
-        <v>33.23301097744483</v>
+        <v>33.23301472798791</v>
       </c>
       <c r="E181" t="n">
-        <v>33.23301097744483</v>
+        <v>33.23301472798791</v>
       </c>
       <c r="F181" t="n">
         <v>929800</v>
@@ -4052,16 +4052,16 @@
         <v>43838</v>
       </c>
       <c r="B182" t="n">
-        <v>33.80147171020508</v>
+        <v>33.80147552490234</v>
       </c>
       <c r="C182" t="n">
-        <v>34.2912192105232</v>
+        <v>34.29122308049138</v>
       </c>
       <c r="D182" t="n">
-        <v>33.4516492075596</v>
+        <v>33.4516529827773</v>
       </c>
       <c r="E182" t="n">
-        <v>33.6090690001346</v>
+        <v>33.60907279311807</v>
       </c>
       <c r="F182" t="n">
         <v>978500</v>
@@ -4072,16 +4072,16 @@
         <v>43839</v>
       </c>
       <c r="B183" t="n">
-        <v>34.02011108398438</v>
+        <v>34.02011489868164</v>
       </c>
       <c r="C183" t="n">
-        <v>34.17753088185141</v>
+        <v>34.17753471420026</v>
       </c>
       <c r="D183" t="n">
-        <v>33.53036023104752</v>
+        <v>33.5303639908287</v>
       </c>
       <c r="E183" t="n">
-        <v>33.86269128611734</v>
+        <v>33.86269508316303</v>
       </c>
       <c r="F183" t="n">
         <v>1002900</v>
@@ -4112,16 +4112,16 @@
         <v>43843</v>
       </c>
       <c r="B185" t="n">
-        <v>35.20949935913086</v>
+        <v>35.20950317382812</v>
       </c>
       <c r="C185" t="n">
-        <v>35.46312050853727</v>
+        <v>35.46312435071257</v>
       </c>
       <c r="D185" t="n">
-        <v>34.27372799450481</v>
+        <v>34.27373170781794</v>
       </c>
       <c r="E185" t="n">
-        <v>34.41365632932306</v>
+        <v>34.41366005779643</v>
       </c>
       <c r="F185" t="n">
         <v>1839000</v>
@@ -4132,16 +4132,16 @@
         <v>43844</v>
       </c>
       <c r="B186" t="n">
-        <v>36.53007888793945</v>
+        <v>36.53008270263672</v>
       </c>
       <c r="C186" t="n">
-        <v>36.74871713600984</v>
+        <v>36.74872097353867</v>
       </c>
       <c r="D186" t="n">
-        <v>35.20950200134754</v>
+        <v>35.20950567814199</v>
       </c>
       <c r="E186" t="n">
-        <v>35.37566920502018</v>
+        <v>35.37567289916683</v>
       </c>
       <c r="F186" t="n">
         <v>1956900</v>
@@ -4192,16 +4192,16 @@
         <v>43847</v>
       </c>
       <c r="B189" t="n">
-        <v>34.36993026733398</v>
+        <v>34.36993408203125</v>
       </c>
       <c r="C189" t="n">
-        <v>36.23272898493374</v>
+        <v>36.23273300638188</v>
       </c>
       <c r="D189" t="n">
-        <v>33.56534315469845</v>
+        <v>33.56534688009509</v>
       </c>
       <c r="E189" t="n">
-        <v>35.52433989442699</v>
+        <v>35.52434383725146</v>
       </c>
       <c r="F189" t="n">
         <v>3718300</v>
@@ -4212,16 +4212,16 @@
         <v>43850</v>
       </c>
       <c r="B190" t="n">
-        <v>35.62928771972656</v>
+        <v>35.62929153442383</v>
       </c>
       <c r="C190" t="n">
-        <v>36.09279970354303</v>
+        <v>36.09280356786682</v>
       </c>
       <c r="D190" t="n">
-        <v>34.54484062216081</v>
+        <v>34.54484432075029</v>
       </c>
       <c r="E190" t="n">
-        <v>34.58856760128704</v>
+        <v>34.58857130455822</v>
       </c>
       <c r="F190" t="n">
         <v>1893400</v>
@@ -4232,16 +4232,16 @@
         <v>43851</v>
       </c>
       <c r="B191" t="n">
-        <v>35.68175888061523</v>
+        <v>35.6817626953125</v>
       </c>
       <c r="C191" t="n">
-        <v>36.29394659891216</v>
+        <v>36.29395047905773</v>
       </c>
       <c r="D191" t="n">
-        <v>35.28820939484188</v>
+        <v>35.28821316746521</v>
       </c>
       <c r="E191" t="n">
-        <v>35.62928783994857</v>
+        <v>35.62929164903621</v>
       </c>
       <c r="F191" t="n">
         <v>1445700</v>
@@ -4292,16 +4292,16 @@
         <v>43854</v>
       </c>
       <c r="B194" t="n">
-        <v>35.29695892333984</v>
+        <v>35.29696273803711</v>
       </c>
       <c r="C194" t="n">
-        <v>36.04032762433681</v>
+        <v>36.04033151937319</v>
       </c>
       <c r="D194" t="n">
-        <v>34.8072080519041</v>
+        <v>34.80721181367183</v>
       </c>
       <c r="E194" t="n">
-        <v>35.63803405288327</v>
+        <v>35.63803790444202</v>
       </c>
       <c r="F194" t="n">
         <v>1110500</v>
@@ -4312,16 +4312,16 @@
         <v>43857</v>
       </c>
       <c r="B195" t="n">
-        <v>34.71975326538086</v>
+        <v>34.71975708007812</v>
       </c>
       <c r="C195" t="n">
-        <v>35.29695808696688</v>
+        <v>35.29696196508228</v>
       </c>
       <c r="D195" t="n">
-        <v>33.44290674128978</v>
+        <v>33.44291041569851</v>
       </c>
       <c r="E195" t="n">
-        <v>34.47487616738799</v>
+        <v>34.47487995518034</v>
       </c>
       <c r="F195" t="n">
         <v>1317600</v>
@@ -4332,16 +4332,16 @@
         <v>43858</v>
       </c>
       <c r="B196" t="n">
-        <v>36.15402221679688</v>
+        <v>36.15402603149414</v>
       </c>
       <c r="C196" t="n">
-        <v>36.15402221679688</v>
+        <v>36.15402603149414</v>
       </c>
       <c r="D196" t="n">
-        <v>34.02885809739983</v>
+        <v>34.02886168786595</v>
       </c>
       <c r="E196" t="n">
-        <v>34.50111753196695</v>
+        <v>34.50112117226229</v>
       </c>
       <c r="F196" t="n">
         <v>1763600</v>
@@ -4352,16 +4352,16 @@
         <v>43859</v>
       </c>
       <c r="B197" t="n">
-        <v>36.39889144897461</v>
+        <v>36.39889526367188</v>
       </c>
       <c r="C197" t="n">
-        <v>37.01982655513928</v>
+        <v>37.01983043491214</v>
       </c>
       <c r="D197" t="n">
-        <v>35.86541363614879</v>
+        <v>35.86541739493622</v>
       </c>
       <c r="E197" t="n">
-        <v>36.64376853416877</v>
+        <v>36.64377237452978</v>
       </c>
       <c r="F197" t="n">
         <v>1294300</v>
@@ -4372,16 +4372,16 @@
         <v>43860</v>
       </c>
       <c r="B198" t="n">
-        <v>34.98212051391602</v>
+        <v>34.98211669921875</v>
       </c>
       <c r="C198" t="n">
-        <v>35.9878578131531</v>
+        <v>35.98785388878314</v>
       </c>
       <c r="D198" t="n">
-        <v>34.10756750106812</v>
+        <v>34.10756378173828</v>
       </c>
       <c r="E198" t="n">
-        <v>35.53308984613359</v>
+        <v>35.53308597135474</v>
       </c>
       <c r="F198" t="n">
         <v>1862000</v>
@@ -4392,16 +4392,16 @@
         <v>43861</v>
       </c>
       <c r="B199" t="n">
-        <v>34.50111389160156</v>
+        <v>34.50112152099609</v>
       </c>
       <c r="C199" t="n">
-        <v>35.2094996325523</v>
+        <v>35.20950741859553</v>
       </c>
       <c r="D199" t="n">
-        <v>34.19501836320331</v>
+        <v>34.19502592490949</v>
       </c>
       <c r="E199" t="n">
-        <v>34.46613097358667</v>
+        <v>34.46613859524527</v>
       </c>
       <c r="F199" t="n">
         <v>1600100</v>
@@ -4492,16 +4492,16 @@
         <v>43868</v>
       </c>
       <c r="B204" t="n">
-        <v>40.86785888671875</v>
+        <v>40.86786270141602</v>
       </c>
       <c r="C204" t="n">
-        <v>47.30456912203875</v>
+        <v>47.30457353755293</v>
       </c>
       <c r="D204" t="n">
-        <v>40.84162336583092</v>
+        <v>40.84162717807931</v>
       </c>
       <c r="E204" t="n">
-        <v>44.61094443906375</v>
+        <v>44.61094860314898</v>
       </c>
       <c r="F204" t="n">
         <v>8429100</v>
@@ -4512,16 +4512,16 @@
         <v>43871</v>
       </c>
       <c r="B205" t="n">
-        <v>41.96979522705078</v>
+        <v>41.96979904174805</v>
       </c>
       <c r="C205" t="n">
-        <v>43.01925604033116</v>
+        <v>43.01925995041548</v>
       </c>
       <c r="D205" t="n">
-        <v>40.67545399651647</v>
+        <v>40.67545769356912</v>
       </c>
       <c r="E205" t="n">
-        <v>40.85911264137964</v>
+        <v>40.8591163551253</v>
       </c>
       <c r="F205" t="n">
         <v>2911200</v>
@@ -4532,16 +4532,16 @@
         <v>43872</v>
       </c>
       <c r="B206" t="n">
-        <v>42.1796875</v>
+        <v>42.17969131469727</v>
       </c>
       <c r="C206" t="n">
-        <v>43.50900835666273</v>
+        <v>43.50901229158271</v>
       </c>
       <c r="D206" t="n">
-        <v>42.04850656192398</v>
+        <v>42.04851036475734</v>
       </c>
       <c r="E206" t="n">
-        <v>42.85309365781857</v>
+        <v>42.85309753341814</v>
       </c>
       <c r="F206" t="n">
         <v>2189100</v>
@@ -4552,16 +4552,16 @@
         <v>43873</v>
       </c>
       <c r="B207" t="n">
-        <v>41.96979522705078</v>
+        <v>41.96979904174805</v>
       </c>
       <c r="C207" t="n">
-        <v>42.97552906247024</v>
+        <v>42.97553296858015</v>
       </c>
       <c r="D207" t="n">
-        <v>41.14771336418537</v>
+        <v>41.14771710416239</v>
       </c>
       <c r="E207" t="n">
-        <v>42.61696250616338</v>
+        <v>42.61696637968264</v>
       </c>
       <c r="F207" t="n">
         <v>1198300</v>
@@ -4592,16 +4592,16 @@
         <v>43875</v>
       </c>
       <c r="B209" t="n">
-        <v>41.45381546020508</v>
+        <v>41.45381164550781</v>
       </c>
       <c r="C209" t="n">
-        <v>41.81238207341615</v>
+        <v>41.81237822572257</v>
       </c>
       <c r="D209" t="n">
-        <v>40.45682219151946</v>
+        <v>40.45681846856834</v>
       </c>
       <c r="E209" t="n">
-        <v>41.69868924401114</v>
+        <v>41.6986854067799</v>
       </c>
       <c r="F209" t="n">
         <v>954600</v>
@@ -4652,16 +4652,16 @@
         <v>43880</v>
       </c>
       <c r="B212" t="n">
-        <v>44.54098129272461</v>
+        <v>44.54098510742188</v>
       </c>
       <c r="C212" t="n">
-        <v>44.54972535417563</v>
+        <v>44.54972916962178</v>
       </c>
       <c r="D212" t="n">
-        <v>42.97553073677084</v>
+        <v>42.97553441739561</v>
       </c>
       <c r="E212" t="n">
-        <v>43.24664334791823</v>
+        <v>43.24664705176236</v>
       </c>
       <c r="F212" t="n">
         <v>2000400</v>
@@ -4692,16 +4692,16 @@
         <v>43882</v>
       </c>
       <c r="B214" t="n">
-        <v>44.17366790771484</v>
+        <v>44.17367172241211</v>
       </c>
       <c r="C214" t="n">
-        <v>44.88205699616382</v>
+        <v>44.88206087203531</v>
       </c>
       <c r="D214" t="n">
-        <v>42.46829232911409</v>
+        <v>42.46829599654055</v>
       </c>
       <c r="E214" t="n">
-        <v>43.43029923684553</v>
+        <v>43.43030298734784</v>
       </c>
       <c r="F214" t="n">
         <v>811000</v>
@@ -4712,16 +4712,16 @@
         <v>43887</v>
       </c>
       <c r="B215" t="n">
-        <v>41.89109039306641</v>
+        <v>41.89108657836914</v>
       </c>
       <c r="C215" t="n">
-        <v>42.372093879953</v>
+        <v>42.37209002145447</v>
       </c>
       <c r="D215" t="n">
-        <v>40.23818240654671</v>
+        <v>40.23817874236698</v>
       </c>
       <c r="E215" t="n">
-        <v>41.23517563745151</v>
+        <v>41.23517188248333</v>
       </c>
       <c r="F215" t="n">
         <v>987000</v>
@@ -4732,16 +4732,16 @@
         <v>43888</v>
       </c>
       <c r="B216" t="n">
-        <v>39.09252166748047</v>
+        <v>39.0925178527832</v>
       </c>
       <c r="C216" t="n">
-        <v>41.60248796536411</v>
+        <v>41.60248390574118</v>
       </c>
       <c r="D216" t="n">
-        <v>38.91761039174722</v>
+        <v>38.91760659411801</v>
       </c>
       <c r="E216" t="n">
-        <v>41.10399299802515</v>
+        <v>41.10398898704599</v>
       </c>
       <c r="F216" t="n">
         <v>1773000</v>
@@ -4752,16 +4752,16 @@
         <v>43889</v>
       </c>
       <c r="B217" t="n">
-        <v>38.12176513671875</v>
+        <v>38.12176895141602</v>
       </c>
       <c r="C217" t="n">
-        <v>38.90011676748805</v>
+        <v>38.90012066007195</v>
       </c>
       <c r="D217" t="n">
-        <v>35.47187063282891</v>
+        <v>35.4718741823615</v>
       </c>
       <c r="E217" t="n">
-        <v>38.05179929585391</v>
+        <v>38.05180310354997</v>
       </c>
       <c r="F217" t="n">
         <v>3154200</v>
@@ -4832,16 +4832,16 @@
         <v>43895</v>
       </c>
       <c r="B221" t="n">
-        <v>38.99631500244141</v>
+        <v>38.99632263183594</v>
       </c>
       <c r="C221" t="n">
-        <v>41.9697962775757</v>
+        <v>41.96980448871395</v>
       </c>
       <c r="D221" t="n">
-        <v>37.78068697224536</v>
+        <v>37.78069436380958</v>
       </c>
       <c r="E221" t="n">
-        <v>41.9697962775757</v>
+        <v>41.96980448871395</v>
       </c>
       <c r="F221" t="n">
         <v>1378200</v>
@@ -4852,16 +4852,16 @@
         <v>43896</v>
       </c>
       <c r="B222" t="n">
-        <v>37.85065078735352</v>
+        <v>37.85065841674805</v>
       </c>
       <c r="C222" t="n">
-        <v>38.43660300142383</v>
+        <v>38.43661074892626</v>
       </c>
       <c r="D222" t="n">
-        <v>34.80720690730548</v>
+        <v>34.80721392324599</v>
       </c>
       <c r="E222" t="n">
-        <v>35.85667111949734</v>
+        <v>35.85667834697387</v>
       </c>
       <c r="F222" t="n">
         <v>1754400</v>
@@ -4872,16 +4872,16 @@
         <v>43899</v>
       </c>
       <c r="B223" t="n">
-        <v>30.7492790222168</v>
+        <v>30.74928283691406</v>
       </c>
       <c r="C223" t="n">
-        <v>34.72849394538029</v>
+        <v>34.72849825373142</v>
       </c>
       <c r="D223" t="n">
-        <v>30.7492790222168</v>
+        <v>30.74928283691406</v>
       </c>
       <c r="E223" t="n">
-        <v>33.23300932637068</v>
+        <v>33.23301344919482</v>
       </c>
       <c r="F223" t="n">
         <v>2155800</v>
@@ -4892,16 +4892,16 @@
         <v>43900</v>
       </c>
       <c r="B224" t="n">
-        <v>34.98212051391602</v>
+        <v>34.98211669921875</v>
       </c>
       <c r="C224" t="n">
-        <v>35.40190555974441</v>
+        <v>35.40190169927082</v>
       </c>
       <c r="D224" t="n">
-        <v>31.99989487355088</v>
+        <v>31.99989138405654</v>
       </c>
       <c r="E224" t="n">
-        <v>34.3611886754712</v>
+        <v>34.36118492848473</v>
       </c>
       <c r="F224" t="n">
         <v>1991900</v>
@@ -4912,16 +4912,16 @@
         <v>43901</v>
       </c>
       <c r="B225" t="n">
-        <v>30.88920974731445</v>
+        <v>30.88921165466309</v>
       </c>
       <c r="C225" t="n">
-        <v>34.1950188115032</v>
+        <v>34.19502092297912</v>
       </c>
       <c r="D225" t="n">
-        <v>28.51917206728659</v>
+        <v>28.51917382829</v>
       </c>
       <c r="E225" t="n">
-        <v>33.06684804804742</v>
+        <v>33.06685008986098</v>
       </c>
       <c r="F225" t="n">
         <v>2211100</v>
@@ -4952,16 +4952,16 @@
         <v>43903</v>
       </c>
       <c r="B227" t="n">
-        <v>29.35000038146973</v>
+        <v>29.35000228881836</v>
       </c>
       <c r="C227" t="n">
-        <v>32.29724310760049</v>
+        <v>32.29724520647959</v>
       </c>
       <c r="D227" t="n">
-        <v>26.67386695482255</v>
+        <v>26.67386868825911</v>
       </c>
       <c r="E227" t="n">
-        <v>31.48390853683973</v>
+        <v>31.48391058286321</v>
       </c>
       <c r="F227" t="n">
         <v>2426800</v>
@@ -4992,16 +4992,16 @@
         <v>43907</v>
       </c>
       <c r="B229" t="n">
-        <v>23.61293029785156</v>
+        <v>23.6129322052002</v>
       </c>
       <c r="C229" t="n">
-        <v>24.86354131755609</v>
+        <v>24.86354332592358</v>
       </c>
       <c r="D229" t="n">
-        <v>21.26038233074467</v>
+        <v>21.26038404806483</v>
       </c>
       <c r="E229" t="n">
-        <v>24.6536488039667</v>
+        <v>24.65365079538</v>
       </c>
       <c r="F229" t="n">
         <v>4197400</v>
@@ -5012,16 +5012,16 @@
         <v>43908</v>
       </c>
       <c r="B230" t="n">
-        <v>15.74195384979248</v>
+        <v>15.74195194244385</v>
       </c>
       <c r="C230" t="n">
-        <v>21.86382479137844</v>
+        <v>21.86382214228312</v>
       </c>
       <c r="D230" t="n">
-        <v>13.73048180217792</v>
+        <v>13.73048013854607</v>
       </c>
       <c r="E230" t="n">
-        <v>21.86382479137844</v>
+        <v>21.86382214228312</v>
       </c>
       <c r="F230" t="n">
         <v>5032100</v>
@@ -5032,16 +5032,16 @@
         <v>43909</v>
       </c>
       <c r="B231" t="n">
-        <v>17.87586402893066</v>
+        <v>17.87586212158203</v>
       </c>
       <c r="C231" t="n">
-        <v>19.41507752992625</v>
+        <v>19.41507545834406</v>
       </c>
       <c r="D231" t="n">
-        <v>12.88216546396326</v>
+        <v>12.88216408944057</v>
       </c>
       <c r="E231" t="n">
-        <v>13.96661183250577</v>
+        <v>13.96661034227302</v>
       </c>
       <c r="F231" t="n">
         <v>3933800</v>
@@ -5052,16 +5052,16 @@
         <v>43910</v>
       </c>
       <c r="B232" t="n">
-        <v>19.54626083374023</v>
+        <v>19.5462589263916</v>
       </c>
       <c r="C232" t="n">
-        <v>23.60418641720726</v>
+        <v>23.60418411388116</v>
       </c>
       <c r="D232" t="n">
-        <v>18.40934087762918</v>
+        <v>18.40933908122262</v>
       </c>
       <c r="E232" t="n">
-        <v>20.11471997775699</v>
+        <v>20.1147180149374</v>
       </c>
       <c r="F232" t="n">
         <v>4389300</v>
@@ -5092,16 +5092,16 @@
         <v>43914</v>
       </c>
       <c r="B234" t="n">
-        <v>20.82310676574707</v>
+        <v>20.82310485839844</v>
       </c>
       <c r="C234" t="n">
-        <v>21.68891404816831</v>
+        <v>21.68891206151372</v>
       </c>
       <c r="D234" t="n">
-        <v>18.97780104320539</v>
+        <v>18.97779930488251</v>
       </c>
       <c r="E234" t="n">
-        <v>20.7356511308598</v>
+        <v>20.7356492315219</v>
       </c>
       <c r="F234" t="n">
         <v>2869200</v>
@@ -5112,16 +5112,16 @@
         <v>43915</v>
       </c>
       <c r="B235" t="n">
-        <v>23.10568809509277</v>
+        <v>23.10569000244141</v>
       </c>
       <c r="C235" t="n">
-        <v>24.05020517714482</v>
+        <v>24.05020716246228</v>
       </c>
       <c r="D235" t="n">
-        <v>20.37708226467723</v>
+        <v>20.37708394678252</v>
       </c>
       <c r="E235" t="n">
-        <v>20.86683309839112</v>
+        <v>20.86683482092478</v>
       </c>
       <c r="F235" t="n">
         <v>2938400</v>
@@ -5132,16 +5132,16 @@
         <v>43916</v>
       </c>
       <c r="B236" t="n">
-        <v>25.69436645507812</v>
+        <v>25.69436836242676</v>
       </c>
       <c r="C236" t="n">
-        <v>26.28031703291938</v>
+        <v>26.2803189837644</v>
       </c>
       <c r="D236" t="n">
-        <v>22.33608446330083</v>
+        <v>22.3360861213569</v>
       </c>
       <c r="E236" t="n">
-        <v>22.73837804339134</v>
+        <v>22.73837973131053</v>
       </c>
       <c r="F236" t="n">
         <v>1725800</v>
@@ -5152,16 +5152,16 @@
         <v>43917</v>
       </c>
       <c r="B237" t="n">
-        <v>23.01823425292969</v>
+        <v>23.01823234558105</v>
       </c>
       <c r="C237" t="n">
-        <v>25.23959963112768</v>
+        <v>25.23959753971114</v>
       </c>
       <c r="D237" t="n">
-        <v>23.00074279292559</v>
+        <v>23.00074088702634</v>
       </c>
       <c r="E237" t="n">
-        <v>24.66239479561177</v>
+        <v>24.66239275202387</v>
       </c>
       <c r="F237" t="n">
         <v>2024100</v>
@@ -5172,16 +5172,16 @@
         <v>43920</v>
       </c>
       <c r="B238" t="n">
-        <v>22.8783073425293</v>
+        <v>22.87830543518066</v>
       </c>
       <c r="C238" t="n">
-        <v>24.37379390503352</v>
+        <v>24.37379187300721</v>
       </c>
       <c r="D238" t="n">
-        <v>22.48475780816567</v>
+        <v>22.48475593362699</v>
       </c>
       <c r="E238" t="n">
-        <v>23.19314697002019</v>
+        <v>23.1931450364236</v>
       </c>
       <c r="F238" t="n">
         <v>1330700</v>
@@ -5192,16 +5192,16 @@
         <v>43921</v>
       </c>
       <c r="B239" t="n">
-        <v>21.0417423248291</v>
+        <v>21.04174423217773</v>
       </c>
       <c r="C239" t="n">
-        <v>23.14066895299826</v>
+        <v>23.14067105060608</v>
       </c>
       <c r="D239" t="n">
-        <v>20.40331910762483</v>
+        <v>20.40332095710298</v>
       </c>
       <c r="E239" t="n">
-        <v>23.06196072656243</v>
+        <v>23.06196281703567</v>
       </c>
       <c r="F239" t="n">
         <v>1663000</v>
@@ -5212,16 +5212,16 @@
         <v>43922</v>
       </c>
       <c r="B240" t="n">
-        <v>18.36561393737793</v>
+        <v>18.3656120300293</v>
       </c>
       <c r="C240" t="n">
-        <v>19.78239060364407</v>
+        <v>19.78238854915703</v>
       </c>
       <c r="D240" t="n">
-        <v>18.36561393737793</v>
+        <v>18.3656120300293</v>
       </c>
       <c r="E240" t="n">
-        <v>19.58998786625428</v>
+        <v>19.58998583174911</v>
       </c>
       <c r="F240" t="n">
         <v>2313200</v>
@@ -5232,16 +5232,16 @@
         <v>43923</v>
       </c>
       <c r="B241" t="n">
-        <v>18.40933990478516</v>
+        <v>18.40933799743652</v>
       </c>
       <c r="C241" t="n">
-        <v>19.1964389359129</v>
+        <v>19.19643694701478</v>
       </c>
       <c r="D241" t="n">
-        <v>17.53478690848985</v>
+        <v>17.53478509175161</v>
       </c>
       <c r="E241" t="n">
-        <v>18.67170680452022</v>
+        <v>18.67170486998837</v>
       </c>
       <c r="F241" t="n">
         <v>2890000</v>
@@ -5272,16 +5272,16 @@
         <v>43927</v>
       </c>
       <c r="B243" t="n">
-        <v>20.12346267700195</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C243" t="n">
-        <v>21.40030912605</v>
+        <v>21.40031115442111</v>
       </c>
       <c r="D243" t="n">
-        <v>18.24317425246051</v>
+        <v>18.24317598159103</v>
       </c>
       <c r="E243" t="n">
-        <v>18.88159747698454</v>
+        <v>18.8815992666263</v>
       </c>
       <c r="F243" t="n">
         <v>4954700</v>
@@ -5292,16 +5292,16 @@
         <v>43928</v>
       </c>
       <c r="B244" t="n">
-        <v>22.03873634338379</v>
+        <v>22.03873443603516</v>
       </c>
       <c r="C244" t="n">
-        <v>23.07945321596411</v>
+        <v>23.07945121854635</v>
       </c>
       <c r="D244" t="n">
-        <v>21.86382507554841</v>
+        <v>21.86382318333752</v>
       </c>
       <c r="E244" t="n">
-        <v>22.30110157705938</v>
+        <v>22.30109964700427</v>
       </c>
       <c r="F244" t="n">
         <v>4003700</v>
@@ -5312,16 +5312,16 @@
         <v>43929</v>
       </c>
       <c r="B245" t="n">
-        <v>22.40604591369629</v>
+        <v>22.40604972839355</v>
       </c>
       <c r="C245" t="n">
-        <v>22.92203058734186</v>
+        <v>22.92203448988708</v>
       </c>
       <c r="D245" t="n">
-        <v>21.61020124426561</v>
+        <v>21.61020492346791</v>
       </c>
       <c r="E245" t="n">
-        <v>22.03873363091185</v>
+        <v>22.03873738307308</v>
       </c>
       <c r="F245" t="n">
         <v>2362000</v>
@@ -5332,16 +5332,16 @@
         <v>43930</v>
       </c>
       <c r="B246" t="n">
-        <v>22.40604591369629</v>
+        <v>22.40604972839355</v>
       </c>
       <c r="C246" t="n">
-        <v>23.3942899515264</v>
+        <v>23.3942939344752</v>
       </c>
       <c r="D246" t="n">
-        <v>22.08246060845015</v>
+        <v>22.08246436805603</v>
       </c>
       <c r="E246" t="n">
-        <v>22.9482677747112</v>
+        <v>22.94827168172338</v>
       </c>
       <c r="F246" t="n">
         <v>1841100</v>
@@ -5372,16 +5372,16 @@
         <v>43935</v>
       </c>
       <c r="B248" t="n">
-        <v>21.86382484436035</v>
+        <v>21.86382675170898</v>
       </c>
       <c r="C248" t="n">
-        <v>22.69465085567703</v>
+        <v>22.69465283550497</v>
       </c>
       <c r="D248" t="n">
-        <v>21.58396815324493</v>
+        <v>21.58397003617953</v>
       </c>
       <c r="E248" t="n">
-        <v>21.95128047735329</v>
+        <v>21.95128239233134</v>
       </c>
       <c r="F248" t="n">
         <v>1384100</v>
@@ -5392,16 +5392,16 @@
         <v>43936</v>
       </c>
       <c r="B249" t="n">
-        <v>21.33909225463867</v>
+        <v>21.3390941619873</v>
       </c>
       <c r="C249" t="n">
-        <v>22.37106503194663</v>
+        <v>22.37106703153592</v>
       </c>
       <c r="D249" t="n">
-        <v>20.55199491081855</v>
+        <v>20.55199674781419</v>
       </c>
       <c r="E249" t="n">
-        <v>20.99801712820135</v>
+        <v>20.99801900506372</v>
       </c>
       <c r="F249" t="n">
         <v>1195900</v>
@@ -5432,16 +5432,16 @@
         <v>43938</v>
       </c>
       <c r="B251" t="n">
-        <v>21.89006042480469</v>
+        <v>21.89006233215332</v>
       </c>
       <c r="C251" t="n">
-        <v>22.41479084801674</v>
+        <v>22.41479280108675</v>
       </c>
       <c r="D251" t="n">
-        <v>21.19916280985691</v>
+        <v>21.1991646570055</v>
       </c>
       <c r="E251" t="n">
-        <v>21.66267646297671</v>
+        <v>21.66267835051267</v>
       </c>
       <c r="F251" t="n">
         <v>2043800</v>
@@ -5492,16 +5492,16 @@
         <v>43944</v>
       </c>
       <c r="B254" t="n">
-        <v>25.66812896728516</v>
+        <v>25.66813278198242</v>
       </c>
       <c r="C254" t="n">
-        <v>29.38497727171535</v>
+        <v>29.38498163879612</v>
       </c>
       <c r="D254" t="n">
-        <v>25.39701802458744</v>
+        <v>25.39702179899325</v>
       </c>
       <c r="E254" t="n">
-        <v>27.98569391064498</v>
+        <v>27.98569806976971</v>
       </c>
       <c r="F254" t="n">
         <v>2837200</v>
@@ -5512,16 +5512,16 @@
         <v>43945</v>
       </c>
       <c r="B255" t="n">
-        <v>23.98899078369141</v>
+        <v>23.98898887634277</v>
       </c>
       <c r="C255" t="n">
-        <v>25.56318562977565</v>
+        <v>25.56318359726384</v>
       </c>
       <c r="D255" t="n">
-        <v>22.65092399686548</v>
+        <v>22.65092219590565</v>
       </c>
       <c r="E255" t="n">
-        <v>24.99472647247176</v>
+        <v>24.99472448515776</v>
       </c>
       <c r="F255" t="n">
         <v>1943600</v>
@@ -5552,16 +5552,16 @@
         <v>43949</v>
       </c>
       <c r="B257" t="n">
-        <v>28.33551979064941</v>
+        <v>28.33551788330078</v>
       </c>
       <c r="C257" t="n">
-        <v>28.93896018638572</v>
+        <v>28.93895823841771</v>
       </c>
       <c r="D257" t="n">
-        <v>25.58942211461507</v>
+        <v>25.58942039211449</v>
       </c>
       <c r="E257" t="n">
-        <v>25.81680610486489</v>
+        <v>25.81680436705841</v>
       </c>
       <c r="F257" t="n">
         <v>3349000</v>
@@ -5632,16 +5632,16 @@
         <v>43956</v>
       </c>
       <c r="B261" t="n">
-        <v>26.4639720916748</v>
+        <v>26.46397590637207</v>
       </c>
       <c r="C261" t="n">
-        <v>28.8952298586858</v>
+        <v>28.89523402384113</v>
       </c>
       <c r="D261" t="n">
-        <v>26.25407958682223</v>
+        <v>26.25408337126416</v>
       </c>
       <c r="E261" t="n">
-        <v>28.4229704717095</v>
+        <v>28.42297456879014</v>
       </c>
       <c r="F261" t="n">
         <v>1862000</v>
@@ -5672,16 +5672,16 @@
         <v>43958</v>
       </c>
       <c r="B263" t="n">
-        <v>24.2513542175293</v>
+        <v>24.25135231018066</v>
       </c>
       <c r="C263" t="n">
-        <v>27.18110709243067</v>
+        <v>27.18110495465943</v>
       </c>
       <c r="D263" t="n">
-        <v>24.2513542175293</v>
+        <v>24.25135231018066</v>
       </c>
       <c r="E263" t="n">
-        <v>27.12863437964844</v>
+        <v>27.12863224600413</v>
       </c>
       <c r="F263" t="n">
         <v>2878900</v>
@@ -5752,16 +5752,16 @@
         <v>43964</v>
       </c>
       <c r="B267" t="n">
-        <v>20.28963088989258</v>
+        <v>20.28962898254395</v>
       </c>
       <c r="C267" t="n">
-        <v>21.12920099498067</v>
+        <v>21.12919900870735</v>
       </c>
       <c r="D267" t="n">
-        <v>19.54626048346404</v>
+        <v>19.54625864599675</v>
       </c>
       <c r="E267" t="n">
-        <v>20.81436137153388</v>
+        <v>20.81435941485739</v>
       </c>
       <c r="F267" t="n">
         <v>3188300</v>
@@ -5792,16 +5792,16 @@
         <v>43966</v>
       </c>
       <c r="B269" t="n">
-        <v>21.57522201538086</v>
+        <v>21.57522010803223</v>
       </c>
       <c r="C269" t="n">
-        <v>21.7676230698671</v>
+        <v>21.76762114550933</v>
       </c>
       <c r="D269" t="n">
-        <v>19.91357169222903</v>
+        <v>19.91356993177791</v>
       </c>
       <c r="E269" t="n">
-        <v>20.10597274671526</v>
+        <v>20.10597096925501</v>
       </c>
       <c r="F269" t="n">
         <v>3697100</v>
@@ -5812,16 +5812,16 @@
         <v>43969</v>
       </c>
       <c r="B270" t="n">
-        <v>22.58095741271973</v>
+        <v>22.58095550537109</v>
       </c>
       <c r="C270" t="n">
-        <v>22.82583284476483</v>
+        <v>22.82583091673227</v>
       </c>
       <c r="D270" t="n">
-        <v>20.99801700448714</v>
+        <v>20.99801523084493</v>
       </c>
       <c r="E270" t="n">
-        <v>22.47601199046998</v>
+        <v>22.47601009198578</v>
       </c>
       <c r="F270" t="n">
         <v>4127300</v>
@@ -5832,16 +5832,16 @@
         <v>43970</v>
       </c>
       <c r="B271" t="n">
-        <v>23.81407737731934</v>
+        <v>23.8140754699707</v>
       </c>
       <c r="C271" t="n">
-        <v>24.31257231179547</v>
+        <v>24.31257036452072</v>
       </c>
       <c r="D271" t="n">
-        <v>21.96877171356359</v>
+        <v>21.96876995401162</v>
       </c>
       <c r="E271" t="n">
-        <v>22.43228372796827</v>
+        <v>22.43228193129208</v>
       </c>
       <c r="F271" t="n">
         <v>2191300</v>
@@ -5892,16 +5892,16 @@
         <v>43973</v>
       </c>
       <c r="B274" t="n">
-        <v>22.33608245849609</v>
+        <v>22.33608436584473</v>
       </c>
       <c r="C274" t="n">
-        <v>23.3330722571277</v>
+        <v>23.33307424961244</v>
       </c>
       <c r="D274" t="n">
-        <v>22.12618828902671</v>
+        <v>22.12619017845182</v>
       </c>
       <c r="E274" t="n">
-        <v>22.78210298140589</v>
+        <v>22.78210492684163</v>
       </c>
       <c r="F274" t="n">
         <v>1380900</v>
@@ -5952,16 +5952,16 @@
         <v>43978</v>
       </c>
       <c r="B277" t="n">
-        <v>25.61565780639648</v>
+        <v>25.61565971374512</v>
       </c>
       <c r="C277" t="n">
-        <v>25.71185750073575</v>
+        <v>25.71185941524744</v>
       </c>
       <c r="D277" t="n">
-        <v>24.78483180098069</v>
+        <v>24.7848336464658</v>
       </c>
       <c r="E277" t="n">
-        <v>24.97723285773666</v>
+        <v>24.977234717548</v>
       </c>
       <c r="F277" t="n">
         <v>2308700</v>
@@ -6032,16 +6032,16 @@
         <v>43984</v>
       </c>
       <c r="B281" t="n">
-        <v>26.76132392883301</v>
+        <v>26.76132202148438</v>
       </c>
       <c r="C281" t="n">
-        <v>26.94497927047589</v>
+        <v>26.94497735003766</v>
       </c>
       <c r="D281" t="n">
-        <v>25.41451141780822</v>
+        <v>25.41450960645039</v>
       </c>
       <c r="E281" t="n">
-        <v>25.49322132653448</v>
+        <v>25.49321950956679</v>
       </c>
       <c r="F281" t="n">
         <v>2117500</v>
@@ -6072,16 +6072,16 @@
         <v>43986</v>
       </c>
       <c r="B283" t="n">
-        <v>27.54841995239258</v>
+        <v>27.54841804504395</v>
       </c>
       <c r="C283" t="n">
-        <v>28.80777509205758</v>
+        <v>28.80777309751596</v>
       </c>
       <c r="D283" t="n">
-        <v>27.22483460312466</v>
+        <v>27.22483271817986</v>
       </c>
       <c r="E283" t="n">
-        <v>28.15186033128633</v>
+        <v>28.15185838215777</v>
       </c>
       <c r="F283" t="n">
         <v>1734000</v>
@@ -6092,16 +6092,16 @@
         <v>43987</v>
       </c>
       <c r="B284" t="n">
-        <v>30.8717212677002</v>
+        <v>30.87171936035156</v>
       </c>
       <c r="C284" t="n">
-        <v>31.47516499306896</v>
+        <v>31.47516304843774</v>
       </c>
       <c r="D284" t="n">
-        <v>28.8777414284244</v>
+        <v>28.87773964426989</v>
       </c>
       <c r="E284" t="n">
-        <v>29.27129095884858</v>
+        <v>29.27128915037939</v>
       </c>
       <c r="F284" t="n">
         <v>5814400</v>
@@ -6112,16 +6112,16 @@
         <v>43990</v>
       </c>
       <c r="B285" t="n">
-        <v>30.56562614440918</v>
+        <v>30.56562995910645</v>
       </c>
       <c r="C285" t="n">
-        <v>31.23903231348672</v>
+        <v>31.23903621222744</v>
       </c>
       <c r="D285" t="n">
-        <v>29.14885130534141</v>
+        <v>29.14885494322021</v>
       </c>
       <c r="E285" t="n">
-        <v>30.87171834119228</v>
+        <v>30.87172219409092</v>
       </c>
       <c r="F285" t="n">
         <v>7141600</v>
@@ -6132,16 +6132,16 @@
         <v>43991</v>
       </c>
       <c r="B286" t="n">
-        <v>29.62985420227051</v>
+        <v>29.62985610961914</v>
       </c>
       <c r="C286" t="n">
-        <v>30.60935254973884</v>
+        <v>30.60935452014026</v>
       </c>
       <c r="D286" t="n">
-        <v>28.96519210722957</v>
+        <v>28.96519397179222</v>
       </c>
       <c r="E286" t="n">
-        <v>29.7347996197463</v>
+        <v>29.73480153385054</v>
       </c>
       <c r="F286" t="n">
         <v>3265200</v>
@@ -6172,16 +6172,16 @@
         <v>43994</v>
       </c>
       <c r="B288" t="n">
-        <v>29.31501960754395</v>
+        <v>29.31501579284668</v>
       </c>
       <c r="C288" t="n">
-        <v>29.31501960754395</v>
+        <v>29.31501579284668</v>
       </c>
       <c r="D288" t="n">
-        <v>26.24533810017622</v>
+        <v>26.24533468492967</v>
       </c>
       <c r="E288" t="n">
-        <v>26.24533810017622</v>
+        <v>26.24533468492967</v>
       </c>
       <c r="F288" t="n">
         <v>3674500</v>
@@ -6192,16 +6192,16 @@
         <v>43997</v>
       </c>
       <c r="B289" t="n">
-        <v>28.93021202087402</v>
+        <v>28.93021392822266</v>
       </c>
       <c r="C289" t="n">
-        <v>29.14885024955842</v>
+        <v>29.14885217132172</v>
       </c>
       <c r="D289" t="n">
-        <v>27.22483150182747</v>
+        <v>27.22483329674156</v>
       </c>
       <c r="E289" t="n">
-        <v>28.422969728972</v>
+        <v>28.4229716028785</v>
       </c>
       <c r="F289" t="n">
         <v>3246400</v>
@@ -6212,16 +6212,16 @@
         <v>43998</v>
       </c>
       <c r="B290" t="n">
-        <v>28.67659568786621</v>
+        <v>28.67659187316895</v>
       </c>
       <c r="C290" t="n">
-        <v>30.1196062376785</v>
+        <v>30.1196022310251</v>
       </c>
       <c r="D290" t="n">
-        <v>27.88949659803756</v>
+        <v>27.88949288804396</v>
       </c>
       <c r="E290" t="n">
-        <v>29.6386027210744</v>
+        <v>29.63859877840638</v>
       </c>
       <c r="F290" t="n">
         <v>3546600</v>
@@ -6252,16 +6252,16 @@
         <v>44000</v>
       </c>
       <c r="B292" t="n">
-        <v>29.38498115539551</v>
+        <v>29.38497924804688</v>
       </c>
       <c r="C292" t="n">
-        <v>30.15458877377712</v>
+        <v>30.15458681647405</v>
       </c>
       <c r="D292" t="n">
-        <v>28.86025065968153</v>
+        <v>28.86024878639261</v>
       </c>
       <c r="E292" t="n">
-        <v>29.4811825247126</v>
+        <v>29.48118061111964</v>
       </c>
       <c r="F292" t="n">
         <v>2070300</v>
@@ -6272,16 +6272,16 @@
         <v>44001</v>
       </c>
       <c r="B293" t="n">
-        <v>30.71430206298828</v>
+        <v>30.71429634094238</v>
       </c>
       <c r="C293" t="n">
-        <v>30.71430206298828</v>
+        <v>30.71429634094238</v>
       </c>
       <c r="D293" t="n">
-        <v>29.26254413905392</v>
+        <v>29.26253868746917</v>
       </c>
       <c r="E293" t="n">
-        <v>29.76978650744496</v>
+        <v>29.76978096136143</v>
       </c>
       <c r="F293" t="n">
         <v>2489900</v>
@@ -6292,16 +6292,16 @@
         <v>44004</v>
       </c>
       <c r="B294" t="n">
-        <v>30.32949638366699</v>
+        <v>30.32949447631836</v>
       </c>
       <c r="C294" t="n">
-        <v>31.46641454434282</v>
+        <v>31.46641256549616</v>
       </c>
       <c r="D294" t="n">
-        <v>29.77852709448115</v>
+        <v>29.77852522178165</v>
       </c>
       <c r="E294" t="n">
-        <v>30.90670119361963</v>
+        <v>30.90669924997198</v>
       </c>
       <c r="F294" t="n">
         <v>1699900</v>
@@ -6312,16 +6312,16 @@
         <v>44005</v>
       </c>
       <c r="B295" t="n">
-        <v>29.64734649658203</v>
+        <v>29.6473445892334</v>
       </c>
       <c r="C295" t="n">
-        <v>30.83673571251537</v>
+        <v>30.83673372864792</v>
       </c>
       <c r="D295" t="n">
-        <v>29.48117930006237</v>
+        <v>29.48117740340403</v>
       </c>
       <c r="E295" t="n">
-        <v>30.62684487164969</v>
+        <v>30.62684290128547</v>
       </c>
       <c r="F295" t="n">
         <v>1337100</v>
@@ -6332,16 +6332,16 @@
         <v>44006</v>
       </c>
       <c r="B296" t="n">
-        <v>29.17509078979492</v>
+        <v>29.17508697509766</v>
       </c>
       <c r="C296" t="n">
-        <v>29.47243896541869</v>
+        <v>29.4724351118426</v>
       </c>
       <c r="D296" t="n">
-        <v>28.01193361168703</v>
+        <v>28.01192994907473</v>
       </c>
       <c r="E296" t="n">
-        <v>29.47243896541869</v>
+        <v>29.4724351118426</v>
       </c>
       <c r="F296" t="n">
         <v>2563900</v>
@@ -6352,16 +6352,16 @@
         <v>44007</v>
       </c>
       <c r="B297" t="n">
-        <v>29.05265426635742</v>
+        <v>29.05265235900879</v>
       </c>
       <c r="C297" t="n">
-        <v>29.36749390765471</v>
+        <v>29.3674919796364</v>
       </c>
       <c r="D297" t="n">
-        <v>28.36175653530562</v>
+        <v>28.36175467331542</v>
       </c>
       <c r="E297" t="n">
-        <v>29.03516280449032</v>
+        <v>29.03516089829003</v>
       </c>
       <c r="F297" t="n">
         <v>2662400</v>
@@ -6432,16 +6432,16 @@
         <v>44013</v>
       </c>
       <c r="B301" t="n">
-        <v>28.17809677124023</v>
+        <v>28.17809867858887</v>
       </c>
       <c r="C301" t="n">
-        <v>28.8602469963108</v>
+        <v>28.86024894983354</v>
       </c>
       <c r="D301" t="n">
-        <v>27.80203874045653</v>
+        <v>27.80204062235016</v>
       </c>
       <c r="E301" t="n">
-        <v>28.51917188377552</v>
+        <v>28.5191738142112</v>
       </c>
       <c r="F301" t="n">
         <v>2441400</v>
@@ -6492,16 +6492,16 @@
         <v>44018</v>
       </c>
       <c r="B304" t="n">
-        <v>28.16060829162598</v>
+        <v>28.16060638427734</v>
       </c>
       <c r="C304" t="n">
-        <v>29.29752656575252</v>
+        <v>29.29752458139918</v>
       </c>
       <c r="D304" t="n">
-        <v>28.02067993998202</v>
+        <v>28.02067804211088</v>
       </c>
       <c r="E304" t="n">
-        <v>28.86899411225568</v>
+        <v>28.86899215692731</v>
       </c>
       <c r="F304" t="n">
         <v>1899100</v>
@@ -6512,16 +6512,16 @@
         <v>44019</v>
       </c>
       <c r="B305" t="n">
-        <v>28.39673614501953</v>
+        <v>28.39673805236816</v>
       </c>
       <c r="C305" t="n">
-        <v>29.46368850515272</v>
+        <v>29.46369048416628</v>
       </c>
       <c r="D305" t="n">
-        <v>27.96820371967529</v>
+        <v>27.96820559824031</v>
       </c>
       <c r="E305" t="n">
-        <v>27.98569517950106</v>
+        <v>27.98569705924094</v>
       </c>
       <c r="F305" t="n">
         <v>2271100</v>
@@ -6592,16 +6592,16 @@
         <v>44025</v>
       </c>
       <c r="B309" t="n">
-        <v>28.62411499023438</v>
+        <v>28.62411880493164</v>
       </c>
       <c r="C309" t="n">
-        <v>29.73479753374515</v>
+        <v>29.73480149646159</v>
       </c>
       <c r="D309" t="n">
-        <v>28.51042218318799</v>
+        <v>28.51042598273357</v>
       </c>
       <c r="E309" t="n">
-        <v>29.30626516020381</v>
+        <v>29.30626906581032</v>
       </c>
       <c r="F309" t="n">
         <v>1518500</v>
@@ -6632,16 +6632,16 @@
         <v>44027</v>
       </c>
       <c r="B311" t="n">
-        <v>27.86325836181641</v>
+        <v>27.86326026916504</v>
       </c>
       <c r="C311" t="n">
-        <v>29.09637792509101</v>
+        <v>29.09637991685148</v>
       </c>
       <c r="D311" t="n">
-        <v>27.68834709930589</v>
+        <v>27.68834899468117</v>
       </c>
       <c r="E311" t="n">
-        <v>28.96519364416941</v>
+        <v>28.96519562694981</v>
       </c>
       <c r="F311" t="n">
         <v>2158900</v>
@@ -6652,16 +6652,16 @@
         <v>44028</v>
       </c>
       <c r="B312" t="n">
-        <v>27.54841995239258</v>
+        <v>27.54841804504395</v>
       </c>
       <c r="C312" t="n">
-        <v>27.91573228514758</v>
+        <v>27.91573035236763</v>
       </c>
       <c r="D312" t="n">
-        <v>26.92748811287299</v>
+        <v>26.92748624851534</v>
       </c>
       <c r="E312" t="n">
-        <v>27.81078518947008</v>
+        <v>27.81078326395627</v>
       </c>
       <c r="F312" t="n">
         <v>1600600</v>
@@ -6672,16 +6672,16 @@
         <v>44029</v>
       </c>
       <c r="B313" t="n">
-        <v>28.07315063476562</v>
+        <v>28.07314872741699</v>
       </c>
       <c r="C313" t="n">
-        <v>28.34426327224438</v>
+        <v>28.34426134647578</v>
       </c>
       <c r="D313" t="n">
-        <v>27.15487063010601</v>
+        <v>27.15486878514724</v>
       </c>
       <c r="E313" t="n">
-        <v>27.54842015671871</v>
+        <v>27.54841828502136</v>
       </c>
       <c r="F313" t="n">
         <v>1920600</v>
@@ -6712,16 +6712,16 @@
         <v>44033</v>
       </c>
       <c r="B315" t="n">
-        <v>28.75530052185059</v>
+        <v>28.75530242919922</v>
       </c>
       <c r="C315" t="n">
-        <v>29.41995926339126</v>
+        <v>29.41996121482692</v>
       </c>
       <c r="D315" t="n">
-        <v>28.24805823433818</v>
+        <v>28.24806010804126</v>
       </c>
       <c r="E315" t="n">
-        <v>29.20132103659892</v>
+        <v>29.20132297353225</v>
       </c>
       <c r="F315" t="n">
         <v>1290100</v>
@@ -6732,16 +6732,16 @@
         <v>44034</v>
       </c>
       <c r="B316" t="n">
-        <v>28.11688041687012</v>
+        <v>28.11687850952148</v>
       </c>
       <c r="C316" t="n">
-        <v>28.6940852661421</v>
+        <v>28.69408331963795</v>
       </c>
       <c r="D316" t="n">
-        <v>27.92447768839448</v>
+        <v>27.92447579409775</v>
       </c>
       <c r="E316" t="n">
-        <v>28.58913650361632</v>
+        <v>28.58913456423152</v>
       </c>
       <c r="F316" t="n">
         <v>1990600</v>
@@ -6752,16 +6752,16 @@
         <v>44035</v>
       </c>
       <c r="B317" t="n">
-        <v>27.02368927001953</v>
+        <v>27.0236873626709</v>
       </c>
       <c r="C317" t="n">
-        <v>28.24806322265285</v>
+        <v>28.24806122888715</v>
       </c>
       <c r="D317" t="n">
-        <v>26.81379673540333</v>
+        <v>26.81379484286904</v>
       </c>
       <c r="E317" t="n">
-        <v>27.98569797140199</v>
+        <v>27.98569599615419</v>
       </c>
       <c r="F317" t="n">
         <v>1990400</v>
@@ -6812,16 +6812,16 @@
         <v>44040</v>
       </c>
       <c r="B320" t="n">
-        <v>24.63615798950195</v>
+        <v>24.63615608215332</v>
       </c>
       <c r="C320" t="n">
-        <v>25.18712564359724</v>
+        <v>25.1871236935923</v>
       </c>
       <c r="D320" t="n">
-        <v>24.35630129738515</v>
+        <v>24.35629941170321</v>
       </c>
       <c r="E320" t="n">
-        <v>24.9247604117571</v>
+        <v>24.92475848206466</v>
       </c>
       <c r="F320" t="n">
         <v>2550000</v>
@@ -6872,16 +6872,16 @@
         <v>44043</v>
       </c>
       <c r="B323" t="n">
-        <v>25.45823669433594</v>
+        <v>25.45823860168457</v>
       </c>
       <c r="C323" t="n">
-        <v>25.79931180818481</v>
+        <v>25.79931374108703</v>
       </c>
       <c r="D323" t="n">
-        <v>24.95099605432184</v>
+        <v>24.95099792366765</v>
       </c>
       <c r="E323" t="n">
-        <v>25.79931180818481</v>
+        <v>25.79931374108703</v>
       </c>
       <c r="F323" t="n">
         <v>1806700</v>
@@ -6892,16 +6892,16 @@
         <v>44046</v>
       </c>
       <c r="B324" t="n">
-        <v>25.67687606811523</v>
+        <v>25.6768741607666</v>
       </c>
       <c r="C324" t="n">
-        <v>26.24533517241919</v>
+        <v>26.24533322284386</v>
       </c>
       <c r="D324" t="n">
-        <v>25.29207228923116</v>
+        <v>25.29207041046681</v>
       </c>
       <c r="E324" t="n">
-        <v>25.53694772453511</v>
+        <v>25.53694582758073</v>
       </c>
       <c r="F324" t="n">
         <v>1504200</v>
@@ -6912,16 +6912,16 @@
         <v>44047</v>
       </c>
       <c r="B325" t="n">
-        <v>25.59816551208496</v>
+        <v>25.59816741943359</v>
       </c>
       <c r="C325" t="n">
-        <v>25.95673209185421</v>
+        <v>25.95673402592005</v>
       </c>
       <c r="D325" t="n">
-        <v>25.20461601327608</v>
+        <v>25.20461789130089</v>
       </c>
       <c r="E325" t="n">
-        <v>25.20461601327608</v>
+        <v>25.20461789130089</v>
       </c>
       <c r="F325" t="n">
         <v>2035900</v>
@@ -6952,16 +6952,16 @@
         <v>44049</v>
       </c>
       <c r="B327" t="n">
-        <v>26.3852653503418</v>
+        <v>26.38526344299316</v>
       </c>
       <c r="C327" t="n">
-        <v>26.65637632636665</v>
+        <v>26.65637439941984</v>
       </c>
       <c r="D327" t="n">
-        <v>25.74684202986365</v>
+        <v>25.74684016866562</v>
       </c>
       <c r="E327" t="n">
-        <v>25.7555877604551</v>
+        <v>25.75558589862485</v>
       </c>
       <c r="F327" t="n">
         <v>1665200</v>
@@ -6992,16 +6992,16 @@
         <v>44053</v>
       </c>
       <c r="B329" t="n">
-        <v>25.26583290100098</v>
+        <v>25.26583671569824</v>
       </c>
       <c r="C329" t="n">
-        <v>26.34153424228719</v>
+        <v>26.34153821939647</v>
       </c>
       <c r="D329" t="n">
-        <v>25.04719467467019</v>
+        <v>25.04719845635692</v>
       </c>
       <c r="E329" t="n">
-        <v>26.21909570124939</v>
+        <v>26.2190996598726</v>
       </c>
       <c r="F329" t="n">
         <v>1821300</v>
@@ -7012,16 +7012,16 @@
         <v>44054</v>
       </c>
       <c r="B330" t="n">
-        <v>26.04418754577637</v>
+        <v>26.044189453125</v>
       </c>
       <c r="C330" t="n">
-        <v>26.98870466847201</v>
+        <v>26.98870664499245</v>
       </c>
       <c r="D330" t="n">
-        <v>25.20461584333725</v>
+        <v>25.20461768919977</v>
       </c>
       <c r="E330" t="n">
-        <v>25.44949127073145</v>
+        <v>25.44949313452744</v>
       </c>
       <c r="F330" t="n">
         <v>2049400</v>
@@ -7052,16 +7052,16 @@
         <v>44056</v>
       </c>
       <c r="B332" t="n">
-        <v>25.08217811584473</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C332" t="n">
-        <v>25.4932173894306</v>
+        <v>25.4932193280363</v>
       </c>
       <c r="D332" t="n">
-        <v>24.4962275903072</v>
+        <v>24.49622945309782</v>
       </c>
       <c r="E332" t="n">
-        <v>24.91601259329838</v>
+        <v>24.91601448801113</v>
       </c>
       <c r="F332" t="n">
         <v>2154700</v>
@@ -7072,16 +7072,16 @@
         <v>44057</v>
       </c>
       <c r="B333" t="n">
-        <v>25.57192802429199</v>
+        <v>25.57192993164062</v>
       </c>
       <c r="C333" t="n">
-        <v>25.82554918013649</v>
+        <v>25.82555110640212</v>
       </c>
       <c r="D333" t="n">
-        <v>24.60117371728042</v>
+        <v>24.60117555222282</v>
       </c>
       <c r="E333" t="n">
-        <v>24.74110372372808</v>
+        <v>24.74110556910752</v>
       </c>
       <c r="F333" t="n">
         <v>1776900</v>
@@ -7112,16 +7112,16 @@
         <v>44061</v>
       </c>
       <c r="B335" t="n">
-        <v>24.90726852416992</v>
+        <v>24.90726661682129</v>
       </c>
       <c r="C335" t="n">
-        <v>25.03845113783942</v>
+        <v>25.03844922044508</v>
       </c>
       <c r="D335" t="n">
-        <v>23.93651584855371</v>
+        <v>23.93651401554337</v>
       </c>
       <c r="E335" t="n">
-        <v>23.96275137044115</v>
+        <v>23.96274953542175</v>
       </c>
       <c r="F335" t="n">
         <v>2792800</v>
@@ -7132,16 +7132,16 @@
         <v>44062</v>
       </c>
       <c r="B336" t="n">
-        <v>23.99773406982422</v>
+        <v>23.99773597717285</v>
       </c>
       <c r="C336" t="n">
-        <v>24.92475975505585</v>
+        <v>24.92476173608482</v>
       </c>
       <c r="D336" t="n">
-        <v>23.78784155626672</v>
+        <v>23.78784344693302</v>
       </c>
       <c r="E336" t="n">
-        <v>24.8110686024079</v>
+        <v>24.81107057440066</v>
       </c>
       <c r="F336" t="n">
         <v>1518600</v>
@@ -7152,16 +7152,16 @@
         <v>44063</v>
       </c>
       <c r="B337" t="n">
-        <v>23.87529563903809</v>
+        <v>23.87529754638672</v>
       </c>
       <c r="C337" t="n">
-        <v>23.97149700043054</v>
+        <v>23.9714989154645</v>
       </c>
       <c r="D337" t="n">
-        <v>23.26310955510841</v>
+        <v>23.26311141355075</v>
       </c>
       <c r="E337" t="n">
-        <v>23.6479133326008</v>
+        <v>23.64791522178433</v>
       </c>
       <c r="F337" t="n">
         <v>2411800</v>
@@ -7172,16 +7172,16 @@
         <v>44064</v>
       </c>
       <c r="B338" t="n">
-        <v>24.44375419616699</v>
+        <v>24.44375610351562</v>
       </c>
       <c r="C338" t="n">
-        <v>24.54869960993182</v>
+        <v>24.54870152546935</v>
       </c>
       <c r="D338" t="n">
-        <v>23.52547265129977</v>
+        <v>23.5254744869948</v>
       </c>
       <c r="E338" t="n">
-        <v>23.87529347731131</v>
+        <v>23.87529534030289</v>
       </c>
       <c r="F338" t="n">
         <v>2429700</v>
@@ -7192,16 +7192,16 @@
         <v>44067</v>
       </c>
       <c r="B339" t="n">
-        <v>24.19888305664062</v>
+        <v>24.19887924194336</v>
       </c>
       <c r="C339" t="n">
-        <v>25.05594464871687</v>
+        <v>25.05594069891293</v>
       </c>
       <c r="D339" t="n">
-        <v>24.18139159523232</v>
+        <v>24.18138778329239</v>
       </c>
       <c r="E339" t="n">
-        <v>24.66239677549536</v>
+        <v>24.66239288773007</v>
       </c>
       <c r="F339" t="n">
         <v>1456200</v>
@@ -7232,16 +7232,16 @@
         <v>44069</v>
       </c>
       <c r="B341" t="n">
-        <v>25.5019645690918</v>
+        <v>25.50196647644043</v>
       </c>
       <c r="C341" t="n">
-        <v>26.40275473213788</v>
+        <v>26.40275670685861</v>
       </c>
       <c r="D341" t="n">
-        <v>25.15214371337205</v>
+        <v>25.15214559455681</v>
       </c>
       <c r="E341" t="n">
-        <v>25.62440145157435</v>
+        <v>25.62440336808031</v>
       </c>
       <c r="F341" t="n">
         <v>2402800</v>
@@ -7272,16 +7272,16 @@
         <v>44071</v>
       </c>
       <c r="B343" t="n">
-        <v>26.62139129638672</v>
+        <v>26.62139511108398</v>
       </c>
       <c r="C343" t="n">
-        <v>26.99744931809544</v>
+        <v>26.99745318667973</v>
       </c>
       <c r="D343" t="n">
-        <v>25.88676671167138</v>
+        <v>25.88677042110103</v>
       </c>
       <c r="E343" t="n">
-        <v>26.66511827506467</v>
+        <v>26.66512209602777</v>
       </c>
       <c r="F343" t="n">
         <v>1984400</v>
@@ -7332,16 +7332,16 @@
         <v>44076</v>
       </c>
       <c r="B346" t="n">
-        <v>27.85451316833496</v>
+        <v>27.85451507568359</v>
       </c>
       <c r="C346" t="n">
-        <v>28.37924529789493</v>
+        <v>28.3792472411748</v>
       </c>
       <c r="D346" t="n">
-        <v>27.50469230465414</v>
+        <v>27.50469418804865</v>
       </c>
       <c r="E346" t="n">
-        <v>28.08189714674686</v>
+        <v>28.0818990696657</v>
       </c>
       <c r="F346" t="n">
         <v>1806800</v>
@@ -7352,16 +7352,16 @@
         <v>44077</v>
       </c>
       <c r="B347" t="n">
-        <v>27.37350845336914</v>
+        <v>27.37350654602051</v>
       </c>
       <c r="C347" t="n">
-        <v>28.26555292089662</v>
+        <v>28.26555095139155</v>
       </c>
       <c r="D347" t="n">
-        <v>26.84877798360237</v>
+        <v>26.84877611281624</v>
       </c>
       <c r="E347" t="n">
-        <v>28.07315019177649</v>
+        <v>28.07314823567778</v>
       </c>
       <c r="F347" t="n">
         <v>2237800</v>
@@ -7392,16 +7392,16 @@
         <v>44082</v>
       </c>
       <c r="B349" t="n">
-        <v>26.92748641967773</v>
+        <v>26.927490234375</v>
       </c>
       <c r="C349" t="n">
-        <v>27.78454791952171</v>
+        <v>27.78455185563506</v>
       </c>
       <c r="D349" t="n">
-        <v>26.1141519005713</v>
+        <v>26.11415560004708</v>
       </c>
       <c r="E349" t="n">
-        <v>26.69135672030928</v>
+        <v>26.6913605015551</v>
       </c>
       <c r="F349" t="n">
         <v>1483700</v>
@@ -7472,16 +7472,16 @@
         <v>44088</v>
       </c>
       <c r="B353" t="n">
-        <v>25.55443954467773</v>
+        <v>25.5544376373291</v>
       </c>
       <c r="C353" t="n">
-        <v>25.84304198472778</v>
+        <v>25.84304005583825</v>
       </c>
       <c r="D353" t="n">
-        <v>24.88103496327935</v>
+        <v>24.88103310619272</v>
       </c>
       <c r="E353" t="n">
-        <v>25.09967322598628</v>
+        <v>25.09967135258078</v>
       </c>
       <c r="F353" t="n">
         <v>899700</v>
@@ -7552,16 +7552,16 @@
         <v>44092</v>
       </c>
       <c r="B357" t="n">
-        <v>24.02396965026855</v>
+        <v>24.02397155761719</v>
       </c>
       <c r="C357" t="n">
-        <v>24.96848679762768</v>
+        <v>24.96848877996489</v>
       </c>
       <c r="D357" t="n">
-        <v>23.78784161448684</v>
+        <v>23.78784350308843</v>
       </c>
       <c r="E357" t="n">
-        <v>24.80232293320303</v>
+        <v>24.80232490234791</v>
       </c>
       <c r="F357" t="n">
         <v>1344400</v>
@@ -7572,16 +7572,16 @@
         <v>44095</v>
       </c>
       <c r="B358" t="n">
-        <v>23.42927742004395</v>
+        <v>23.42927360534668</v>
       </c>
       <c r="C358" t="n">
-        <v>23.75286112008121</v>
+        <v>23.75285725269885</v>
       </c>
       <c r="D358" t="n">
-        <v>22.87830805478197</v>
+        <v>22.87830432979218</v>
       </c>
       <c r="E358" t="n">
-        <v>23.49049586772248</v>
+        <v>23.49049204305778</v>
       </c>
       <c r="F358" t="n">
         <v>1701600</v>
@@ -7592,16 +7592,16 @@
         <v>44096</v>
       </c>
       <c r="B359" t="n">
-        <v>23.06196212768555</v>
+        <v>23.06196594238281</v>
       </c>
       <c r="C359" t="n">
-        <v>23.79658507431088</v>
+        <v>23.7965890105227</v>
       </c>
       <c r="D359" t="n">
-        <v>22.9132880588034</v>
+        <v>22.91329184890837</v>
       </c>
       <c r="E359" t="n">
-        <v>23.53421985537879</v>
+        <v>23.53422374819257</v>
       </c>
       <c r="F359" t="n">
         <v>1853300</v>
@@ -7612,16 +7612,16 @@
         <v>44097</v>
       </c>
       <c r="B360" t="n">
-        <v>22.91328811645508</v>
+        <v>22.91329002380371</v>
       </c>
       <c r="C360" t="n">
-        <v>23.32432740530353</v>
+        <v>23.32432934686791</v>
       </c>
       <c r="D360" t="n">
-        <v>22.51973861898936</v>
+        <v>22.51974049357813</v>
       </c>
       <c r="E360" t="n">
-        <v>23.06196218571131</v>
+        <v>23.06196410543587</v>
       </c>
       <c r="F360" t="n">
         <v>3121100</v>
@@ -7632,16 +7632,16 @@
         <v>44098</v>
       </c>
       <c r="B361" t="n">
-        <v>22.83458137512207</v>
+        <v>22.83457946777344</v>
       </c>
       <c r="C361" t="n">
-        <v>23.17565654138019</v>
+        <v>23.1756546055419</v>
       </c>
       <c r="D361" t="n">
-        <v>22.40605056754511</v>
+        <v>22.4060486959912</v>
       </c>
       <c r="E361" t="n">
-        <v>23.0007452587425</v>
+        <v>23.00074333751437</v>
       </c>
       <c r="F361" t="n">
         <v>3887300</v>
@@ -7652,16 +7652,16 @@
         <v>44099</v>
       </c>
       <c r="B362" t="n">
-        <v>22.38855743408203</v>
+        <v>22.3885555267334</v>
       </c>
       <c r="C362" t="n">
-        <v>22.96576228838224</v>
+        <v>22.96576033185978</v>
       </c>
       <c r="D362" t="n">
-        <v>22.18741064172113</v>
+        <v>22.18740875150879</v>
       </c>
       <c r="E362" t="n">
-        <v>22.84332540052386</v>
+        <v>22.84332345443217</v>
       </c>
       <c r="F362" t="n">
         <v>3181400</v>
@@ -7832,16 +7832,16 @@
         <v>44112</v>
       </c>
       <c r="B371" t="n">
-        <v>21.531494140625</v>
+        <v>21.53149604797363</v>
       </c>
       <c r="C371" t="n">
-        <v>21.67142247773394</v>
+        <v>21.67142439747801</v>
       </c>
       <c r="D371" t="n">
-        <v>21.09421767014021</v>
+        <v>21.09421953875309</v>
       </c>
       <c r="E371" t="n">
-        <v>21.48776549273011</v>
+        <v>21.48776739620508</v>
       </c>
       <c r="F371" t="n">
         <v>1373200</v>
@@ -7872,16 +7872,16 @@
         <v>44117</v>
       </c>
       <c r="B373" t="n">
-        <v>21.64518737792969</v>
+        <v>21.64518547058105</v>
       </c>
       <c r="C373" t="n">
-        <v>22.84332575664192</v>
+        <v>22.84332374371474</v>
       </c>
       <c r="D373" t="n">
-        <v>21.4702761056245</v>
+        <v>21.47027421368885</v>
       </c>
       <c r="E373" t="n">
-        <v>21.95128127042501</v>
+        <v>21.95127933610373</v>
       </c>
       <c r="F373" t="n">
         <v>3744600</v>
@@ -7892,16 +7892,16 @@
         <v>44118</v>
       </c>
       <c r="B374" t="n">
-        <v>21.51400184631348</v>
+        <v>21.51400566101074</v>
       </c>
       <c r="C374" t="n">
-        <v>22.01249673642265</v>
+        <v>22.01250063950919</v>
       </c>
       <c r="D374" t="n">
-        <v>21.21665372448041</v>
+        <v>21.2166574864542</v>
       </c>
       <c r="E374" t="n">
-        <v>21.71514861458958</v>
+        <v>21.71515246495265</v>
       </c>
       <c r="F374" t="n">
         <v>2069800</v>
@@ -7912,16 +7912,16 @@
         <v>44119</v>
       </c>
       <c r="B375" t="n">
-        <v>22.11744499206543</v>
+        <v>22.11744689941406</v>
       </c>
       <c r="C375" t="n">
-        <v>22.61593990860884</v>
+        <v>22.61594185894634</v>
       </c>
       <c r="D375" t="n">
-        <v>21.01550807061701</v>
+        <v>21.01550988293759</v>
       </c>
       <c r="E375" t="n">
-        <v>21.19916339015306</v>
+        <v>21.19916521831157</v>
       </c>
       <c r="F375" t="n">
         <v>2238800</v>
@@ -7972,16 +7972,16 @@
         <v>44124</v>
       </c>
       <c r="B378" t="n">
-        <v>22.39730453491211</v>
+        <v>22.39730072021484</v>
       </c>
       <c r="C378" t="n">
-        <v>23.33307604784032</v>
+        <v>23.33307207376293</v>
       </c>
       <c r="D378" t="n">
-        <v>22.06497343599255</v>
+        <v>22.06496967789774</v>
       </c>
       <c r="E378" t="n">
-        <v>22.96576369371099</v>
+        <v>22.96575978219406</v>
       </c>
       <c r="F378" t="n">
         <v>2866000</v>
@@ -7992,16 +7992,16 @@
         <v>44125</v>
       </c>
       <c r="B379" t="n">
-        <v>21.86382484436035</v>
+        <v>21.86382675170898</v>
       </c>
       <c r="C379" t="n">
-        <v>22.42353822659119</v>
+        <v>22.4235401827679</v>
       </c>
       <c r="D379" t="n">
-        <v>21.86382484436035</v>
+        <v>21.86382675170898</v>
       </c>
       <c r="E379" t="n">
-        <v>22.37981124413345</v>
+        <v>22.37981319649553</v>
       </c>
       <c r="F379" t="n">
         <v>1597600</v>
@@ -8012,16 +8012,16 @@
         <v>44126</v>
       </c>
       <c r="B380" t="n">
-        <v>22.07371520996094</v>
+        <v>22.07371711730957</v>
       </c>
       <c r="C380" t="n">
-        <v>22.178662292933</v>
+        <v>22.17866420934991</v>
       </c>
       <c r="D380" t="n">
-        <v>21.4702732360455</v>
+        <v>21.47027509125183</v>
       </c>
       <c r="E380" t="n">
-        <v>21.91629541954149</v>
+        <v>21.91629731328777</v>
       </c>
       <c r="F380" t="n">
         <v>2196600</v>
@@ -8032,16 +8032,16 @@
         <v>44127</v>
       </c>
       <c r="B381" t="n">
-        <v>22.18741035461426</v>
+        <v>22.18741226196289</v>
       </c>
       <c r="C381" t="n">
-        <v>22.34482849350482</v>
+        <v>22.34483041438596</v>
       </c>
       <c r="D381" t="n">
-        <v>21.80260656736768</v>
+        <v>21.80260844163652</v>
       </c>
       <c r="E381" t="n">
-        <v>22.07371753043625</v>
+        <v>22.07371942801124</v>
       </c>
       <c r="F381" t="n">
         <v>1279900</v>
@@ -8052,16 +8052,16 @@
         <v>44130</v>
       </c>
       <c r="B382" t="n">
-        <v>22.08246421813965</v>
+        <v>22.08246231079102</v>
       </c>
       <c r="C382" t="n">
-        <v>22.58095918310227</v>
+        <v>22.58095723269669</v>
       </c>
       <c r="D382" t="n">
-        <v>21.64518769896857</v>
+        <v>21.64518582938921</v>
       </c>
       <c r="E382" t="n">
-        <v>22.20490110972274</v>
+        <v>22.20489919179875</v>
       </c>
       <c r="F382" t="n">
         <v>1812600</v>
@@ -8172,16 +8172,16 @@
         <v>44139</v>
       </c>
       <c r="B388" t="n">
-        <v>21.72389602661133</v>
+        <v>21.72389793395996</v>
       </c>
       <c r="C388" t="n">
-        <v>21.77636873803556</v>
+        <v>21.77637064999127</v>
       </c>
       <c r="D388" t="n">
-        <v>20.53450344714602</v>
+        <v>20.53450525006649</v>
       </c>
       <c r="E388" t="n">
-        <v>20.87558024159705</v>
+        <v>20.87558207446392</v>
       </c>
       <c r="F388" t="n">
         <v>1697200</v>
@@ -8232,16 +8232,16 @@
         <v>44144</v>
       </c>
       <c r="B391" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C391" t="n">
-        <v>24.55744868989206</v>
+        <v>24.55744677641046</v>
       </c>
       <c r="D391" t="n">
-        <v>22.72963274799409</v>
+        <v>22.72963097693332</v>
       </c>
       <c r="E391" t="n">
-        <v>23.00948944698904</v>
+        <v>23.00948765412223</v>
       </c>
       <c r="F391" t="n">
         <v>4038900</v>
@@ -8312,16 +8312,16 @@
         <v>44148</v>
       </c>
       <c r="B395" t="n">
-        <v>25.18712425231934</v>
+        <v>25.18712615966797</v>
       </c>
       <c r="C395" t="n">
-        <v>25.3445440499589</v>
+        <v>25.34454596922849</v>
       </c>
       <c r="D395" t="n">
-        <v>23.17565313778064</v>
+        <v>23.17565489280634</v>
       </c>
       <c r="E395" t="n">
-        <v>23.61292961207839</v>
+        <v>23.61293140021778</v>
       </c>
       <c r="F395" t="n">
         <v>2680000</v>
@@ -8372,16 +8372,16 @@
         <v>44153</v>
       </c>
       <c r="B398" t="n">
-        <v>25.53695106506348</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="C398" t="n">
-        <v>26.32404851768251</v>
+        <v>26.32404655154576</v>
       </c>
       <c r="D398" t="n">
-        <v>25.23085714791228</v>
+        <v>25.23085526342573</v>
       </c>
       <c r="E398" t="n">
-        <v>26.00920886940383</v>
+        <v>26.00920692678238</v>
       </c>
       <c r="F398" t="n">
         <v>2536100</v>
@@ -8392,16 +8392,16 @@
         <v>44154</v>
       </c>
       <c r="B399" t="n">
-        <v>25.34454727172852</v>
+        <v>25.34454536437988</v>
       </c>
       <c r="C399" t="n">
-        <v>25.62440398396176</v>
+        <v>25.62440205555201</v>
       </c>
       <c r="D399" t="n">
-        <v>24.98598065066998</v>
+        <v>24.98597877030591</v>
       </c>
       <c r="E399" t="n">
-        <v>25.37953019479646</v>
+        <v>25.37952828481513</v>
       </c>
       <c r="F399" t="n">
         <v>1026500</v>
@@ -8412,16 +8412,16 @@
         <v>44158</v>
       </c>
       <c r="B400" t="n">
-        <v>24.76734161376953</v>
+        <v>24.7673397064209</v>
       </c>
       <c r="C400" t="n">
-        <v>26.05293563912775</v>
+        <v>26.05293363277471</v>
       </c>
       <c r="D400" t="n">
-        <v>24.76734161376953</v>
+        <v>24.7673397064209</v>
       </c>
       <c r="E400" t="n">
-        <v>25.92175134978934</v>
+        <v>25.92174935353888</v>
       </c>
       <c r="F400" t="n">
         <v>941500</v>
@@ -8432,16 +8432,16 @@
         <v>44159</v>
       </c>
       <c r="B401" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C401" t="n">
-        <v>24.97723373838448</v>
+        <v>24.97723179219383</v>
       </c>
       <c r="D401" t="n">
-        <v>23.95400664013575</v>
+        <v>23.95400477367351</v>
       </c>
       <c r="E401" t="n">
-        <v>24.85479684959357</v>
+        <v>24.85479491294302</v>
       </c>
       <c r="F401" t="n">
         <v>2384200</v>
@@ -8472,16 +8472,16 @@
         <v>44161</v>
       </c>
       <c r="B403" t="n">
-        <v>24.85479736328125</v>
+        <v>24.85479545593262</v>
       </c>
       <c r="C403" t="n">
-        <v>25.09092708346753</v>
+        <v>25.09092515799838</v>
       </c>
       <c r="D403" t="n">
-        <v>24.4350123061129</v>
+        <v>24.43501043097842</v>
       </c>
       <c r="E403" t="n">
-        <v>24.85479736328125</v>
+        <v>24.85479545593262</v>
       </c>
       <c r="F403" t="n">
         <v>546200</v>
@@ -8492,16 +8492,16 @@
         <v>44162</v>
       </c>
       <c r="B404" t="n">
-        <v>24.18138694763184</v>
+        <v>24.1813907623291</v>
       </c>
       <c r="C404" t="n">
-        <v>25.274578054379</v>
+        <v>25.27458204153094</v>
       </c>
       <c r="D404" t="n">
-        <v>24.13765997059285</v>
+        <v>24.13766377839204</v>
       </c>
       <c r="E404" t="n">
-        <v>24.96848421087435</v>
+        <v>24.96848814973892</v>
       </c>
       <c r="F404" t="n">
         <v>1199600</v>
@@ -8512,16 +8512,16 @@
         <v>44165</v>
       </c>
       <c r="B405" t="n">
-        <v>23.22812652587891</v>
+        <v>23.22812843322754</v>
       </c>
       <c r="C405" t="n">
-        <v>24.65364880783709</v>
+        <v>24.65365083224071</v>
       </c>
       <c r="D405" t="n">
-        <v>23.053216931899</v>
+        <v>23.05321882488515</v>
       </c>
       <c r="E405" t="n">
-        <v>24.17264367121815</v>
+        <v>24.17264565612463</v>
       </c>
       <c r="F405" t="n">
         <v>1770500</v>
@@ -8532,16 +8532,16 @@
         <v>44166</v>
       </c>
       <c r="B406" t="n">
-        <v>24.96848678588867</v>
+        <v>24.9684886932373</v>
       </c>
       <c r="C406" t="n">
-        <v>25.08217960683885</v>
+        <v>25.0821815228725</v>
       </c>
       <c r="D406" t="n">
-        <v>23.42927501675685</v>
+        <v>23.42927680652473</v>
       </c>
       <c r="E406" t="n">
-        <v>23.74411295367693</v>
+        <v>23.74411476749535</v>
       </c>
       <c r="F406" t="n">
         <v>1601900</v>
@@ -8552,16 +8552,16 @@
         <v>44167</v>
       </c>
       <c r="B407" t="n">
-        <v>24.59243202209473</v>
+        <v>24.59243011474609</v>
       </c>
       <c r="C407" t="n">
-        <v>25.63314893035655</v>
+        <v>25.63314694229162</v>
       </c>
       <c r="D407" t="n">
-        <v>24.22511968150893</v>
+        <v>24.22511780264844</v>
       </c>
       <c r="E407" t="n">
-        <v>25.03845260101977</v>
+        <v>25.03845065907852</v>
       </c>
       <c r="F407" t="n">
         <v>1534600</v>
@@ -8572,16 +8572,16 @@
         <v>44168</v>
       </c>
       <c r="B408" t="n">
-        <v>24.09393501281738</v>
+        <v>24.09393310546875</v>
       </c>
       <c r="C408" t="n">
-        <v>25.08218085868143</v>
+        <v>25.08217887310027</v>
       </c>
       <c r="D408" t="n">
-        <v>23.73536840837539</v>
+        <v>23.73536652941197</v>
       </c>
       <c r="E408" t="n">
-        <v>24.59243163496901</v>
+        <v>24.59242968815787</v>
       </c>
       <c r="F408" t="n">
         <v>3140600</v>
@@ -8592,16 +8592,16 @@
         <v>44169</v>
       </c>
       <c r="B409" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C409" t="n">
-        <v>24.6274121739206</v>
+        <v>24.62741018388957</v>
       </c>
       <c r="D409" t="n">
-        <v>23.36805539568675</v>
+        <v>23.3680535074187</v>
       </c>
       <c r="E409" t="n">
-        <v>24.22511859741778</v>
+        <v>24.22511663989429</v>
       </c>
       <c r="F409" t="n">
         <v>2314400</v>
@@ -8632,16 +8632,16 @@
         <v>44173</v>
       </c>
       <c r="B411" t="n">
-        <v>23.61293029785156</v>
+        <v>23.6129322052002</v>
       </c>
       <c r="C411" t="n">
-        <v>23.90153271254665</v>
+        <v>23.90153464320732</v>
       </c>
       <c r="D411" t="n">
-        <v>23.19314527067278</v>
+        <v>23.19314714411303</v>
       </c>
       <c r="E411" t="n">
-        <v>23.29809069342877</v>
+        <v>23.29809257534604</v>
       </c>
       <c r="F411" t="n">
         <v>1524000</v>
@@ -8672,16 +8672,16 @@
         <v>44175</v>
       </c>
       <c r="B413" t="n">
-        <v>24.63615798950195</v>
+        <v>24.63615608215332</v>
       </c>
       <c r="C413" t="n">
-        <v>24.83730477845123</v>
+        <v>24.83730285552967</v>
       </c>
       <c r="D413" t="n">
-        <v>23.39429266717552</v>
+        <v>23.39429085597297</v>
       </c>
       <c r="E413" t="n">
-        <v>24.18139003077341</v>
+        <v>24.18138815863323</v>
       </c>
       <c r="F413" t="n">
         <v>1331100</v>
@@ -8732,16 +8732,16 @@
         <v>44180</v>
       </c>
       <c r="B416" t="n">
-        <v>25.30956268310547</v>
+        <v>25.3095645904541</v>
       </c>
       <c r="C416" t="n">
-        <v>26.01795010115077</v>
+        <v>26.01795206188404</v>
       </c>
       <c r="D416" t="n">
-        <v>24.58368380583007</v>
+        <v>24.5836856584759</v>
       </c>
       <c r="E416" t="n">
-        <v>24.95099610927529</v>
+        <v>24.95099798960207</v>
       </c>
       <c r="F416" t="n">
         <v>1779500</v>
@@ -8752,16 +8752,16 @@
         <v>44181</v>
       </c>
       <c r="B417" t="n">
-        <v>26.31529998779297</v>
+        <v>26.31529808044434</v>
       </c>
       <c r="C417" t="n">
-        <v>26.60390241199491</v>
+        <v>26.6039004837282</v>
       </c>
       <c r="D417" t="n">
-        <v>24.7673407724928</v>
+        <v>24.76733897734118</v>
       </c>
       <c r="E417" t="n">
-        <v>25.39702000208065</v>
+        <v>25.3970181612895</v>
       </c>
       <c r="F417" t="n">
         <v>2062300</v>
@@ -8772,16 +8772,16 @@
         <v>44182</v>
       </c>
       <c r="B418" t="n">
-        <v>26.07917022705078</v>
+        <v>26.07917213439941</v>
       </c>
       <c r="C418" t="n">
-        <v>26.48146547497467</v>
+        <v>26.48146741174591</v>
       </c>
       <c r="D418" t="n">
-        <v>25.85178624658554</v>
+        <v>25.85178813730402</v>
       </c>
       <c r="E418" t="n">
-        <v>26.31529993769671</v>
+        <v>26.31530186231512</v>
       </c>
       <c r="F418" t="n">
         <v>1046800</v>
@@ -8792,16 +8792,16 @@
         <v>44183</v>
       </c>
       <c r="B419" t="n">
-        <v>26.1928653717041</v>
+        <v>26.19286346435547</v>
       </c>
       <c r="C419" t="n">
-        <v>26.91874436023017</v>
+        <v>26.91874240002346</v>
       </c>
       <c r="D419" t="n">
-        <v>25.99171689588401</v>
+        <v>25.99171500318289</v>
       </c>
       <c r="E419" t="n">
-        <v>26.04419128161671</v>
+        <v>26.04418938509443</v>
       </c>
       <c r="F419" t="n">
         <v>1257300</v>
@@ -8812,16 +8812,16 @@
         <v>44186</v>
       </c>
       <c r="B420" t="n">
-        <v>25.27458190917969</v>
+        <v>25.27458000183105</v>
       </c>
       <c r="C420" t="n">
-        <v>25.79056832370717</v>
+        <v>25.79056637741958</v>
       </c>
       <c r="D420" t="n">
-        <v>24.79357841608068</v>
+        <v>24.79357654503102</v>
       </c>
       <c r="E420" t="n">
-        <v>25.36203754467337</v>
+        <v>25.36203563072489</v>
       </c>
       <c r="F420" t="n">
         <v>1168100</v>
@@ -8872,16 +8872,16 @@
         <v>44193</v>
       </c>
       <c r="B423" t="n">
-        <v>25.27458190917969</v>
+        <v>25.27458000183105</v>
       </c>
       <c r="C423" t="n">
-        <v>25.49322016387515</v>
+        <v>25.49321824002696</v>
       </c>
       <c r="D423" t="n">
-        <v>24.67113985915852</v>
+        <v>24.67113799734869</v>
       </c>
       <c r="E423" t="n">
-        <v>25.16963648104927</v>
+        <v>25.16963458162035</v>
       </c>
       <c r="F423" t="n">
         <v>745000</v>
@@ -8892,16 +8892,16 @@
         <v>44194</v>
       </c>
       <c r="B424" t="n">
-        <v>25.5019645690918</v>
+        <v>25.50196647644043</v>
       </c>
       <c r="C424" t="n">
-        <v>25.72934854232898</v>
+        <v>25.72935046668417</v>
       </c>
       <c r="D424" t="n">
-        <v>24.99472391127881</v>
+        <v>24.99472578068979</v>
       </c>
       <c r="E424" t="n">
-        <v>25.44949185775319</v>
+        <v>25.44949376117727</v>
       </c>
       <c r="F424" t="n">
         <v>637100</v>
@@ -8952,16 +8952,16 @@
         <v>44201</v>
       </c>
       <c r="B427" t="n">
-        <v>23.95400428771973</v>
+        <v>23.95400619506836</v>
       </c>
       <c r="C427" t="n">
-        <v>24.95974149457043</v>
+        <v>24.95974348200135</v>
       </c>
       <c r="D427" t="n">
-        <v>23.90153157883066</v>
+        <v>23.90153348200113</v>
       </c>
       <c r="E427" t="n">
-        <v>24.88977565861522</v>
+        <v>24.88977764047509</v>
       </c>
       <c r="F427" t="n">
         <v>1214100</v>
@@ -8992,16 +8992,16 @@
         <v>44203</v>
       </c>
       <c r="B429" t="n">
-        <v>21.47027587890625</v>
+        <v>21.47027397155762</v>
       </c>
       <c r="C429" t="n">
-        <v>22.93077948257636</v>
+        <v>22.9307774454814</v>
       </c>
       <c r="D429" t="n">
-        <v>21.45278608632243</v>
+        <v>21.45278418052753</v>
       </c>
       <c r="E429" t="n">
-        <v>22.7296326892037</v>
+        <v>22.72963066997795</v>
       </c>
       <c r="F429" t="n">
         <v>2745600</v>
@@ -9012,16 +9012,16 @@
         <v>44204</v>
       </c>
       <c r="B430" t="n">
-        <v>23.1756534576416</v>
+        <v>23.17565536499023</v>
       </c>
       <c r="C430" t="n">
-        <v>23.75285827823479</v>
+        <v>23.75286023308718</v>
       </c>
       <c r="D430" t="n">
-        <v>21.54898441701859</v>
+        <v>21.5489861904929</v>
       </c>
       <c r="E430" t="n">
-        <v>21.68016869558037</v>
+        <v>21.6801704798511</v>
       </c>
       <c r="F430" t="n">
         <v>2774700</v>
@@ -9032,16 +9032,16 @@
         <v>44207</v>
       </c>
       <c r="B431" t="n">
-        <v>22.82583045959473</v>
+        <v>22.82583427429199</v>
       </c>
       <c r="C431" t="n">
-        <v>23.38554376797962</v>
+        <v>23.38554767621726</v>
       </c>
       <c r="D431" t="n">
-        <v>22.58095505313772</v>
+        <v>22.58095882691093</v>
       </c>
       <c r="E431" t="n">
-        <v>22.81708473064156</v>
+        <v>22.81708854387722</v>
       </c>
       <c r="F431" t="n">
         <v>1353300</v>
@@ -9052,16 +9052,16 @@
         <v>44208</v>
       </c>
       <c r="B432" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C432" t="n">
-        <v>23.26310866176136</v>
+        <v>23.26311060044971</v>
       </c>
       <c r="D432" t="n">
-        <v>22.52848405479477</v>
+        <v>22.52848593226138</v>
       </c>
       <c r="E432" t="n">
-        <v>22.93077760866452</v>
+        <v>22.93077951965725</v>
       </c>
       <c r="F432" t="n">
         <v>1882900</v>
@@ -9092,16 +9092,16 @@
         <v>44210</v>
       </c>
       <c r="B434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="D434" t="n">
-        <v>22.58095740790637</v>
+        <v>22.58095923867744</v>
       </c>
       <c r="E434" t="n">
-        <v>22.92203253226147</v>
+        <v>22.92203439068551</v>
       </c>
       <c r="F434" t="n">
         <v>1124400</v>
@@ -9212,16 +9212,16 @@
         <v>44218</v>
       </c>
       <c r="B440" t="n">
-        <v>21.47027587890625</v>
+        <v>21.47027397155762</v>
       </c>
       <c r="C440" t="n">
-        <v>21.82009841982262</v>
+        <v>21.82009648139691</v>
       </c>
       <c r="D440" t="n">
-        <v>21.25163762487227</v>
+        <v>21.25163573694674</v>
       </c>
       <c r="E440" t="n">
-        <v>21.82009841982262</v>
+        <v>21.82009648139691</v>
       </c>
       <c r="F440" t="n">
         <v>1350400</v>
@@ -9232,16 +9232,16 @@
         <v>44222</v>
       </c>
       <c r="B441" t="n">
-        <v>21.93378829956055</v>
+        <v>21.93379020690918</v>
       </c>
       <c r="C441" t="n">
-        <v>22.30110061165203</v>
+        <v>22.30110255094191</v>
       </c>
       <c r="D441" t="n">
-        <v>21.3128564949721</v>
+        <v>21.31285834832488</v>
       </c>
       <c r="E441" t="n">
-        <v>21.5314947362628</v>
+        <v>21.53149660862823</v>
       </c>
       <c r="F441" t="n">
         <v>1600800</v>
@@ -9252,16 +9252,16 @@
         <v>44223</v>
       </c>
       <c r="B442" t="n">
-        <v>21.48776435852051</v>
+        <v>21.48776626586914</v>
       </c>
       <c r="C442" t="n">
-        <v>22.17866194609529</v>
+        <v>22.17866391477103</v>
       </c>
       <c r="D442" t="n">
-        <v>21.33909029968019</v>
+        <v>21.33909219383186</v>
       </c>
       <c r="E442" t="n">
-        <v>21.9425322641588</v>
+        <v>21.94253421187463</v>
       </c>
       <c r="F442" t="n">
         <v>1472500</v>
@@ -9312,16 +9312,16 @@
         <v>44228</v>
       </c>
       <c r="B445" t="n">
-        <v>21.85507965087891</v>
+        <v>21.85507774353027</v>
       </c>
       <c r="C445" t="n">
-        <v>22.68590568259553</v>
+        <v>22.68590370273859</v>
       </c>
       <c r="D445" t="n">
-        <v>21.34783896875815</v>
+        <v>21.34783710567771</v>
       </c>
       <c r="E445" t="n">
-        <v>22.65092276130841</v>
+        <v>22.65092078450452</v>
       </c>
       <c r="F445" t="n">
         <v>3093300</v>
@@ -9412,16 +9412,16 @@
         <v>44235</v>
       </c>
       <c r="B450" t="n">
-        <v>21.5839672088623</v>
+        <v>21.58396911621094</v>
       </c>
       <c r="C450" t="n">
-        <v>21.83758669855977</v>
+        <v>21.83758862832044</v>
       </c>
       <c r="D450" t="n">
-        <v>21.46153032887576</v>
+        <v>21.4615322254048</v>
       </c>
       <c r="E450" t="n">
-        <v>21.78511398829088</v>
+        <v>21.7851159134146</v>
       </c>
       <c r="F450" t="n">
         <v>1066300</v>
@@ -9472,16 +9472,16 @@
         <v>44238</v>
       </c>
       <c r="B453" t="n">
-        <v>20.2109203338623</v>
+        <v>20.21092224121094</v>
       </c>
       <c r="C453" t="n">
-        <v>20.58697839019794</v>
+        <v>20.58698033303599</v>
       </c>
       <c r="D453" t="n">
-        <v>20.12346470037629</v>
+        <v>20.12346659947154</v>
       </c>
       <c r="E453" t="n">
-        <v>20.33335721989625</v>
+        <v>20.33335913879952</v>
       </c>
       <c r="F453" t="n">
         <v>1364100</v>
@@ -9552,16 +9552,16 @@
         <v>44246</v>
       </c>
       <c r="B457" t="n">
-        <v>21.19916343688965</v>
+        <v>21.19916534423828</v>
       </c>
       <c r="C457" t="n">
-        <v>21.21665489633471</v>
+        <v>21.21665680525709</v>
       </c>
       <c r="D457" t="n">
-        <v>19.99228109249628</v>
+        <v>19.9922828912583</v>
       </c>
       <c r="E457" t="n">
-        <v>20.34210194101049</v>
+        <v>20.34210377124688</v>
       </c>
       <c r="F457" t="n">
         <v>1586300</v>
@@ -9652,16 +9652,16 @@
         <v>44253</v>
       </c>
       <c r="B462" t="n">
-        <v>19.55500411987305</v>
+        <v>19.55500602722168</v>
       </c>
       <c r="C462" t="n">
-        <v>20.5170110119182</v>
+        <v>20.5170130130987</v>
       </c>
       <c r="D462" t="n">
-        <v>19.12647338278011</v>
+        <v>19.12647524833087</v>
       </c>
       <c r="E462" t="n">
-        <v>20.40331986455776</v>
+        <v>20.4033218546491</v>
       </c>
       <c r="F462" t="n">
         <v>2042700</v>
@@ -9672,16 +9672,16 @@
         <v>44256</v>
       </c>
       <c r="B463" t="n">
-        <v>19.55500411987305</v>
+        <v>19.55500602722168</v>
       </c>
       <c r="C463" t="n">
-        <v>20.23715434019035</v>
+        <v>20.23715631407429</v>
       </c>
       <c r="D463" t="n">
-        <v>19.32762015707483</v>
+        <v>19.32762204224498</v>
       </c>
       <c r="E463" t="n">
-        <v>19.56374984937421</v>
+        <v>19.56375175757588</v>
       </c>
       <c r="F463" t="n">
         <v>1263600</v>
@@ -9692,16 +9692,16 @@
         <v>44257</v>
       </c>
       <c r="B464" t="n">
-        <v>19.46755027770996</v>
+        <v>19.46754837036133</v>
       </c>
       <c r="C464" t="n">
-        <v>19.72116978418598</v>
+        <v>19.72116785198877</v>
       </c>
       <c r="D464" t="n">
-        <v>18.49679589908823</v>
+        <v>18.49679408685002</v>
       </c>
       <c r="E464" t="n">
-        <v>19.3800946427578</v>
+        <v>19.3800927439777</v>
       </c>
       <c r="F464" t="n">
         <v>1214000</v>
@@ -9752,16 +9752,16 @@
         <v>44260</v>
       </c>
       <c r="B467" t="n">
-        <v>20.89306831359863</v>
+        <v>20.89307022094727</v>
       </c>
       <c r="C467" t="n">
-        <v>20.90181404279569</v>
+        <v>20.90181595094273</v>
       </c>
       <c r="D467" t="n">
-        <v>19.31887375582787</v>
+        <v>19.31887551946674</v>
       </c>
       <c r="E467" t="n">
-        <v>19.49378500361453</v>
+        <v>19.49378678322121</v>
       </c>
       <c r="F467" t="n">
         <v>2934300</v>
@@ -9772,16 +9772,16 @@
         <v>44263</v>
       </c>
       <c r="B468" t="n">
-        <v>19.74740600585938</v>
+        <v>19.74740791320801</v>
       </c>
       <c r="C468" t="n">
-        <v>20.87558013840683</v>
+        <v>20.87558215472276</v>
       </c>
       <c r="D468" t="n">
-        <v>19.62496912378225</v>
+        <v>19.62497101930504</v>
       </c>
       <c r="E468" t="n">
-        <v>20.62195897630147</v>
+        <v>20.62196096812081</v>
       </c>
       <c r="F468" t="n">
         <v>1138000</v>
@@ -9852,16 +9852,16 @@
         <v>44267</v>
       </c>
       <c r="B472" t="n">
-        <v>20.65694427490234</v>
+        <v>20.65694236755371</v>
       </c>
       <c r="C472" t="n">
-        <v>21.3740775263663</v>
+        <v>21.37407555280153</v>
       </c>
       <c r="D472" t="n">
-        <v>19.82611819006331</v>
+        <v>19.82611635942859</v>
       </c>
       <c r="E472" t="n">
-        <v>20.24590326388451</v>
+        <v>20.24590139448915</v>
       </c>
       <c r="F472" t="n">
         <v>2643100</v>
@@ -9872,16 +9872,16 @@
         <v>44270</v>
       </c>
       <c r="B473" t="n">
-        <v>20.98052597045898</v>
+        <v>20.98052787780762</v>
       </c>
       <c r="C473" t="n">
-        <v>21.27787411966231</v>
+        <v>21.27787605404299</v>
       </c>
       <c r="D473" t="n">
-        <v>20.31586549977375</v>
+        <v>20.31586734669781</v>
       </c>
       <c r="E473" t="n">
-        <v>20.46453957437541</v>
+        <v>20.4645414348155</v>
       </c>
       <c r="F473" t="n">
         <v>840900</v>
@@ -9932,16 +9932,16 @@
         <v>44273</v>
       </c>
       <c r="B476" t="n">
-        <v>20.42955589294434</v>
+        <v>20.4295597076416</v>
       </c>
       <c r="C476" t="n">
-        <v>21.25163440244285</v>
+        <v>21.25163837064226</v>
       </c>
       <c r="D476" t="n">
-        <v>20.19342621405386</v>
+        <v>20.19342998465995</v>
       </c>
       <c r="E476" t="n">
-        <v>21.25163440244285</v>
+        <v>21.25163837064226</v>
       </c>
       <c r="F476" t="n">
         <v>770600</v>
@@ -9952,16 +9952,16 @@
         <v>44274</v>
       </c>
       <c r="B477" t="n">
-        <v>21.64518737792969</v>
+        <v>21.64518547058105</v>
       </c>
       <c r="C477" t="n">
-        <v>21.64518737792969</v>
+        <v>21.64518547058105</v>
       </c>
       <c r="D477" t="n">
-        <v>20.34210357029636</v>
+        <v>20.34210177777394</v>
       </c>
       <c r="E477" t="n">
-        <v>20.55199609621607</v>
+        <v>20.55199428519817</v>
       </c>
       <c r="F477" t="n">
         <v>1152500</v>
@@ -9992,16 +9992,16 @@
         <v>44278</v>
       </c>
       <c r="B479" t="n">
-        <v>23.40303802490234</v>
+        <v>23.40303611755371</v>
       </c>
       <c r="C479" t="n">
-        <v>23.60418481065078</v>
+        <v>23.60418288690867</v>
       </c>
       <c r="D479" t="n">
-        <v>21.72389623084414</v>
+        <v>21.72389446034564</v>
       </c>
       <c r="E479" t="n">
-        <v>22.18740991233514</v>
+        <v>22.18740810406026</v>
       </c>
       <c r="F479" t="n">
         <v>2996700</v>
@@ -10012,16 +10012,16 @@
         <v>44279</v>
       </c>
       <c r="B480" t="n">
-        <v>23.39429473876953</v>
+        <v>23.3942928314209</v>
       </c>
       <c r="C480" t="n">
-        <v>23.98899109621759</v>
+        <v>23.98898914038306</v>
       </c>
       <c r="D480" t="n">
-        <v>23.01823664990811</v>
+        <v>23.01823477321968</v>
       </c>
       <c r="E480" t="n">
-        <v>23.60418727644338</v>
+        <v>23.60418535198211</v>
       </c>
       <c r="F480" t="n">
         <v>3020300</v>
@@ -10052,16 +10052,16 @@
         <v>44281</v>
       </c>
       <c r="B482" t="n">
-        <v>23.34182167053223</v>
+        <v>23.34181976318359</v>
       </c>
       <c r="C482" t="n">
-        <v>24.35630308807987</v>
+        <v>24.35630109783412</v>
       </c>
       <c r="D482" t="n">
-        <v>22.87830794758745</v>
+        <v>22.87830607811428</v>
       </c>
       <c r="E482" t="n">
-        <v>24.05020918304379</v>
+        <v>24.05020721781013</v>
       </c>
       <c r="F482" t="n">
         <v>1658200</v>
@@ -10092,16 +10092,16 @@
         <v>44285</v>
       </c>
       <c r="B484" t="n">
-        <v>24.55744743347168</v>
+        <v>24.55744934082031</v>
       </c>
       <c r="C484" t="n">
-        <v>25.00346965020434</v>
+        <v>25.003471592195</v>
       </c>
       <c r="D484" t="n">
-        <v>23.29809068434873</v>
+        <v>23.29809249388458</v>
       </c>
       <c r="E484" t="n">
-        <v>23.40303777514124</v>
+        <v>23.4030395928282</v>
       </c>
       <c r="F484" t="n">
         <v>2083600</v>
@@ -10132,16 +10132,16 @@
         <v>44287</v>
       </c>
       <c r="B486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="C486" t="n">
-        <v>23.52547508492306</v>
+        <v>23.52547317686509</v>
       </c>
       <c r="D486" t="n">
-        <v>22.2223913306826</v>
+        <v>22.22238952831259</v>
       </c>
       <c r="E486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="F486" t="n">
         <v>1244600</v>
@@ -10172,16 +10172,16 @@
         <v>44292</v>
       </c>
       <c r="B488" t="n">
-        <v>24.31257057189941</v>
+        <v>24.31257247924805</v>
       </c>
       <c r="C488" t="n">
-        <v>24.79357567999479</v>
+        <v>24.79357762507881</v>
       </c>
       <c r="D488" t="n">
-        <v>23.77034869421477</v>
+        <v>23.77035055902548</v>
       </c>
       <c r="E488" t="n">
-        <v>24.19887942595822</v>
+        <v>24.19888132438765</v>
       </c>
       <c r="F488" t="n">
         <v>874200</v>
@@ -10192,16 +10192,16 @@
         <v>44293</v>
       </c>
       <c r="B489" t="n">
-        <v>24.09393501281738</v>
+        <v>24.09393310546875</v>
       </c>
       <c r="C489" t="n">
-        <v>24.82855968242477</v>
+        <v>24.82855771692103</v>
       </c>
       <c r="D489" t="n">
-        <v>23.84031550463823</v>
+        <v>23.84031361736688</v>
       </c>
       <c r="E489" t="n">
-        <v>24.55744871352222</v>
+        <v>24.55744676948045</v>
       </c>
       <c r="F489" t="n">
         <v>331100</v>
@@ -10252,16 +10252,16 @@
         <v>44298</v>
       </c>
       <c r="B492" t="n">
-        <v>24.04146194458008</v>
+        <v>24.04146003723145</v>
       </c>
       <c r="C492" t="n">
-        <v>24.04146194458008</v>
+        <v>24.04146003723145</v>
       </c>
       <c r="D492" t="n">
-        <v>23.46425709383076</v>
+        <v>23.46425523227514</v>
       </c>
       <c r="E492" t="n">
-        <v>23.66540388495424</v>
+        <v>23.66540200744048</v>
       </c>
       <c r="F492" t="n">
         <v>607300</v>
@@ -10272,16 +10272,16 @@
         <v>44299</v>
       </c>
       <c r="B493" t="n">
-        <v>23.84905815124512</v>
+        <v>23.84906005859375</v>
       </c>
       <c r="C493" t="n">
-        <v>24.19013325086169</v>
+        <v>24.19013518548809</v>
       </c>
       <c r="D493" t="n">
-        <v>23.7003840904753</v>
+        <v>23.7003859859336</v>
       </c>
       <c r="E493" t="n">
-        <v>23.75285679778309</v>
+        <v>23.75285869743794</v>
       </c>
       <c r="F493" t="n">
         <v>376700</v>
@@ -10292,16 +10292,16 @@
         <v>44300</v>
       </c>
       <c r="B494" t="n">
-        <v>23.86655235290527</v>
+        <v>23.86655044555664</v>
       </c>
       <c r="C494" t="n">
-        <v>24.40002855268584</v>
+        <v>24.40002660270327</v>
       </c>
       <c r="D494" t="n">
-        <v>23.61293118029162</v>
+        <v>23.61292929321169</v>
       </c>
       <c r="E494" t="n">
-        <v>23.91902506624423</v>
+        <v>23.91902315470212</v>
       </c>
       <c r="F494" t="n">
         <v>555300</v>
@@ -10312,16 +10312,16 @@
         <v>44301</v>
       </c>
       <c r="B495" t="n">
-        <v>24.05020713806152</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C495" t="n">
-        <v>24.40002799918148</v>
+        <v>24.40002993427333</v>
       </c>
       <c r="D495" t="n">
-        <v>23.70038627694157</v>
+        <v>23.70038815654698</v>
       </c>
       <c r="E495" t="n">
-        <v>23.70038627694157</v>
+        <v>23.70038815654698</v>
       </c>
       <c r="F495" t="n">
         <v>383100</v>
@@ -10372,16 +10372,16 @@
         <v>44306</v>
       </c>
       <c r="B498" t="n">
-        <v>24.05895233154297</v>
+        <v>24.05895042419434</v>
       </c>
       <c r="C498" t="n">
-        <v>24.90726810934962</v>
+        <v>24.90726613474811</v>
       </c>
       <c r="D498" t="n">
-        <v>23.83156835986669</v>
+        <v>23.83156647054464</v>
       </c>
       <c r="E498" t="n">
-        <v>24.90726810934962</v>
+        <v>24.90726613474811</v>
       </c>
       <c r="F498" t="n">
         <v>947500</v>
@@ -10392,16 +10392,16 @@
         <v>44308</v>
       </c>
       <c r="B499" t="n">
-        <v>23.4730052947998</v>
+        <v>23.47300338745117</v>
       </c>
       <c r="C499" t="n">
-        <v>24.61866938665658</v>
+        <v>24.6186673862146</v>
       </c>
       <c r="D499" t="n">
-        <v>23.34182266365367</v>
+        <v>23.34182076696456</v>
       </c>
       <c r="E499" t="n">
-        <v>24.05895593745834</v>
+        <v>24.05895398249705</v>
       </c>
       <c r="F499" t="n">
         <v>479300</v>
@@ -10532,16 +10532,16 @@
         <v>44319</v>
       </c>
       <c r="B506" t="n">
-        <v>23.08819961547852</v>
+        <v>23.08819770812988</v>
       </c>
       <c r="C506" t="n">
-        <v>23.75286011721265</v>
+        <v>23.75285815495547</v>
       </c>
       <c r="D506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="E506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="F506" t="n">
         <v>492900</v>
@@ -10552,16 +10552,16 @@
         <v>44320</v>
       </c>
       <c r="B507" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="C507" t="n">
-        <v>23.90153313731625</v>
+        <v>23.90153119875771</v>
       </c>
       <c r="D507" t="n">
-        <v>22.790850440266</v>
+        <v>22.79084859179052</v>
       </c>
       <c r="E507" t="n">
-        <v>23.08819859015469</v>
+        <v>23.08819671756248</v>
       </c>
       <c r="F507" t="n">
         <v>826900</v>
@@ -10592,16 +10592,16 @@
         <v>44322</v>
       </c>
       <c r="B509" t="n">
-        <v>24.26009941101074</v>
+        <v>24.26010131835938</v>
       </c>
       <c r="C509" t="n">
-        <v>24.67113871018761</v>
+        <v>24.67114064985248</v>
       </c>
       <c r="D509" t="n">
-        <v>23.92777001330481</v>
+        <v>23.92777189452544</v>
       </c>
       <c r="E509" t="n">
-        <v>24.13766252786815</v>
+        <v>24.1376644255907</v>
       </c>
       <c r="F509" t="n">
         <v>839200</v>
@@ -10652,16 +10652,16 @@
         <v>44327</v>
       </c>
       <c r="B512" t="n">
-        <v>25.53695106506348</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="C512" t="n">
-        <v>25.53695106506348</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="D512" t="n">
-        <v>24.46999522059804</v>
+        <v>24.46999339294008</v>
       </c>
       <c r="E512" t="n">
-        <v>24.93350896188857</v>
+        <v>24.93350709961088</v>
       </c>
       <c r="F512" t="n">
         <v>476700</v>
@@ -10732,16 +10732,16 @@
         <v>44333</v>
       </c>
       <c r="B516" t="n">
-        <v>24.81107139587402</v>
+        <v>24.81106948852539</v>
       </c>
       <c r="C516" t="n">
-        <v>25.01221820217063</v>
+        <v>25.01221627935886</v>
       </c>
       <c r="D516" t="n">
-        <v>23.4817503255982</v>
+        <v>23.48174852044099</v>
       </c>
       <c r="E516" t="n">
-        <v>23.83157122091352</v>
+        <v>23.83156938886387</v>
       </c>
       <c r="F516" t="n">
         <v>854000</v>
@@ -10872,16 +10872,16 @@
         <v>44342</v>
       </c>
       <c r="B523" t="n">
-        <v>27.02368927001953</v>
+        <v>27.0236873626709</v>
       </c>
       <c r="C523" t="n">
-        <v>27.11114490979568</v>
+        <v>27.11114299627437</v>
       </c>
       <c r="D523" t="n">
-        <v>26.13164474684247</v>
+        <v>26.13164290245489</v>
       </c>
       <c r="E523" t="n">
-        <v>26.2978102956094</v>
+        <v>26.29780843949375</v>
       </c>
       <c r="F523" t="n">
         <v>688100</v>
@@ -10932,16 +10932,16 @@
         <v>44347</v>
       </c>
       <c r="B526" t="n">
-        <v>29.21881675720215</v>
+        <v>29.21881294250488</v>
       </c>
       <c r="C526" t="n">
-        <v>29.35000104687511</v>
+        <v>29.34999721505092</v>
       </c>
       <c r="D526" t="n">
-        <v>28.42297362903536</v>
+        <v>28.42296991824034</v>
       </c>
       <c r="E526" t="n">
-        <v>28.59788490321429</v>
+        <v>28.59788116958352</v>
       </c>
       <c r="F526" t="n">
         <v>1368000</v>
@@ -10952,16 +10952,16 @@
         <v>44348</v>
       </c>
       <c r="B527" t="n">
-        <v>30.37322616577148</v>
+        <v>30.37322425842285</v>
       </c>
       <c r="C527" t="n">
-        <v>31.21279626931154</v>
+        <v>31.21279430924039</v>
       </c>
       <c r="D527" t="n">
-        <v>29.13136247130453</v>
+        <v>29.13136064194126</v>
       </c>
       <c r="E527" t="n">
-        <v>29.29752634508171</v>
+        <v>29.29752450528385</v>
       </c>
       <c r="F527" t="n">
         <v>3409000</v>
@@ -10972,16 +10972,16 @@
         <v>44349</v>
       </c>
       <c r="B528" t="n">
-        <v>30.69680786132812</v>
+        <v>30.69680976867676</v>
       </c>
       <c r="C528" t="n">
-        <v>31.42268842657149</v>
+        <v>31.42269037902277</v>
       </c>
       <c r="D528" t="n">
-        <v>29.90971219133409</v>
+        <v>29.90971404977647</v>
       </c>
       <c r="E528" t="n">
-        <v>30.3732241970913</v>
+        <v>30.37322608433403</v>
       </c>
       <c r="F528" t="n">
         <v>1420200</v>
@@ -10992,16 +10992,16 @@
         <v>44351</v>
       </c>
       <c r="B529" t="n">
-        <v>30.52190017700195</v>
+        <v>30.52189826965332</v>
       </c>
       <c r="C529" t="n">
-        <v>30.85422790563423</v>
+        <v>30.85422597751805</v>
       </c>
       <c r="D529" t="n">
-        <v>30.18082171421382</v>
+        <v>30.18081982817957</v>
       </c>
       <c r="E529" t="n">
-        <v>30.60935414008311</v>
+        <v>30.60935222726938</v>
       </c>
       <c r="F529" t="n">
         <v>1113000</v>
@@ -11012,16 +11012,16 @@
         <v>44354</v>
       </c>
       <c r="B530" t="n">
-        <v>30.60061073303223</v>
+        <v>30.60060882568359</v>
       </c>
       <c r="C530" t="n">
-        <v>31.96491126875886</v>
+        <v>31.96490927637281</v>
       </c>
       <c r="D530" t="n">
-        <v>30.03214995237619</v>
+        <v>30.03214808045995</v>
       </c>
       <c r="E530" t="n">
-        <v>30.521900830113</v>
+        <v>30.52189892767039</v>
       </c>
       <c r="F530" t="n">
         <v>1187500</v>
@@ -11032,16 +11032,16 @@
         <v>44355</v>
       </c>
       <c r="B531" t="n">
-        <v>31.42269134521484</v>
+        <v>31.42268753051758</v>
       </c>
       <c r="C531" t="n">
-        <v>31.60634668498982</v>
+        <v>31.6063428479969</v>
       </c>
       <c r="D531" t="n">
-        <v>30.30326450907581</v>
+        <v>30.30326083027634</v>
       </c>
       <c r="E531" t="n">
-        <v>30.30326450907581</v>
+        <v>30.30326083027634</v>
       </c>
       <c r="F531" t="n">
         <v>1062900</v>
@@ -11052,16 +11052,16 @@
         <v>44356</v>
       </c>
       <c r="B532" t="n">
-        <v>31.91244125366211</v>
+        <v>31.91243553161621</v>
       </c>
       <c r="C532" t="n">
-        <v>32.10484064999491</v>
+        <v>32.10483489345093</v>
       </c>
       <c r="D532" t="n">
-        <v>30.91544800580656</v>
+        <v>30.91544246252609</v>
       </c>
       <c r="E532" t="n">
-        <v>31.42269036012719</v>
+        <v>31.42268472589586</v>
       </c>
       <c r="F532" t="n">
         <v>930900</v>
@@ -11072,16 +11072,16 @@
         <v>44357</v>
       </c>
       <c r="B533" t="n">
-        <v>31.92118453979492</v>
+        <v>31.92118644714355</v>
       </c>
       <c r="C533" t="n">
-        <v>32.32347811961926</v>
+        <v>32.32348005100567</v>
       </c>
       <c r="D533" t="n">
-        <v>30.81050182807168</v>
+        <v>30.81050366905501</v>
       </c>
       <c r="E533" t="n">
-        <v>31.65881930669883</v>
+        <v>31.65882119837066</v>
       </c>
       <c r="F533" t="n">
         <v>1334900</v>
@@ -11092,16 +11092,16 @@
         <v>44358</v>
       </c>
       <c r="B534" t="n">
-        <v>33.14555740356445</v>
+        <v>33.14556121826172</v>
       </c>
       <c r="C534" t="n">
-        <v>33.95889189589919</v>
+        <v>33.95889580420251</v>
       </c>
       <c r="D534" t="n">
-        <v>31.65881675434211</v>
+        <v>31.65882039793151</v>
       </c>
       <c r="E534" t="n">
-        <v>31.79874508978923</v>
+        <v>31.79874874948288</v>
       </c>
       <c r="F534" t="n">
         <v>1304000</v>
@@ -11132,16 +11132,16 @@
         <v>44362</v>
       </c>
       <c r="B536" t="n">
-        <v>34.06383514404297</v>
+        <v>34.0638427734375</v>
       </c>
       <c r="C536" t="n">
-        <v>34.49236418449064</v>
+        <v>34.4923719098643</v>
       </c>
       <c r="D536" t="n">
-        <v>33.05809800346221</v>
+        <v>33.05810540759833</v>
       </c>
       <c r="E536" t="n">
-        <v>33.49537444090524</v>
+        <v>33.49538194297968</v>
       </c>
       <c r="F536" t="n">
         <v>1322200</v>
@@ -11152,16 +11152,16 @@
         <v>44363</v>
       </c>
       <c r="B537" t="n">
-        <v>33.69652557373047</v>
+        <v>33.6965217590332</v>
       </c>
       <c r="C537" t="n">
-        <v>34.36993177510205</v>
+        <v>34.36992788417019</v>
       </c>
       <c r="D537" t="n">
-        <v>33.101829274757</v>
+        <v>33.10182552738377</v>
       </c>
       <c r="E537" t="n">
-        <v>34.05509216550963</v>
+        <v>34.05508831021996</v>
       </c>
       <c r="F537" t="n">
         <v>1453900</v>
@@ -11172,16 +11172,16 @@
         <v>44364</v>
       </c>
       <c r="B538" t="n">
-        <v>33.45165252685547</v>
+        <v>33.4516487121582</v>
       </c>
       <c r="C538" t="n">
-        <v>34.48362534228877</v>
+        <v>34.4836214099093</v>
       </c>
       <c r="D538" t="n">
-        <v>33.3904340832412</v>
+        <v>33.39043027552505</v>
       </c>
       <c r="E538" t="n">
-        <v>33.69652630131254</v>
+        <v>33.69652245869081</v>
       </c>
       <c r="F538" t="n">
         <v>1405500</v>
@@ -11192,16 +11192,16 @@
         <v>44365</v>
       </c>
       <c r="B539" t="n">
-        <v>33.9676399230957</v>
+        <v>33.96763610839844</v>
       </c>
       <c r="C539" t="n">
-        <v>34.53610072880572</v>
+        <v>34.53609685026812</v>
       </c>
       <c r="D539" t="n">
-        <v>33.10183095282514</v>
+        <v>33.10182723536157</v>
       </c>
       <c r="E539" t="n">
-        <v>33.93265700111092</v>
+        <v>33.93265319034237</v>
       </c>
       <c r="F539" t="n">
         <v>1658000</v>
@@ -11212,16 +11212,16 @@
         <v>44368</v>
       </c>
       <c r="B540" t="n">
-        <v>33.9676399230957</v>
+        <v>33.96763610839844</v>
       </c>
       <c r="C540" t="n">
-        <v>34.29997100964103</v>
+        <v>34.29996715762169</v>
       </c>
       <c r="D540" t="n">
-        <v>33.29423368758639</v>
+        <v>33.29422994851525</v>
       </c>
       <c r="E540" t="n">
-        <v>33.85394709472268</v>
+        <v>33.85394329279357</v>
       </c>
       <c r="F540" t="n">
         <v>1020900</v>
@@ -11272,16 +11272,16 @@
         <v>44371</v>
       </c>
       <c r="B543" t="n">
-        <v>32.3234748840332</v>
+        <v>32.32347869873047</v>
       </c>
       <c r="C543" t="n">
-        <v>33.58283321468035</v>
+        <v>33.58283717800244</v>
       </c>
       <c r="D543" t="n">
-        <v>32.04361821859042</v>
+        <v>32.04362200026004</v>
       </c>
       <c r="E543" t="n">
-        <v>32.96189811058422</v>
+        <v>32.96190200062584</v>
       </c>
       <c r="F543" t="n">
         <v>1167600</v>
@@ -11292,16 +11292,16 @@
         <v>44372</v>
       </c>
       <c r="B544" t="n">
-        <v>31.66756439208984</v>
+        <v>31.66756248474121</v>
       </c>
       <c r="C544" t="n">
-        <v>33.32046908377672</v>
+        <v>33.32046707687306</v>
       </c>
       <c r="D544" t="n">
-        <v>31.37021622866461</v>
+        <v>31.37021433922536</v>
       </c>
       <c r="E544" t="n">
-        <v>33.32046908377672</v>
+        <v>33.32046707687306</v>
       </c>
       <c r="F544" t="n">
         <v>888100</v>
@@ -11332,16 +11332,16 @@
         <v>44376</v>
       </c>
       <c r="B546" t="n">
-        <v>32.84821319580078</v>
+        <v>32.84820938110352</v>
       </c>
       <c r="C546" t="n">
-        <v>33.15430542359048</v>
+        <v>33.1543015733464</v>
       </c>
       <c r="D546" t="n">
-        <v>31.75502190204463</v>
+        <v>31.75501821430081</v>
       </c>
       <c r="E546" t="n">
-        <v>32.30598791206608</v>
+        <v>32.305984160338</v>
       </c>
       <c r="F546" t="n">
         <v>877800</v>
@@ -11352,16 +11352,16 @@
         <v>44377</v>
       </c>
       <c r="B547" t="n">
-        <v>33.46039581298828</v>
+        <v>33.46039962768555</v>
       </c>
       <c r="C547" t="n">
-        <v>34.09007503116541</v>
+        <v>34.0900789176501</v>
       </c>
       <c r="D547" t="n">
-        <v>32.64706460438268</v>
+        <v>32.64706832635503</v>
       </c>
       <c r="E547" t="n">
-        <v>32.83071993096604</v>
+        <v>32.83072367387626</v>
       </c>
       <c r="F547" t="n">
         <v>1605100</v>
@@ -11392,16 +11392,16 @@
         <v>44379</v>
       </c>
       <c r="B549" t="n">
-        <v>34.02885437011719</v>
+        <v>34.02885818481445</v>
       </c>
       <c r="C549" t="n">
-        <v>34.7634789647043</v>
+        <v>34.76348286175433</v>
       </c>
       <c r="D549" t="n">
-        <v>33.26799425520169</v>
+        <v>33.26799798460513</v>
       </c>
       <c r="E549" t="n">
-        <v>33.5391035283409</v>
+        <v>33.53910728813619</v>
       </c>
       <c r="F549" t="n">
         <v>1253300</v>
@@ -11412,16 +11412,16 @@
         <v>44382</v>
       </c>
       <c r="B550" t="n">
-        <v>34.14255142211914</v>
+        <v>34.14254760742188</v>
       </c>
       <c r="C550" t="n">
-        <v>34.76348327874786</v>
+        <v>34.76347939467478</v>
       </c>
       <c r="D550" t="n">
-        <v>33.84520325559686</v>
+        <v>33.84519947412186</v>
       </c>
       <c r="E550" t="n">
-        <v>34.02885859299604</v>
+        <v>34.02885479100151</v>
       </c>
       <c r="F550" t="n">
         <v>928400</v>
@@ -11472,16 +11472,16 @@
         <v>44385</v>
       </c>
       <c r="B553" t="n">
-        <v>34.2125129699707</v>
+        <v>34.21250915527344</v>
       </c>
       <c r="C553" t="n">
-        <v>34.2125129699707</v>
+        <v>34.21250915527344</v>
       </c>
       <c r="D553" t="n">
-        <v>32.20978910359841</v>
+        <v>32.20978551220497</v>
       </c>
       <c r="E553" t="n">
-        <v>32.93566637034174</v>
+        <v>32.93566269801294</v>
       </c>
       <c r="F553" t="n">
         <v>781400</v>
@@ -11512,16 +11512,16 @@
         <v>44390</v>
       </c>
       <c r="B555" t="n">
-        <v>34.04635238647461</v>
+        <v>34.04634857177734</v>
       </c>
       <c r="C555" t="n">
-        <v>34.57108291103507</v>
+        <v>34.57107903754478</v>
       </c>
       <c r="D555" t="n">
-        <v>33.39043756269638</v>
+        <v>33.39043382149058</v>
       </c>
       <c r="E555" t="n">
-        <v>34.57108291103507</v>
+        <v>34.57107903754478</v>
       </c>
       <c r="F555" t="n">
         <v>920800</v>
@@ -11552,16 +11552,16 @@
         <v>44392</v>
       </c>
       <c r="B557" t="n">
-        <v>34.14255142211914</v>
+        <v>34.14254760742188</v>
       </c>
       <c r="C557" t="n">
-        <v>34.80721026343979</v>
+        <v>34.80720637448117</v>
       </c>
       <c r="D557" t="n">
-        <v>33.93265722498073</v>
+        <v>33.93265343373464</v>
       </c>
       <c r="E557" t="n">
-        <v>34.29122383730274</v>
+        <v>34.29122000599452</v>
       </c>
       <c r="F557" t="n">
         <v>384200</v>
@@ -11592,16 +11592,16 @@
         <v>44396</v>
       </c>
       <c r="B559" t="n">
-        <v>32.82197570800781</v>
+        <v>32.82197189331055</v>
       </c>
       <c r="C559" t="n">
-        <v>33.10183242401401</v>
+        <v>33.10182857679071</v>
       </c>
       <c r="D559" t="n">
-        <v>31.64133039586639</v>
+        <v>31.6413267183883</v>
       </c>
       <c r="E559" t="n">
-        <v>32.27100967495793</v>
+        <v>32.27100592429607</v>
       </c>
       <c r="F559" t="n">
         <v>692000</v>
@@ -11612,16 +11612,16 @@
         <v>44397</v>
       </c>
       <c r="B560" t="n">
-        <v>32.88318634033203</v>
+        <v>32.88319396972656</v>
       </c>
       <c r="C560" t="n">
-        <v>33.21551736265797</v>
+        <v>33.2155250691583</v>
       </c>
       <c r="D560" t="n">
-        <v>31.96490650068703</v>
+        <v>31.9649139170268</v>
       </c>
       <c r="E560" t="n">
-        <v>32.82196790676599</v>
+        <v>32.82197552195692</v>
       </c>
       <c r="F560" t="n">
         <v>924500</v>
@@ -11672,16 +11672,16 @@
         <v>44400</v>
       </c>
       <c r="B563" t="n">
-        <v>32.76075744628906</v>
+        <v>32.7607536315918</v>
       </c>
       <c r="C563" t="n">
-        <v>33.33796234335534</v>
+        <v>33.33795846144773</v>
       </c>
       <c r="D563" t="n">
-        <v>32.36720789461769</v>
+        <v>32.36720412574574</v>
       </c>
       <c r="E563" t="n">
-        <v>33.11932407422182</v>
+        <v>33.11932021777268</v>
       </c>
       <c r="F563" t="n">
         <v>561000</v>
@@ -11692,16 +11692,16 @@
         <v>44403</v>
       </c>
       <c r="B564" t="n">
-        <v>32.97064590454102</v>
+        <v>32.97064971923828</v>
       </c>
       <c r="C564" t="n">
-        <v>33.41666642790693</v>
+        <v>33.41667029420868</v>
       </c>
       <c r="D564" t="n">
-        <v>32.37594964928337</v>
+        <v>32.3759533951744</v>
       </c>
       <c r="E564" t="n">
-        <v>33.08433871879298</v>
+        <v>33.08434254664448</v>
       </c>
       <c r="F564" t="n">
         <v>436800</v>
@@ -11712,16 +11712,16 @@
         <v>44404</v>
       </c>
       <c r="B565" t="n">
-        <v>32.09609985351562</v>
+        <v>32.09609603881836</v>
       </c>
       <c r="C565" t="n">
-        <v>32.9793970280636</v>
+        <v>32.97939310838438</v>
       </c>
       <c r="D565" t="n">
-        <v>31.17781975383665</v>
+        <v>31.17781604827914</v>
       </c>
       <c r="E565" t="n">
-        <v>32.49839348405607</v>
+        <v>32.49838962154526</v>
       </c>
       <c r="F565" t="n">
         <v>900400</v>
@@ -11732,16 +11732,16 @@
         <v>44405</v>
       </c>
       <c r="B566" t="n">
-        <v>32.62082672119141</v>
+        <v>32.62082290649414</v>
       </c>
       <c r="C566" t="n">
-        <v>32.69079256359336</v>
+        <v>32.69078874071425</v>
       </c>
       <c r="D566" t="n">
-        <v>31.60634535944806</v>
+        <v>31.6063416633848</v>
       </c>
       <c r="E566" t="n">
-        <v>32.09609624779674</v>
+        <v>32.09609249446174</v>
       </c>
       <c r="F566" t="n">
         <v>535400</v>
@@ -11752,16 +11752,16 @@
         <v>44406</v>
       </c>
       <c r="B567" t="n">
-        <v>31.98240089416504</v>
+        <v>31.9824047088623</v>
       </c>
       <c r="C567" t="n">
-        <v>32.74326102129739</v>
+        <v>32.74326492674616</v>
       </c>
       <c r="D567" t="n">
-        <v>31.60634286136468</v>
+        <v>31.60634663120767</v>
       </c>
       <c r="E567" t="n">
-        <v>32.55086164220875</v>
+        <v>32.55086552470911</v>
       </c>
       <c r="F567" t="n">
         <v>709900</v>
@@ -11772,16 +11772,16 @@
         <v>44407</v>
       </c>
       <c r="B568" t="n">
-        <v>30.69680786132812</v>
+        <v>30.69680976867676</v>
       </c>
       <c r="C568" t="n">
-        <v>31.65007073048404</v>
+        <v>31.65007269706374</v>
       </c>
       <c r="D568" t="n">
-        <v>30.48691701712498</v>
+        <v>30.48691891143203</v>
       </c>
       <c r="E568" t="n">
-        <v>31.52763384867307</v>
+        <v>31.52763580764514</v>
       </c>
       <c r="F568" t="n">
         <v>1140100</v>
@@ -11812,16 +11812,16 @@
         <v>44411</v>
       </c>
       <c r="B570" t="n">
-        <v>31.45767402648926</v>
+        <v>31.45767021179199</v>
       </c>
       <c r="C570" t="n">
-        <v>31.80749324202077</v>
+        <v>31.80748938490287</v>
       </c>
       <c r="D570" t="n">
-        <v>30.52190253730594</v>
+        <v>30.52189883608448</v>
       </c>
       <c r="E570" t="n">
-        <v>30.83673883043777</v>
+        <v>30.83673509103786</v>
       </c>
       <c r="F570" t="n">
         <v>798700</v>
@@ -11832,16 +11832,16 @@
         <v>44412</v>
       </c>
       <c r="B571" t="n">
-        <v>31.17781257629395</v>
+        <v>31.17781639099121</v>
       </c>
       <c r="C571" t="n">
-        <v>31.73752590491517</v>
+        <v>31.73752978809501</v>
       </c>
       <c r="D571" t="n">
-        <v>30.5393860161711</v>
+        <v>30.539389752755</v>
       </c>
       <c r="E571" t="n">
-        <v>31.45766924060456</v>
+        <v>31.45767308954311</v>
       </c>
       <c r="F571" t="n">
         <v>454700</v>
@@ -11852,16 +11852,16 @@
         <v>44413</v>
       </c>
       <c r="B572" t="n">
-        <v>30.79300880432129</v>
+        <v>30.79301071166992</v>
       </c>
       <c r="C572" t="n">
-        <v>31.4139406028929</v>
+        <v>31.41394254870265</v>
       </c>
       <c r="D572" t="n">
-        <v>30.32949680484596</v>
+        <v>30.32949868348422</v>
       </c>
       <c r="E572" t="n">
-        <v>31.18655830206202</v>
+        <v>31.18656023378749</v>
       </c>
       <c r="F572" t="n">
         <v>680400</v>
@@ -11912,16 +11912,16 @@
         <v>44418</v>
       </c>
       <c r="B575" t="n">
-        <v>30.79300880432129</v>
+        <v>30.79301071166992</v>
       </c>
       <c r="C575" t="n">
-        <v>31.1953023637208</v>
+        <v>31.19530429598789</v>
       </c>
       <c r="D575" t="n">
-        <v>30.32949680484596</v>
+        <v>30.32949868348422</v>
       </c>
       <c r="E575" t="n">
-        <v>30.5656265034904</v>
+        <v>30.56562839675476</v>
       </c>
       <c r="F575" t="n">
         <v>335500</v>
@@ -11952,16 +11952,16 @@
         <v>44420</v>
       </c>
       <c r="B577" t="n">
-        <v>30.32949638366699</v>
+        <v>30.32949447631836</v>
       </c>
       <c r="C577" t="n">
-        <v>30.66182743671691</v>
+        <v>30.66182550846878</v>
       </c>
       <c r="D577" t="n">
-        <v>29.6560902160298</v>
+        <v>29.65608835103005</v>
       </c>
       <c r="E577" t="n">
-        <v>30.34698784289643</v>
+        <v>30.3469859344478</v>
       </c>
       <c r="F577" t="n">
         <v>452300</v>
@@ -11992,16 +11992,16 @@
         <v>44424</v>
       </c>
       <c r="B579" t="n">
-        <v>29.35000038146973</v>
+        <v>29.35000228881836</v>
       </c>
       <c r="C579" t="n">
-        <v>29.76978542828899</v>
+        <v>29.76978736291791</v>
       </c>
       <c r="D579" t="n">
-        <v>27.74082103250755</v>
+        <v>27.74082283528154</v>
       </c>
       <c r="E579" t="n">
-        <v>29.56863863519778</v>
+        <v>29.56864055675491</v>
       </c>
       <c r="F579" t="n">
         <v>1220000</v>
@@ -12012,16 +12012,16 @@
         <v>44425</v>
       </c>
       <c r="B580" t="n">
-        <v>28.75530052185059</v>
+        <v>28.75530242919922</v>
       </c>
       <c r="C580" t="n">
-        <v>28.86024593658762</v>
+        <v>28.86024785089732</v>
       </c>
       <c r="D580" t="n">
-        <v>26.63888075170044</v>
+        <v>26.63888251866625</v>
       </c>
       <c r="E580" t="n">
-        <v>28.85150187542395</v>
+        <v>28.85150378915365</v>
       </c>
       <c r="F580" t="n">
         <v>2491100</v>
@@ -12052,16 +12052,16 @@
         <v>44427</v>
       </c>
       <c r="B582" t="n">
-        <v>29.0089225769043</v>
+        <v>29.00892066955566</v>
       </c>
       <c r="C582" t="n">
-        <v>29.02641403794732</v>
+        <v>29.02641212944861</v>
       </c>
       <c r="D582" t="n">
-        <v>27.06741710730059</v>
+        <v>27.06741532760674</v>
       </c>
       <c r="E582" t="n">
-        <v>27.11114409183059</v>
+        <v>27.11114230926168</v>
       </c>
       <c r="F582" t="n">
         <v>1191700</v>
@@ -12072,16 +12072,16 @@
         <v>44428</v>
       </c>
       <c r="B583" t="n">
-        <v>29.48992919921875</v>
+        <v>29.48992729187012</v>
       </c>
       <c r="C583" t="n">
-        <v>29.77852996392715</v>
+        <v>29.7785280379124</v>
       </c>
       <c r="D583" t="n">
-        <v>28.57164585003873</v>
+        <v>28.5716440020828</v>
       </c>
       <c r="E583" t="n">
-        <v>28.64161169369838</v>
+        <v>28.64160984121719</v>
       </c>
       <c r="F583" t="n">
         <v>449500</v>
@@ -12112,16 +12112,16 @@
         <v>44432</v>
       </c>
       <c r="B585" t="n">
-        <v>32.09609985351562</v>
+        <v>32.09609603881836</v>
       </c>
       <c r="C585" t="n">
-        <v>32.384700645458</v>
+        <v>32.38469679645984</v>
       </c>
       <c r="D585" t="n">
-        <v>30.27702778056781</v>
+        <v>30.27702418207156</v>
       </c>
       <c r="E585" t="n">
-        <v>30.62685035956712</v>
+        <v>30.62684671949362</v>
       </c>
       <c r="F585" t="n">
         <v>1338400</v>
@@ -12152,16 +12152,16 @@
         <v>44434</v>
       </c>
       <c r="B587" t="n">
-        <v>30.47817039489746</v>
+        <v>30.47817230224609</v>
       </c>
       <c r="C587" t="n">
-        <v>32.20104085434187</v>
+        <v>32.20104286950913</v>
       </c>
       <c r="D587" t="n">
-        <v>30.39946049227932</v>
+        <v>30.39946239470222</v>
       </c>
       <c r="E587" t="n">
-        <v>31.9561670844876</v>
+        <v>31.95616908433047</v>
       </c>
       <c r="F587" t="n">
         <v>852900</v>
@@ -12252,16 +12252,16 @@
         <v>44441</v>
       </c>
       <c r="B592" t="n">
-        <v>29.23630332946777</v>
+        <v>29.23630523681641</v>
       </c>
       <c r="C592" t="n">
-        <v>29.62985279652395</v>
+        <v>29.62985472954738</v>
       </c>
       <c r="D592" t="n">
-        <v>28.74655251089181</v>
+        <v>28.74655438628956</v>
       </c>
       <c r="E592" t="n">
-        <v>29.47243300970148</v>
+        <v>29.47243493245499</v>
       </c>
       <c r="F592" t="n">
         <v>669700</v>
@@ -12312,16 +12312,16 @@
         <v>44447</v>
       </c>
       <c r="B595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="C595" t="n">
-        <v>27.96820405019139</v>
+        <v>27.96820604747386</v>
       </c>
       <c r="D595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="E595" t="n">
-        <v>27.89823987813893</v>
+        <v>27.89824187042507</v>
       </c>
       <c r="F595" t="n">
         <v>518300</v>
@@ -12352,16 +12352,16 @@
         <v>44449</v>
       </c>
       <c r="B597" t="n">
-        <v>28.16060829162598</v>
+        <v>28.16060638427734</v>
       </c>
       <c r="C597" t="n">
-        <v>28.72906576061172</v>
+        <v>28.72906381476085</v>
       </c>
       <c r="D597" t="n">
-        <v>27.81078574443855</v>
+        <v>27.81078386078378</v>
       </c>
       <c r="E597" t="n">
-        <v>28.03817140095689</v>
+        <v>28.03816950190105</v>
       </c>
       <c r="F597" t="n">
         <v>695400</v>
@@ -12412,16 +12412,16 @@
         <v>44454</v>
       </c>
       <c r="B600" t="n">
-        <v>28.22182464599609</v>
+        <v>28.22182655334473</v>
       </c>
       <c r="C600" t="n">
-        <v>29.47243565572363</v>
+        <v>29.47243764759377</v>
       </c>
       <c r="D600" t="n">
-        <v>27.98569494456277</v>
+        <v>27.98569683595277</v>
       </c>
       <c r="E600" t="n">
-        <v>29.44619679812783</v>
+        <v>29.44619878822463</v>
       </c>
       <c r="F600" t="n">
         <v>944900</v>
@@ -12452,16 +12452,16 @@
         <v>44456</v>
       </c>
       <c r="B602" t="n">
-        <v>27.54841995239258</v>
+        <v>27.54841804504395</v>
       </c>
       <c r="C602" t="n">
-        <v>27.86325957134758</v>
+        <v>27.86325764220064</v>
       </c>
       <c r="D602" t="n">
-        <v>27.18985334995049</v>
+        <v>27.18985146742766</v>
       </c>
       <c r="E602" t="n">
-        <v>27.86325957134758</v>
+        <v>27.86325764220064</v>
       </c>
       <c r="F602" t="n">
         <v>407600</v>
@@ -12492,16 +12492,16 @@
         <v>44460</v>
       </c>
       <c r="B604" t="n">
-        <v>27.69709396362305</v>
+        <v>27.69709587097168</v>
       </c>
       <c r="C604" t="n">
-        <v>28.16935172281972</v>
+        <v>28.16935366269018</v>
       </c>
       <c r="D604" t="n">
-        <v>26.90125085595213</v>
+        <v>26.90125270849537</v>
       </c>
       <c r="E604" t="n">
-        <v>27.25107172722328</v>
+        <v>27.25107360385678</v>
       </c>
       <c r="F604" t="n">
         <v>267700</v>
@@ -12532,16 +12532,16 @@
         <v>44462</v>
       </c>
       <c r="B606" t="n">
-        <v>29.44619750976562</v>
+        <v>29.44619560241699</v>
       </c>
       <c r="C606" t="n">
-        <v>29.58612919057884</v>
+        <v>29.58612727416627</v>
       </c>
       <c r="D606" t="n">
-        <v>28.46669909715735</v>
+        <v>28.46669725325478</v>
       </c>
       <c r="E606" t="n">
-        <v>28.86024860905729</v>
+        <v>28.86024673966293</v>
       </c>
       <c r="F606" t="n">
         <v>1113800</v>
@@ -12612,16 +12612,16 @@
         <v>44468</v>
       </c>
       <c r="B610" t="n">
-        <v>25.05594062805176</v>
+        <v>25.05594253540039</v>
       </c>
       <c r="C610" t="n">
-        <v>26.09665906175857</v>
+        <v>26.09666104833045</v>
       </c>
       <c r="D610" t="n">
-        <v>24.79357542133852</v>
+        <v>24.79357730871497</v>
       </c>
       <c r="E610" t="n">
-        <v>24.97723073242232</v>
+        <v>24.97723263377928</v>
       </c>
       <c r="F610" t="n">
         <v>1006800</v>
@@ -12632,16 +12632,16 @@
         <v>44469</v>
       </c>
       <c r="B611" t="n">
-        <v>24.44375419616699</v>
+        <v>24.44375610351562</v>
       </c>
       <c r="C611" t="n">
-        <v>25.51945386168145</v>
+        <v>25.51945585296703</v>
       </c>
       <c r="D611" t="n">
-        <v>23.74411087606664</v>
+        <v>23.74411272882204</v>
       </c>
       <c r="E611" t="n">
-        <v>25.20461428423243</v>
+        <v>25.20461625095105</v>
       </c>
       <c r="F611" t="n">
         <v>2108000</v>
@@ -12652,16 +12652,16 @@
         <v>44470</v>
       </c>
       <c r="B612" t="n">
-        <v>25.08217811584473</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C612" t="n">
-        <v>25.08217811584473</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="D612" t="n">
-        <v>23.8578043564151</v>
+        <v>23.85780617065748</v>
       </c>
       <c r="E612" t="n">
-        <v>24.44375488195263</v>
+        <v>24.44375674075302</v>
       </c>
       <c r="F612" t="n">
         <v>1977000</v>
@@ -12672,16 +12672,16 @@
         <v>44473</v>
       </c>
       <c r="B613" t="n">
-        <v>24.40002632141113</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="C613" t="n">
-        <v>25.08217820474767</v>
+        <v>25.08218212609248</v>
       </c>
       <c r="D613" t="n">
-        <v>24.06769694321784</v>
+        <v>24.06770070595877</v>
       </c>
       <c r="E613" t="n">
-        <v>25.08217820474767</v>
+        <v>25.08218212609248</v>
       </c>
       <c r="F613" t="n">
         <v>966400</v>
@@ -12692,16 +12692,16 @@
         <v>44474</v>
       </c>
       <c r="B614" t="n">
-        <v>24.1289176940918</v>
+        <v>24.12891578674316</v>
       </c>
       <c r="C614" t="n">
-        <v>24.95974372133053</v>
+        <v>24.95974174830655</v>
       </c>
       <c r="D614" t="n">
-        <v>23.93651663228211</v>
+        <v>23.93651474014245</v>
       </c>
       <c r="E614" t="n">
-        <v>24.95974372133053</v>
+        <v>24.95974174830655</v>
       </c>
       <c r="F614" t="n">
         <v>1123700</v>
@@ -12732,16 +12732,16 @@
         <v>44476</v>
       </c>
       <c r="B616" t="n">
-        <v>25.20461845397949</v>
+        <v>25.20461654663086</v>
       </c>
       <c r="C616" t="n">
-        <v>25.74684207505855</v>
+        <v>25.74684012667738</v>
       </c>
       <c r="D616" t="n">
-        <v>25.01221738486243</v>
+        <v>25.01221549207367</v>
       </c>
       <c r="E616" t="n">
-        <v>25.28332836136319</v>
+        <v>25.28332644805822</v>
       </c>
       <c r="F616" t="n">
         <v>920700</v>
@@ -12772,16 +12772,16 @@
         <v>44480</v>
       </c>
       <c r="B618" t="n">
-        <v>24.31257057189941</v>
+        <v>24.31257247924805</v>
       </c>
       <c r="C618" t="n">
-        <v>25.81680266577481</v>
+        <v>25.81680469113214</v>
       </c>
       <c r="D618" t="n">
-        <v>24.00647838356647</v>
+        <v>24.00648026690182</v>
       </c>
       <c r="E618" t="n">
-        <v>25.49321735058056</v>
+        <v>25.49321935055227</v>
       </c>
       <c r="F618" t="n">
         <v>1581200</v>
@@ -12872,16 +12872,16 @@
         <v>44488</v>
       </c>
       <c r="B623" t="n">
-        <v>22.98325347900391</v>
+        <v>22.98325538635254</v>
       </c>
       <c r="C623" t="n">
-        <v>24.68863083101386</v>
+        <v>24.68863287988942</v>
       </c>
       <c r="D623" t="n">
-        <v>22.65092240432388</v>
+        <v>22.65092428409281</v>
       </c>
       <c r="E623" t="n">
-        <v>24.53995675404174</v>
+        <v>24.53995879057904</v>
       </c>
       <c r="F623" t="n">
         <v>1196900</v>
@@ -12912,16 +12912,16 @@
         <v>44490</v>
       </c>
       <c r="B625" t="n">
-        <v>21.36532974243164</v>
+        <v>21.36533164978027</v>
       </c>
       <c r="C625" t="n">
-        <v>22.56346640067376</v>
+        <v>22.56346841498373</v>
       </c>
       <c r="D625" t="n">
-        <v>21.08547305344304</v>
+        <v>21.08547493580801</v>
       </c>
       <c r="E625" t="n">
-        <v>22.41479232613888</v>
+        <v>22.41479432717626</v>
       </c>
       <c r="F625" t="n">
         <v>1161600</v>
@@ -12932,16 +12932,16 @@
         <v>44491</v>
       </c>
       <c r="B626" t="n">
-        <v>20.77063369750977</v>
+        <v>20.77063179016113</v>
       </c>
       <c r="C626" t="n">
-        <v>21.49651261895227</v>
+        <v>21.49651064494683</v>
       </c>
       <c r="D626" t="n">
-        <v>18.8378723730713</v>
+        <v>18.8378706432064</v>
       </c>
       <c r="E626" t="n">
-        <v>21.14669175345181</v>
+        <v>21.1466898115701</v>
       </c>
       <c r="F626" t="n">
         <v>2354200</v>
@@ -12952,16 +12952,16 @@
         <v>44494</v>
       </c>
       <c r="B627" t="n">
-        <v>21.74138641357422</v>
+        <v>21.74138832092285</v>
       </c>
       <c r="C627" t="n">
-        <v>22.17866287937851</v>
+        <v>22.17866482508894</v>
       </c>
       <c r="D627" t="n">
-        <v>20.98927035860608</v>
+        <v>20.98927219997238</v>
       </c>
       <c r="E627" t="n">
-        <v>21.01550754706219</v>
+        <v>21.01550939073024</v>
       </c>
       <c r="F627" t="n">
         <v>1250000</v>
@@ -12972,16 +12972,16 @@
         <v>44495</v>
       </c>
       <c r="B628" t="n">
-        <v>20.12346267700195</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C628" t="n">
-        <v>21.57522037543505</v>
+        <v>21.57522242038466</v>
       </c>
       <c r="D628" t="n">
-        <v>19.92231590786325</v>
+        <v>19.92231779614673</v>
       </c>
       <c r="E628" t="n">
-        <v>21.55772891688109</v>
+        <v>21.55773096017281</v>
       </c>
       <c r="F628" t="n">
         <v>1203400</v>
@@ -12992,16 +12992,16 @@
         <v>44496</v>
       </c>
       <c r="B629" t="n">
-        <v>19.92231750488281</v>
+        <v>19.92231559753418</v>
       </c>
       <c r="C629" t="n">
-        <v>20.74439610589131</v>
+        <v>20.74439411983746</v>
       </c>
       <c r="D629" t="n">
-        <v>19.68618779970748</v>
+        <v>19.68618591496573</v>
       </c>
       <c r="E629" t="n">
-        <v>20.21091992184908</v>
+        <v>20.21091798686986</v>
       </c>
       <c r="F629" t="n">
         <v>1470900</v>
@@ -13092,16 +13092,16 @@
         <v>44504</v>
       </c>
       <c r="B634" t="n">
-        <v>20.17593574523926</v>
+        <v>20.17593765258789</v>
       </c>
       <c r="C634" t="n">
-        <v>21.11170710959876</v>
+        <v>21.11170910541131</v>
       </c>
       <c r="D634" t="n">
-        <v>19.6424579263483</v>
+        <v>19.64245978326417</v>
       </c>
       <c r="E634" t="n">
-        <v>20.64819512617433</v>
+        <v>20.64819707816839</v>
       </c>
       <c r="F634" t="n">
         <v>1063000</v>
@@ -13132,16 +13132,16 @@
         <v>44508</v>
       </c>
       <c r="B636" t="n">
-        <v>20.2109203338623</v>
+        <v>20.21092224121094</v>
       </c>
       <c r="C636" t="n">
-        <v>20.7793794494052</v>
+        <v>20.77938141040056</v>
       </c>
       <c r="D636" t="n">
-        <v>19.72116945357161</v>
+        <v>19.72117131470138</v>
       </c>
       <c r="E636" t="n">
-        <v>20.7793794494052</v>
+        <v>20.77938141040056</v>
       </c>
       <c r="F636" t="n">
         <v>938800</v>
@@ -13152,16 +13152,16 @@
         <v>44509</v>
       </c>
       <c r="B637" t="n">
-        <v>21.48776435852051</v>
+        <v>21.48776626586914</v>
       </c>
       <c r="C637" t="n">
-        <v>21.87256809929731</v>
+        <v>21.87257004080282</v>
       </c>
       <c r="D637" t="n">
-        <v>20.1934264745444</v>
+        <v>20.1934282670019</v>
       </c>
       <c r="E637" t="n">
-        <v>20.29837188779799</v>
+        <v>20.29837368957091</v>
       </c>
       <c r="F637" t="n">
         <v>1107100</v>
@@ -13252,16 +13252,16 @@
         <v>44517</v>
       </c>
       <c r="B642" t="n">
-        <v>21.64518737792969</v>
+        <v>21.64518547058105</v>
       </c>
       <c r="C642" t="n">
-        <v>22.3448291309954</v>
+        <v>22.34482716199515</v>
       </c>
       <c r="D642" t="n">
-        <v>20.56074182663908</v>
+        <v>20.56074001485052</v>
       </c>
       <c r="E642" t="n">
-        <v>21.95128127042501</v>
+        <v>21.95127933610373</v>
       </c>
       <c r="F642" t="n">
         <v>1875600</v>
@@ -13312,16 +13312,16 @@
         <v>44522</v>
       </c>
       <c r="B645" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C645" t="n">
-        <v>24.76734051949353</v>
+        <v>24.76733851815552</v>
       </c>
       <c r="D645" t="n">
-        <v>23.01823453175441</v>
+        <v>23.01823267175383</v>
       </c>
       <c r="E645" t="n">
-        <v>24.57493946135012</v>
+        <v>24.57493747555916</v>
       </c>
       <c r="F645" t="n">
         <v>1417300</v>
@@ -13332,16 +13332,16 @@
         <v>44523</v>
       </c>
       <c r="B646" t="n">
-        <v>22.82583045959473</v>
+        <v>22.82583427429199</v>
       </c>
       <c r="C646" t="n">
-        <v>23.9015300996759</v>
+        <v>23.90153409414619</v>
       </c>
       <c r="D646" t="n">
-        <v>22.467263912901</v>
+        <v>22.46726766767393</v>
       </c>
       <c r="E646" t="n">
-        <v>23.61292771653029</v>
+        <v>23.61293166276878</v>
       </c>
       <c r="F646" t="n">
         <v>1018600</v>
@@ -13452,16 +13452,16 @@
         <v>44531</v>
       </c>
       <c r="B652" t="n">
-        <v>21.12045478820801</v>
+        <v>21.12045288085938</v>
       </c>
       <c r="C652" t="n">
-        <v>22.61594129777468</v>
+        <v>22.61593925537147</v>
       </c>
       <c r="D652" t="n">
-        <v>20.89307080618885</v>
+        <v>20.89306891937484</v>
       </c>
       <c r="E652" t="n">
-        <v>21.54023983128454</v>
+        <v>21.5402378860259</v>
       </c>
       <c r="F652" t="n">
         <v>1232500</v>
@@ -13512,16 +13512,16 @@
         <v>44536</v>
       </c>
       <c r="B655" t="n">
-        <v>22.54597854614258</v>
+        <v>22.54597663879395</v>
       </c>
       <c r="C655" t="n">
-        <v>22.93078069253087</v>
+        <v>22.93077875262868</v>
       </c>
       <c r="D655" t="n">
-        <v>21.99500918278135</v>
+        <v>21.99500732204372</v>
       </c>
       <c r="E655" t="n">
-        <v>22.30110308819564</v>
+        <v>22.30110120156302</v>
       </c>
       <c r="F655" t="n">
         <v>546700</v>
@@ -13532,16 +13532,16 @@
         <v>44537</v>
       </c>
       <c r="B656" t="n">
-        <v>22.51099395751953</v>
+        <v>22.5109920501709</v>
       </c>
       <c r="C656" t="n">
-        <v>23.21063735642938</v>
+        <v>23.2106353898002</v>
       </c>
       <c r="D656" t="n">
-        <v>22.48475676708427</v>
+        <v>22.4847548619587</v>
       </c>
       <c r="E656" t="n">
-        <v>22.91328920380625</v>
+        <v>22.91328726237128</v>
       </c>
       <c r="F656" t="n">
         <v>687200</v>
@@ -13572,16 +13572,16 @@
         <v>44539</v>
       </c>
       <c r="B658" t="n">
-        <v>21.5839672088623</v>
+        <v>21.58396911621094</v>
       </c>
       <c r="C658" t="n">
-        <v>22.47601162382038</v>
+        <v>22.47601360999788</v>
       </c>
       <c r="D658" t="n">
-        <v>20.91930676250594</v>
+        <v>20.91930861111934</v>
       </c>
       <c r="E658" t="n">
-        <v>21.9162965980018</v>
+        <v>21.91629853471797</v>
       </c>
       <c r="F658" t="n">
         <v>688300</v>
@@ -13632,16 +13632,16 @@
         <v>44544</v>
       </c>
       <c r="B661" t="n">
-        <v>20.06224822998047</v>
+        <v>20.06224632263184</v>
       </c>
       <c r="C661" t="n">
-        <v>22.05622819551692</v>
+        <v>22.05622609859756</v>
       </c>
       <c r="D661" t="n">
-        <v>19.87859121479401</v>
+        <v>19.87858932490593</v>
       </c>
       <c r="E661" t="n">
-        <v>22.038738401562</v>
+        <v>22.03873630630543</v>
       </c>
       <c r="F661" t="n">
         <v>1317100</v>
@@ -13692,16 +13692,16 @@
         <v>44547</v>
       </c>
       <c r="B664" t="n">
-        <v>19.57249641418457</v>
+        <v>19.5724925994873</v>
       </c>
       <c r="C664" t="n">
-        <v>19.89608177480587</v>
+        <v>19.89607789704152</v>
       </c>
       <c r="D664" t="n">
-        <v>19.1527113529009</v>
+        <v>19.15270762002013</v>
       </c>
       <c r="E664" t="n">
-        <v>19.71242643602335</v>
+        <v>19.71242259405359</v>
       </c>
       <c r="F664" t="n">
         <v>983600</v>
@@ -13812,16 +13812,16 @@
         <v>44558</v>
       </c>
       <c r="B670" t="n">
-        <v>19.3713493347168</v>
+        <v>19.37134742736816</v>
       </c>
       <c r="C670" t="n">
-        <v>19.59873332331799</v>
+        <v>19.5987313935806</v>
       </c>
       <c r="D670" t="n">
-        <v>18.95156427948884</v>
+        <v>18.95156241347323</v>
       </c>
       <c r="E670" t="n">
-        <v>19.26640390494857</v>
+        <v>19.26640200793311</v>
       </c>
       <c r="F670" t="n">
         <v>786500</v>
@@ -13872,16 +13872,16 @@
         <v>44564</v>
       </c>
       <c r="B673" t="n">
-        <v>18.41808700561523</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="C673" t="n">
-        <v>19.69493534263136</v>
+        <v>19.69493330305429</v>
       </c>
       <c r="D673" t="n">
-        <v>18.41808700561523</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="E673" t="n">
-        <v>19.43256842337061</v>
+        <v>19.43256641096385</v>
       </c>
       <c r="F673" t="n">
         <v>684800</v>
@@ -13892,16 +13892,16 @@
         <v>44565</v>
       </c>
       <c r="B674" t="n">
-        <v>17.84087944030762</v>
+        <v>17.84088134765625</v>
       </c>
       <c r="C674" t="n">
-        <v>18.62797674377699</v>
+        <v>18.62797873527332</v>
       </c>
       <c r="D674" t="n">
-        <v>17.70969683440894</v>
+        <v>17.70969872773299</v>
       </c>
       <c r="E674" t="n">
-        <v>18.50553986734854</v>
+        <v>18.50554184575528</v>
       </c>
       <c r="F674" t="n">
         <v>701900</v>
@@ -13932,16 +13932,16 @@
         <v>44567</v>
       </c>
       <c r="B676" t="n">
-        <v>17.26367378234863</v>
+        <v>17.26367568969727</v>
       </c>
       <c r="C676" t="n">
-        <v>17.67471303856744</v>
+        <v>17.67471499132907</v>
       </c>
       <c r="D676" t="n">
-        <v>16.83514306805824</v>
+        <v>16.83514492806136</v>
       </c>
       <c r="E676" t="n">
-        <v>17.25492805331284</v>
+        <v>17.25492995969521</v>
       </c>
       <c r="F676" t="n">
         <v>1271200</v>
@@ -13972,16 +13972,16 @@
         <v>44571</v>
       </c>
       <c r="B678" t="n">
-        <v>17.31614875793457</v>
+        <v>17.31614685058594</v>
       </c>
       <c r="C678" t="n">
-        <v>17.79715390948009</v>
+        <v>17.79715194914944</v>
       </c>
       <c r="D678" t="n">
-        <v>16.94883643067766</v>
+        <v>16.94883456378794</v>
       </c>
       <c r="E678" t="n">
-        <v>17.79715390948009</v>
+        <v>17.79715194914944</v>
       </c>
       <c r="F678" t="n">
         <v>513900</v>
@@ -13992,16 +13992,16 @@
         <v>44572</v>
       </c>
       <c r="B679" t="n">
-        <v>17.67471504211426</v>
+        <v>17.67471694946289</v>
       </c>
       <c r="C679" t="n">
-        <v>18.04202736286865</v>
+        <v>18.04202930985541</v>
       </c>
       <c r="D679" t="n">
-        <v>17.1237473950214</v>
+        <v>17.12374924291292</v>
       </c>
       <c r="E679" t="n">
-        <v>17.31614845138705</v>
+        <v>17.31615032004134</v>
       </c>
       <c r="F679" t="n">
         <v>597700</v>
@@ -14052,16 +14052,16 @@
         <v>44575</v>
       </c>
       <c r="B682" t="n">
-        <v>18.34811973571777</v>
+        <v>18.34812355041504</v>
       </c>
       <c r="C682" t="n">
-        <v>18.4268296314254</v>
+        <v>18.42683346248698</v>
       </c>
       <c r="D682" t="n">
-        <v>17.51729546824893</v>
+        <v>17.51729911021225</v>
       </c>
       <c r="E682" t="n">
-        <v>18.27815556931958</v>
+        <v>18.27815936947083</v>
       </c>
       <c r="F682" t="n">
         <v>846900</v>
@@ -14072,16 +14072,16 @@
         <v>44578</v>
       </c>
       <c r="B683" t="n">
-        <v>18.10324668884277</v>
+        <v>18.10324859619141</v>
       </c>
       <c r="C683" t="n">
-        <v>18.66296004171654</v>
+        <v>18.66296200803628</v>
       </c>
       <c r="D683" t="n">
-        <v>17.84087980362516</v>
+        <v>17.84088168333096</v>
       </c>
       <c r="E683" t="n">
-        <v>18.47055899368553</v>
+        <v>18.47056093973399</v>
       </c>
       <c r="F683" t="n">
         <v>353900</v>
@@ -14172,16 +14172,16 @@
         <v>44585</v>
       </c>
       <c r="B688" t="n">
-        <v>19.24891090393066</v>
+        <v>19.2489128112793</v>
       </c>
       <c r="C688" t="n">
-        <v>19.34511226358611</v>
+        <v>19.34511418046721</v>
       </c>
       <c r="D688" t="n">
-        <v>18.14697397106082</v>
+        <v>18.14697576922</v>
       </c>
       <c r="E688" t="n">
-        <v>19.14396381448132</v>
+        <v>19.14396571143088</v>
       </c>
       <c r="F688" t="n">
         <v>1257200</v>
@@ -14372,16 +14372,16 @@
         <v>44599</v>
       </c>
       <c r="B698" t="n">
-        <v>19.82611846923828</v>
+        <v>19.82611656188965</v>
       </c>
       <c r="C698" t="n">
-        <v>20.61321591075569</v>
+        <v>20.61321392768527</v>
       </c>
       <c r="D698" t="n">
-        <v>19.52002455640439</v>
+        <v>19.52002267850317</v>
       </c>
       <c r="E698" t="n">
-        <v>20.00102975316554</v>
+        <v>20.00102782898977</v>
       </c>
       <c r="F698" t="n">
         <v>648500</v>
@@ -14392,16 +14392,16 @@
         <v>44600</v>
       </c>
       <c r="B699" t="n">
-        <v>19.58123970031738</v>
+        <v>19.58124351501465</v>
       </c>
       <c r="C699" t="n">
-        <v>19.91357075007084</v>
+        <v>19.9135746295108</v>
       </c>
       <c r="D699" t="n">
-        <v>19.26640177769722</v>
+        <v>19.26640553105968</v>
       </c>
       <c r="E699" t="n">
-        <v>19.6337140774852</v>
+        <v>19.6337179024052</v>
       </c>
       <c r="F699" t="n">
         <v>905900</v>
@@ -14412,16 +14412,16 @@
         <v>44601</v>
       </c>
       <c r="B700" t="n">
-        <v>19.55500411987305</v>
+        <v>19.55500602722168</v>
       </c>
       <c r="C700" t="n">
-        <v>20.272137258195</v>
+        <v>20.2721392354911</v>
       </c>
       <c r="D700" t="n">
-        <v>19.26640171864403</v>
+        <v>19.26640359784307</v>
       </c>
       <c r="E700" t="n">
-        <v>19.75615089416777</v>
+        <v>19.75615282113579</v>
       </c>
       <c r="F700" t="n">
         <v>1302000</v>
@@ -14432,16 +14432,16 @@
         <v>44602</v>
       </c>
       <c r="B701" t="n">
-        <v>19.7911319732666</v>
+        <v>19.79113388061523</v>
       </c>
       <c r="C701" t="n">
-        <v>20.02726166352781</v>
+        <v>20.02726359363318</v>
       </c>
       <c r="D701" t="n">
-        <v>18.89034352742746</v>
+        <v>18.8903453479636</v>
       </c>
       <c r="E701" t="n">
-        <v>19.46754832490331</v>
+        <v>19.46755020106692</v>
       </c>
       <c r="F701" t="n">
         <v>1325100</v>
@@ -14472,16 +14472,16 @@
         <v>44606</v>
       </c>
       <c r="B703" t="n">
-        <v>19.29263877868652</v>
+        <v>19.29264068603516</v>
       </c>
       <c r="C703" t="n">
-        <v>19.76489820097314</v>
+        <v>19.76490015501126</v>
       </c>
       <c r="D703" t="n">
-        <v>18.89909092819181</v>
+        <v>18.89909279663271</v>
       </c>
       <c r="E703" t="n">
-        <v>19.31013023908472</v>
+        <v>19.31013214816264</v>
       </c>
       <c r="F703" t="n">
         <v>1665200</v>
@@ -14492,16 +14492,16 @@
         <v>44607</v>
       </c>
       <c r="B704" t="n">
-        <v>20.92805480957031</v>
+        <v>20.92805290222168</v>
       </c>
       <c r="C704" t="n">
-        <v>21.08547462588529</v>
+        <v>21.08547270418967</v>
       </c>
       <c r="D704" t="n">
-        <v>19.16145724348956</v>
+        <v>19.16145549714573</v>
       </c>
       <c r="E704" t="n">
-        <v>19.29263986772618</v>
+        <v>19.29263810942659</v>
       </c>
       <c r="F704" t="n">
         <v>1764300</v>
@@ -14512,16 +14512,16 @@
         <v>44608</v>
       </c>
       <c r="B705" t="n">
-        <v>20.63070487976074</v>
+        <v>20.63070678710938</v>
       </c>
       <c r="C705" t="n">
-        <v>21.14669127010925</v>
+        <v>21.14669322516183</v>
       </c>
       <c r="D705" t="n">
-        <v>20.13220994930683</v>
+        <v>20.13221181056864</v>
       </c>
       <c r="E705" t="n">
-        <v>21.05048990876642</v>
+        <v>21.05049185492499</v>
       </c>
       <c r="F705" t="n">
         <v>863200</v>
@@ -14532,16 +14532,16 @@
         <v>44609</v>
       </c>
       <c r="B706" t="n">
-        <v>19.78239059448242</v>
+        <v>19.78238868713379</v>
       </c>
       <c r="C706" t="n">
-        <v>20.91930888475303</v>
+        <v>20.91930686778672</v>
       </c>
       <c r="D706" t="n">
-        <v>19.78239059448242</v>
+        <v>19.78238868713379</v>
       </c>
       <c r="E706" t="n">
-        <v>20.38583099398668</v>
+        <v>20.38582902845644</v>
       </c>
       <c r="F706" t="n">
         <v>844900</v>
@@ -14572,16 +14572,16 @@
         <v>44613</v>
       </c>
       <c r="B708" t="n">
-        <v>18.92532539367676</v>
+        <v>18.92532920837402</v>
       </c>
       <c r="C708" t="n">
-        <v>19.6686957383062</v>
+        <v>19.66869970284147</v>
       </c>
       <c r="D708" t="n">
-        <v>18.71543288485386</v>
+        <v>18.71543665724399</v>
       </c>
       <c r="E708" t="n">
-        <v>19.31887489026805</v>
+        <v>19.31887878429141</v>
       </c>
       <c r="F708" t="n">
         <v>1006600</v>
@@ -14632,16 +14632,16 @@
         <v>44616</v>
       </c>
       <c r="B711" t="n">
-        <v>20.42081451416016</v>
+        <v>20.42081260681152</v>
       </c>
       <c r="C711" t="n">
-        <v>20.61321558901495</v>
+        <v>20.61321366369564</v>
       </c>
       <c r="D711" t="n">
-        <v>19.02152926881567</v>
+        <v>19.02152749216333</v>
       </c>
       <c r="E711" t="n">
-        <v>19.85235535238579</v>
+        <v>19.85235349813248</v>
       </c>
       <c r="F711" t="n">
         <v>1354200</v>
@@ -14792,16 +14792,16 @@
         <v>44630</v>
       </c>
       <c r="B719" t="n">
-        <v>17.70095252990723</v>
+        <v>17.70095062255859</v>
       </c>
       <c r="C719" t="n">
-        <v>18.61048845110218</v>
+        <v>18.6104864457474</v>
       </c>
       <c r="D719" t="n">
-        <v>17.51729720047986</v>
+        <v>17.51729531292083</v>
       </c>
       <c r="E719" t="n">
-        <v>18.61048845110218</v>
+        <v>18.6104864457474</v>
       </c>
       <c r="F719" t="n">
         <v>1059400</v>
@@ -14812,16 +14812,16 @@
         <v>44631</v>
       </c>
       <c r="B720" t="n">
-        <v>16.49407196044922</v>
+        <v>16.49407005310059</v>
       </c>
       <c r="C720" t="n">
-        <v>17.99830268835392</v>
+        <v>17.9983006070584</v>
       </c>
       <c r="D720" t="n">
-        <v>16.2054695048606</v>
+        <v>16.2054676308855</v>
       </c>
       <c r="E720" t="n">
-        <v>17.99830268835392</v>
+        <v>17.9983006070584</v>
       </c>
       <c r="F720" t="n">
         <v>1712100</v>
@@ -14832,16 +14832,16 @@
         <v>44634</v>
       </c>
       <c r="B721" t="n">
-        <v>16.52030563354492</v>
+        <v>16.52030372619629</v>
       </c>
       <c r="C721" t="n">
-        <v>16.66897971024399</v>
+        <v>16.66897778573022</v>
       </c>
       <c r="D721" t="n">
-        <v>15.98682943792383</v>
+        <v>15.98682759216759</v>
       </c>
       <c r="E721" t="n">
-        <v>16.60776126714628</v>
+        <v>16.60775934970047</v>
       </c>
       <c r="F721" t="n">
         <v>1266200</v>
@@ -14852,16 +14852,16 @@
         <v>44635</v>
       </c>
       <c r="B722" t="n">
-        <v>16.4765796661377</v>
+        <v>16.47657775878906</v>
       </c>
       <c r="C722" t="n">
-        <v>16.66898073745525</v>
+        <v>16.66897880783404</v>
       </c>
       <c r="D722" t="n">
-        <v>15.87313759198696</v>
+        <v>15.8731357544935</v>
       </c>
       <c r="E722" t="n">
-        <v>16.4503424740172</v>
+        <v>16.45034056970582</v>
       </c>
       <c r="F722" t="n">
         <v>1881800</v>
@@ -14892,16 +14892,16 @@
         <v>44637</v>
       </c>
       <c r="B724" t="n">
-        <v>17.46482467651367</v>
+        <v>17.46482276916504</v>
       </c>
       <c r="C724" t="n">
-        <v>17.4735704076179</v>
+        <v>17.47356849931414</v>
       </c>
       <c r="D724" t="n">
-        <v>16.48532614592688</v>
+        <v>16.48532434555013</v>
       </c>
       <c r="E724" t="n">
-        <v>16.53779886447462</v>
+        <v>16.53779705836727</v>
       </c>
       <c r="F724" t="n">
         <v>1189900</v>
@@ -14912,16 +14912,16 @@
         <v>44638</v>
       </c>
       <c r="B725" t="n">
-        <v>18.00704574584961</v>
+        <v>18.00704765319824</v>
       </c>
       <c r="C725" t="n">
-        <v>18.21693825801528</v>
+        <v>18.21694018759622</v>
       </c>
       <c r="D725" t="n">
-        <v>17.14123850763719</v>
+        <v>17.14124032327748</v>
       </c>
       <c r="E725" t="n">
-        <v>17.46482217169691</v>
+        <v>17.46482402161194</v>
       </c>
       <c r="F725" t="n">
         <v>1389200</v>
@@ -14932,16 +14932,16 @@
         <v>44641</v>
       </c>
       <c r="B726" t="n">
-        <v>17.95457458496094</v>
+        <v>17.9545726776123</v>
       </c>
       <c r="C726" t="n">
-        <v>18.26066681574773</v>
+        <v>18.26066487588234</v>
       </c>
       <c r="D726" t="n">
-        <v>17.46482367954697</v>
+        <v>17.4648218242255</v>
       </c>
       <c r="E726" t="n">
-        <v>17.91959166254099</v>
+        <v>17.91958975890866</v>
       </c>
       <c r="F726" t="n">
         <v>801400</v>
@@ -15012,16 +15012,16 @@
         <v>44645</v>
       </c>
       <c r="B730" t="n">
-        <v>21.31285858154297</v>
+        <v>21.31285667419434</v>
       </c>
       <c r="C730" t="n">
-        <v>21.8026078229199</v>
+        <v>21.8026058717422</v>
       </c>
       <c r="D730" t="n">
-        <v>19.86984471328848</v>
+        <v>19.86984293507929</v>
       </c>
       <c r="E730" t="n">
-        <v>19.86984471328848</v>
+        <v>19.86984293507929</v>
       </c>
       <c r="F730" t="n">
         <v>2456800</v>
@@ -15092,16 +15092,16 @@
         <v>44651</v>
       </c>
       <c r="B734" t="n">
-        <v>22.12619018554688</v>
+        <v>22.12618827819824</v>
       </c>
       <c r="C734" t="n">
-        <v>22.26611853180204</v>
+        <v>22.26611661239113</v>
       </c>
       <c r="D734" t="n">
-        <v>21.50525835754926</v>
+        <v>21.50525650372695</v>
       </c>
       <c r="E734" t="n">
-        <v>21.93378912646539</v>
+        <v>21.93378723570235</v>
       </c>
       <c r="F734" t="n">
         <v>1166300</v>
@@ -15112,16 +15112,16 @@
         <v>44652</v>
       </c>
       <c r="B735" t="n">
-        <v>23.50798225402832</v>
+        <v>23.50798416137695</v>
       </c>
       <c r="C735" t="n">
-        <v>23.62167507016197</v>
+        <v>23.62167698673521</v>
       </c>
       <c r="D735" t="n">
-        <v>22.02124325935501</v>
+        <v>22.02124504607528</v>
       </c>
       <c r="E735" t="n">
-        <v>22.35357264204656</v>
+        <v>22.35357445573077</v>
       </c>
       <c r="F735" t="n">
         <v>2217800</v>
@@ -15132,16 +15132,16 @@
         <v>44655</v>
       </c>
       <c r="B736" t="n">
-        <v>23.38554763793945</v>
+        <v>23.38554573059082</v>
       </c>
       <c r="C736" t="n">
-        <v>24.38253755050633</v>
+        <v>24.3825355618422</v>
       </c>
       <c r="D736" t="n">
-        <v>22.93952539598124</v>
+        <v>22.93952352501063</v>
       </c>
       <c r="E736" t="n">
-        <v>23.49924046506788</v>
+        <v>23.49923854844634</v>
       </c>
       <c r="F736" t="n">
         <v>2090400</v>
@@ -15172,16 +15172,16 @@
         <v>44657</v>
       </c>
       <c r="B738" t="n">
-        <v>22.47601318359375</v>
+        <v>22.47601127624512</v>
       </c>
       <c r="C738" t="n">
-        <v>22.57221288108315</v>
+        <v>22.57221096557086</v>
       </c>
       <c r="D738" t="n">
-        <v>21.6364414206406</v>
+        <v>21.6364395845393</v>
       </c>
       <c r="E738" t="n">
-        <v>22.4235388016059</v>
+        <v>22.42353689871032</v>
       </c>
       <c r="F738" t="n">
         <v>1740900</v>
@@ -15192,16 +15192,16 @@
         <v>44658</v>
       </c>
       <c r="B739" t="n">
-        <v>23.26311111450195</v>
+        <v>23.26310920715332</v>
       </c>
       <c r="C739" t="n">
-        <v>23.62167772617468</v>
+        <v>23.62167578942707</v>
       </c>
       <c r="D739" t="n">
-        <v>22.2398839946346</v>
+        <v>22.23988217118062</v>
       </c>
       <c r="E739" t="n">
-        <v>22.45852225385346</v>
+        <v>22.45852041247328</v>
       </c>
       <c r="F739" t="n">
         <v>1772800</v>
@@ -15212,16 +15212,16 @@
         <v>44659</v>
       </c>
       <c r="B740" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C740" t="n">
-        <v>23.28934418253186</v>
+        <v>23.28934612340661</v>
       </c>
       <c r="D740" t="n">
-        <v>22.3535727986304</v>
+        <v>22.35357466152034</v>
       </c>
       <c r="E740" t="n">
-        <v>23.08819740559698</v>
+        <v>23.08819932970868</v>
       </c>
       <c r="F740" t="n">
         <v>1404400</v>
@@ -15252,16 +15252,16 @@
         <v>44663</v>
       </c>
       <c r="B742" t="n">
-        <v>22.91328811645508</v>
+        <v>22.91329002380371</v>
       </c>
       <c r="C742" t="n">
-        <v>23.14941614685713</v>
+        <v>23.14941807386153</v>
       </c>
       <c r="D742" t="n">
-        <v>22.44102871949622</v>
+        <v>22.44103058753301</v>
       </c>
       <c r="E742" t="n">
-        <v>22.79084956831164</v>
+        <v>22.79085146546824</v>
       </c>
       <c r="F742" t="n">
         <v>1246700</v>
@@ -15272,16 +15272,16 @@
         <v>44664</v>
       </c>
       <c r="B743" t="n">
-        <v>22.91328811645508</v>
+        <v>22.91329002380371</v>
       </c>
       <c r="C743" t="n">
-        <v>23.31558167557347</v>
+        <v>23.31558361640984</v>
       </c>
       <c r="D743" t="n">
-        <v>22.7995952980417</v>
+        <v>22.79959719592631</v>
       </c>
       <c r="E743" t="n">
-        <v>23.0881977068241</v>
+        <v>23.08819962873256</v>
       </c>
       <c r="F743" t="n">
         <v>777300</v>
@@ -15292,16 +15292,16 @@
         <v>44665</v>
       </c>
       <c r="B744" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C744" t="n">
-        <v>23.29808991214781</v>
+        <v>23.29809185375142</v>
       </c>
       <c r="D744" t="n">
-        <v>22.51973832517882</v>
+        <v>22.51974020191658</v>
       </c>
       <c r="E744" t="n">
-        <v>22.78210354134801</v>
+        <v>22.78210543995062</v>
       </c>
       <c r="F744" t="n">
         <v>1181000</v>
@@ -15332,16 +15332,16 @@
         <v>44670</v>
       </c>
       <c r="B746" t="n">
-        <v>22.83458137512207</v>
+        <v>22.83457946777344</v>
       </c>
       <c r="C746" t="n">
-        <v>23.07070943818205</v>
+        <v>23.07070751110989</v>
       </c>
       <c r="D746" t="n">
-        <v>22.48475880984669</v>
+        <v>22.48475693171837</v>
       </c>
       <c r="E746" t="n">
-        <v>22.95701827212188</v>
+        <v>22.95701635454622</v>
       </c>
       <c r="F746" t="n">
         <v>1086700</v>
@@ -15352,16 +15352,16 @@
         <v>44671</v>
       </c>
       <c r="B747" t="n">
-        <v>22.39730453491211</v>
+        <v>22.39730072021484</v>
       </c>
       <c r="C747" t="n">
-        <v>23.29809312455296</v>
+        <v>23.29808915643385</v>
       </c>
       <c r="D747" t="n">
-        <v>22.18741199942072</v>
+        <v>22.18740822047224</v>
       </c>
       <c r="E747" t="n">
-        <v>22.83458106753857</v>
+        <v>22.83457717836459</v>
       </c>
       <c r="F747" t="n">
         <v>1171700</v>
@@ -15392,16 +15392,16 @@
         <v>44676</v>
       </c>
       <c r="B749" t="n">
-        <v>22.02124404907227</v>
+        <v>22.0212459564209</v>
       </c>
       <c r="C749" t="n">
-        <v>22.03873550880892</v>
+        <v>22.03873741767256</v>
       </c>
       <c r="D749" t="n">
-        <v>21.10296242982674</v>
+        <v>21.1029642576393</v>
       </c>
       <c r="E749" t="n">
-        <v>21.24289243964258</v>
+        <v>21.24289427957504</v>
       </c>
       <c r="F749" t="n">
         <v>807800</v>
@@ -15412,16 +15412,16 @@
         <v>44677</v>
       </c>
       <c r="B750" t="n">
-        <v>21.29536437988281</v>
+        <v>21.29536628723145</v>
       </c>
       <c r="C750" t="n">
-        <v>22.39730128224088</v>
+        <v>22.397303288286</v>
       </c>
       <c r="D750" t="n">
-        <v>21.03299749756288</v>
+        <v>21.03299938141226</v>
       </c>
       <c r="E750" t="n">
-        <v>21.93378762446315</v>
+        <v>21.93378958899304</v>
       </c>
       <c r="F750" t="n">
         <v>740500</v>
@@ -15472,16 +15472,16 @@
         <v>44680</v>
       </c>
       <c r="B753" t="n">
-        <v>21.10296440124512</v>
+        <v>21.10296249389648</v>
       </c>
       <c r="C753" t="n">
-        <v>21.9075532754437</v>
+        <v>21.90755129537393</v>
       </c>
       <c r="D753" t="n">
-        <v>20.79687216764585</v>
+        <v>20.79687028796274</v>
       </c>
       <c r="E753" t="n">
-        <v>21.7676249206333</v>
+        <v>21.76762295321067</v>
       </c>
       <c r="F753" t="n">
         <v>1100200</v>
@@ -15512,16 +15512,16 @@
         <v>44684</v>
       </c>
       <c r="B755" t="n">
-        <v>20.21343803405762</v>
+        <v>20.21343994140625</v>
       </c>
       <c r="C755" t="n">
-        <v>20.60891901392524</v>
+        <v>20.60892095859163</v>
       </c>
       <c r="D755" t="n">
-        <v>19.67734196718463</v>
+        <v>19.67734382394701</v>
       </c>
       <c r="E755" t="n">
-        <v>20.45072662197819</v>
+        <v>20.45072855171748</v>
       </c>
       <c r="F755" t="n">
         <v>1194800</v>
@@ -15832,16 +15832,16 @@
         <v>44706</v>
       </c>
       <c r="B771" t="n">
-        <v>20.43315124511719</v>
+        <v>20.43314933776855</v>
       </c>
       <c r="C771" t="n">
-        <v>20.53861340845469</v>
+        <v>20.53861149126161</v>
       </c>
       <c r="D771" t="n">
-        <v>19.56309468357358</v>
+        <v>19.56309285744106</v>
       </c>
       <c r="E771" t="n">
-        <v>20.4155739385169</v>
+        <v>20.41557203280903</v>
       </c>
       <c r="F771" t="n">
         <v>1204100</v>
@@ -15852,16 +15852,16 @@
         <v>44707</v>
       </c>
       <c r="B772" t="n">
-        <v>20.67043876647949</v>
+        <v>20.67044067382812</v>
       </c>
       <c r="C772" t="n">
-        <v>21.1010726979148</v>
+        <v>21.10107464499984</v>
       </c>
       <c r="D772" t="n">
-        <v>20.12555402442544</v>
+        <v>20.12555588149525</v>
       </c>
       <c r="E772" t="n">
-        <v>20.38041992791024</v>
+        <v>20.38042180849761</v>
       </c>
       <c r="F772" t="n">
         <v>1009800</v>
@@ -15872,16 +15872,16 @@
         <v>44708</v>
       </c>
       <c r="B773" t="n">
-        <v>21.37351226806641</v>
+        <v>21.37351417541504</v>
       </c>
       <c r="C773" t="n">
-        <v>21.37351226806641</v>
+        <v>21.37351417541504</v>
       </c>
       <c r="D773" t="n">
-        <v>20.45072559634</v>
+        <v>20.45072742134017</v>
       </c>
       <c r="E773" t="n">
-        <v>20.64407091220977</v>
+        <v>20.64407275446386</v>
       </c>
       <c r="F773" t="n">
         <v>733300</v>
@@ -15972,16 +15972,16 @@
         <v>44715</v>
       </c>
       <c r="B778" t="n">
-        <v>21.97112846374512</v>
+        <v>21.97113037109375</v>
       </c>
       <c r="C778" t="n">
-        <v>22.26114729241599</v>
+        <v>22.26114922494162</v>
       </c>
       <c r="D778" t="n">
-        <v>21.76020583164485</v>
+        <v>21.76020772068296</v>
       </c>
       <c r="E778" t="n">
-        <v>22.26114729241599</v>
+        <v>22.26114922494162</v>
       </c>
       <c r="F778" t="n">
         <v>447800</v>
@@ -16072,16 +16072,16 @@
         <v>44722</v>
       </c>
       <c r="B783" t="n">
-        <v>19.94099807739258</v>
+        <v>19.94099617004395</v>
       </c>
       <c r="C783" t="n">
-        <v>20.48588116323218</v>
+        <v>20.4858792037657</v>
       </c>
       <c r="D783" t="n">
-        <v>19.55430571965002</v>
+        <v>19.55430384928836</v>
       </c>
       <c r="E783" t="n">
-        <v>20.33647741203148</v>
+        <v>20.3364754668554</v>
       </c>
       <c r="F783" t="n">
         <v>1031200</v>
@@ -16252,16 +16252,16 @@
         <v>44736</v>
       </c>
       <c r="B792" t="n">
-        <v>17.40991973876953</v>
+        <v>17.40992164611816</v>
       </c>
       <c r="C792" t="n">
-        <v>18.17451565962031</v>
+        <v>18.17451765073446</v>
       </c>
       <c r="D792" t="n">
-        <v>17.21657443380519</v>
+        <v>17.21657631997182</v>
       </c>
       <c r="E792" t="n">
-        <v>17.98995732992644</v>
+        <v>17.98995930082126</v>
       </c>
       <c r="F792" t="n">
         <v>1906300</v>
@@ -16332,16 +16332,16 @@
         <v>44742</v>
       </c>
       <c r="B796" t="n">
-        <v>16.63653755187988</v>
+        <v>16.63653945922852</v>
       </c>
       <c r="C796" t="n">
-        <v>17.06717143783872</v>
+        <v>17.06717339455875</v>
       </c>
       <c r="D796" t="n">
-        <v>16.39924897912788</v>
+        <v>16.39925085927182</v>
       </c>
       <c r="E796" t="n">
-        <v>16.56623001287158</v>
+        <v>16.56623191215958</v>
       </c>
       <c r="F796" t="n">
         <v>1355100</v>
@@ -16412,16 +16412,16 @@
         <v>44748</v>
       </c>
       <c r="B800" t="n">
-        <v>16.96171188354492</v>
+        <v>16.96170997619629</v>
       </c>
       <c r="C800" t="n">
-        <v>17.11990428955699</v>
+        <v>17.11990236441959</v>
       </c>
       <c r="D800" t="n">
-        <v>16.32015528250859</v>
+        <v>16.32015344730316</v>
       </c>
       <c r="E800" t="n">
-        <v>16.32894393576084</v>
+        <v>16.32894209956712</v>
       </c>
       <c r="F800" t="n">
         <v>1247700</v>
@@ -16532,16 +16532,16 @@
         <v>44756</v>
       </c>
       <c r="B806" t="n">
-        <v>16.81230735778809</v>
+        <v>16.81230926513672</v>
       </c>
       <c r="C806" t="n">
-        <v>17.31325051254866</v>
+        <v>17.31325247672907</v>
       </c>
       <c r="D806" t="n">
-        <v>16.81230735778809</v>
+        <v>16.81230926513672</v>
       </c>
       <c r="E806" t="n">
-        <v>17.13748080811364</v>
+        <v>17.13748275235305</v>
       </c>
       <c r="F806" t="n">
         <v>1103500</v>
@@ -16552,16 +16552,16 @@
         <v>44757</v>
       </c>
       <c r="B807" t="n">
-        <v>16.52228736877441</v>
+        <v>16.52228927612305</v>
       </c>
       <c r="C807" t="n">
-        <v>17.09353803029265</v>
+        <v>17.09354000358701</v>
       </c>
       <c r="D807" t="n">
-        <v>16.28500046344753</v>
+        <v>16.28500234340354</v>
       </c>
       <c r="E807" t="n">
-        <v>17.07596072581984</v>
+        <v>17.07596269708505</v>
       </c>
       <c r="F807" t="n">
         <v>1251500</v>
@@ -16572,16 +16572,16 @@
         <v>44760</v>
       </c>
       <c r="B808" t="n">
-        <v>15.86315536499023</v>
+        <v>15.8631534576416</v>
       </c>
       <c r="C808" t="n">
-        <v>17.08475134636454</v>
+        <v>17.08474929213407</v>
       </c>
       <c r="D808" t="n">
-        <v>15.86315536499023</v>
+        <v>15.8631534576416</v>
       </c>
       <c r="E808" t="n">
-        <v>16.68927033148361</v>
+        <v>16.68926832480485</v>
       </c>
       <c r="F808" t="n">
         <v>925600</v>
@@ -16612,16 +16612,16 @@
         <v>44762</v>
       </c>
       <c r="B810" t="n">
-        <v>16.98807716369629</v>
+        <v>16.98807525634766</v>
       </c>
       <c r="C810" t="n">
-        <v>17.1814224987184</v>
+        <v>17.18142056966178</v>
       </c>
       <c r="D810" t="n">
-        <v>15.95103958911631</v>
+        <v>15.95103779820182</v>
       </c>
       <c r="E810" t="n">
-        <v>15.95103958911631</v>
+        <v>15.95103779820182</v>
       </c>
       <c r="F810" t="n">
         <v>1160100</v>
@@ -17412,16 +17412,16 @@
         <v>44819</v>
       </c>
       <c r="B850" t="n">
-        <v>19.5455150604248</v>
+        <v>19.54551696777344</v>
       </c>
       <c r="C850" t="n">
-        <v>20.03766785305302</v>
+        <v>20.03766980842837</v>
       </c>
       <c r="D850" t="n">
-        <v>19.22913028417465</v>
+        <v>19.22913216064889</v>
       </c>
       <c r="E850" t="n">
-        <v>19.89705276944496</v>
+        <v>19.89705471109839</v>
       </c>
       <c r="F850" t="n">
         <v>1477600</v>
@@ -17432,16 +17432,16 @@
         <v>44820</v>
       </c>
       <c r="B851" t="n">
-        <v>19.56309509277344</v>
+        <v>19.5630931854248</v>
       </c>
       <c r="C851" t="n">
-        <v>19.56309509277344</v>
+        <v>19.5630931854248</v>
       </c>
       <c r="D851" t="n">
-        <v>18.71061581999887</v>
+        <v>18.71061399576465</v>
       </c>
       <c r="E851" t="n">
-        <v>19.41369133607436</v>
+        <v>19.41368944329219</v>
       </c>
       <c r="F851" t="n">
         <v>1313300</v>
@@ -17532,16 +17532,16 @@
         <v>44827</v>
       </c>
       <c r="B856" t="n">
-        <v>20.15192222595215</v>
+        <v>20.15192031860352</v>
       </c>
       <c r="C856" t="n">
-        <v>20.61770914431645</v>
+        <v>20.61770719288179</v>
       </c>
       <c r="D856" t="n">
-        <v>19.95857519454268</v>
+        <v>19.95857330549405</v>
       </c>
       <c r="E856" t="n">
-        <v>20.48588268961456</v>
+        <v>20.48588075065707</v>
       </c>
       <c r="F856" t="n">
         <v>1009700</v>
@@ -17572,16 +17572,16 @@
         <v>44831</v>
       </c>
       <c r="B858" t="n">
-        <v>18.37664985656738</v>
+        <v>18.37665176391602</v>
       </c>
       <c r="C858" t="n">
-        <v>19.28186086128439</v>
+        <v>19.28186286258666</v>
       </c>
       <c r="D858" t="n">
-        <v>18.35028390161931</v>
+        <v>18.35028580623137</v>
       </c>
       <c r="E858" t="n">
-        <v>19.21155332435344</v>
+        <v>19.21155531835834</v>
       </c>
       <c r="F858" t="n">
         <v>1438200</v>
@@ -17592,16 +17592,16 @@
         <v>44832</v>
       </c>
       <c r="B859" t="n">
-        <v>18.20088386535645</v>
+        <v>18.20088195800781</v>
       </c>
       <c r="C859" t="n">
-        <v>18.55242329753082</v>
+        <v>18.55242135334287</v>
       </c>
       <c r="D859" t="n">
-        <v>17.66478941619259</v>
+        <v>17.66478756502359</v>
       </c>
       <c r="E859" t="n">
-        <v>18.27998006996926</v>
+        <v>18.27997815433179</v>
       </c>
       <c r="F859" t="n">
         <v>1384700</v>
@@ -17732,16 +17732,16 @@
         <v>44841</v>
       </c>
       <c r="B866" t="n">
-        <v>17.47144317626953</v>
+        <v>17.4714412689209</v>
       </c>
       <c r="C866" t="n">
-        <v>18.50848085988</v>
+        <v>18.50847883931848</v>
       </c>
       <c r="D866" t="n">
-        <v>17.41871292958584</v>
+        <v>17.41871102799374</v>
       </c>
       <c r="E866" t="n">
-        <v>18.44696195937163</v>
+        <v>18.44695994552611</v>
       </c>
       <c r="F866" t="n">
         <v>1871900</v>
@@ -17812,16 +17812,16 @@
         <v>44848</v>
       </c>
       <c r="B870" t="n">
-        <v>16.63653755187988</v>
+        <v>16.63653945922852</v>
       </c>
       <c r="C870" t="n">
-        <v>17.56811286280587</v>
+        <v>17.56811487695791</v>
       </c>
       <c r="D870" t="n">
-        <v>16.52228675332642</v>
+        <v>16.52228864757641</v>
       </c>
       <c r="E870" t="n">
-        <v>17.4099204809712</v>
+        <v>17.40992247698677</v>
       </c>
       <c r="F870" t="n">
         <v>1935700</v>
@@ -17852,16 +17852,16 @@
         <v>44852</v>
       </c>
       <c r="B872" t="n">
-        <v>16.49592399597168</v>
+        <v>16.49592590332031</v>
       </c>
       <c r="C872" t="n">
-        <v>17.09353897081722</v>
+        <v>17.09354094726535</v>
       </c>
       <c r="D872" t="n">
-        <v>16.39046183959607</v>
+        <v>16.39046373475059</v>
       </c>
       <c r="E872" t="n">
-        <v>16.90019196350595</v>
+        <v>16.90019391759825</v>
       </c>
       <c r="F872" t="n">
         <v>864000</v>
@@ -17872,16 +17872,16 @@
         <v>44853</v>
       </c>
       <c r="B873" t="n">
-        <v>16.10923194885254</v>
+        <v>16.10923385620117</v>
       </c>
       <c r="C873" t="n">
-        <v>16.53107722945332</v>
+        <v>16.53107918674884</v>
       </c>
       <c r="D873" t="n">
-        <v>15.90709796143102</v>
+        <v>15.90709984484679</v>
       </c>
       <c r="E873" t="n">
-        <v>16.43440540031406</v>
+        <v>16.43440734616354</v>
       </c>
       <c r="F873" t="n">
         <v>1513900</v>
@@ -17932,16 +17932,16 @@
         <v>44858</v>
       </c>
       <c r="B876" t="n">
-        <v>15.59071350097656</v>
+        <v>15.59071254730225</v>
       </c>
       <c r="C876" t="n">
-        <v>15.91588695949038</v>
+        <v>15.9158859859254</v>
       </c>
       <c r="D876" t="n">
-        <v>15.30948330781011</v>
+        <v>15.30948237133847</v>
       </c>
       <c r="E876" t="n">
-        <v>15.59950215404604</v>
+        <v>15.59950119983412</v>
       </c>
       <c r="F876" t="n">
         <v>2881700</v>
@@ -17952,16 +17952,16 @@
         <v>44859</v>
       </c>
       <c r="B877" t="n">
-        <v>16.10923194885254</v>
+        <v>16.10923385620117</v>
       </c>
       <c r="C877" t="n">
-        <v>16.45198102980765</v>
+        <v>16.45198297773811</v>
       </c>
       <c r="D877" t="n">
-        <v>15.42373211067817</v>
+        <v>15.42373393686296</v>
       </c>
       <c r="E877" t="n">
-        <v>15.50282831032383</v>
+        <v>15.50283014587369</v>
       </c>
       <c r="F877" t="n">
         <v>2142700</v>
@@ -17972,16 +17972,16 @@
         <v>44860</v>
       </c>
       <c r="B878" t="n">
-        <v>15.21281051635742</v>
+        <v>15.21280956268311</v>
       </c>
       <c r="C878" t="n">
-        <v>16.0652914653156</v>
+        <v>16.06529045820019</v>
       </c>
       <c r="D878" t="n">
-        <v>15.11613868057135</v>
+        <v>15.11613773295728</v>
       </c>
       <c r="E878" t="n">
-        <v>15.96861795326526</v>
+        <v>15.96861695221021</v>
       </c>
       <c r="F878" t="n">
         <v>1638200</v>
@@ -17992,16 +17992,16 @@
         <v>44861</v>
       </c>
       <c r="B879" t="n">
-        <v>15.77527236938477</v>
+        <v>15.77527046203613</v>
       </c>
       <c r="C879" t="n">
-        <v>16.11802146877758</v>
+        <v>16.11801951998802</v>
       </c>
       <c r="D879" t="n">
-        <v>15.14250273818051</v>
+        <v>15.14250090733847</v>
       </c>
       <c r="E879" t="n">
-        <v>15.2567535554876</v>
+        <v>15.25675171083178</v>
       </c>
       <c r="F879" t="n">
         <v>2067700</v>
@@ -18172,16 +18172,16 @@
         <v>44875</v>
       </c>
       <c r="B888" t="n">
-        <v>14.79975318908691</v>
+        <v>14.7997522354126</v>
       </c>
       <c r="C888" t="n">
-        <v>16.21469448668665</v>
+        <v>16.2146934418356</v>
       </c>
       <c r="D888" t="n">
-        <v>14.59761919693386</v>
+        <v>14.59761825628476</v>
       </c>
       <c r="E888" t="n">
-        <v>16.21469448668665</v>
+        <v>16.2146934418356</v>
       </c>
       <c r="F888" t="n">
         <v>2325200</v>
@@ -18212,16 +18212,16 @@
         <v>44879</v>
       </c>
       <c r="B890" t="n">
-        <v>14.56246471405029</v>
+        <v>14.56246376037598</v>
       </c>
       <c r="C890" t="n">
-        <v>14.94036841872623</v>
+        <v>14.94036744030356</v>
       </c>
       <c r="D890" t="n">
-        <v>14.12304211349952</v>
+        <v>14.12304118860234</v>
       </c>
       <c r="E890" t="n">
-        <v>14.32517610744947</v>
+        <v>14.32517516931483</v>
       </c>
       <c r="F890" t="n">
         <v>1798400</v>
@@ -18232,16 +18232,16 @@
         <v>44881</v>
       </c>
       <c r="B891" t="n">
-        <v>13.55179214477539</v>
+        <v>13.55179309844971</v>
       </c>
       <c r="C891" t="n">
-        <v>14.57125237449792</v>
+        <v>14.57125339991427</v>
       </c>
       <c r="D891" t="n">
-        <v>13.40238840371619</v>
+        <v>13.40238934687658</v>
       </c>
       <c r="E891" t="n">
-        <v>14.56246372193396</v>
+        <v>14.56246474673182</v>
       </c>
       <c r="F891" t="n">
         <v>2598100</v>
@@ -18352,16 +18352,16 @@
         <v>44889</v>
       </c>
       <c r="B897" t="n">
-        <v>13.58694648742676</v>
+        <v>13.58694744110107</v>
       </c>
       <c r="C897" t="n">
-        <v>13.92090775569229</v>
+        <v>13.92090873280751</v>
       </c>
       <c r="D897" t="n">
-        <v>13.27056252502723</v>
+        <v>13.27056345649441</v>
       </c>
       <c r="E897" t="n">
-        <v>13.28813899276117</v>
+        <v>13.28813992546204</v>
       </c>
       <c r="F897" t="n">
         <v>1494400</v>
@@ -18392,16 +18392,16 @@
         <v>44893</v>
       </c>
       <c r="B899" t="n">
-        <v>12.83113956451416</v>
+        <v>12.83114051818848</v>
       </c>
       <c r="C899" t="n">
-        <v>13.45511965644873</v>
+        <v>13.45512065650036</v>
       </c>
       <c r="D899" t="n">
-        <v>12.78719713925329</v>
+        <v>12.78719808966159</v>
       </c>
       <c r="E899" t="n">
-        <v>13.24419618282298</v>
+        <v>13.24419716719772</v>
       </c>
       <c r="F899" t="n">
         <v>874000</v>
@@ -18452,16 +18452,16 @@
         <v>44896</v>
       </c>
       <c r="B902" t="n">
-        <v>12.48838901519775</v>
+        <v>12.48838996887207</v>
       </c>
       <c r="C902" t="n">
-        <v>12.77840783371735</v>
+        <v>12.77840880953892</v>
       </c>
       <c r="D902" t="n">
-        <v>12.15442777366234</v>
+        <v>12.15442870183375</v>
       </c>
       <c r="E902" t="n">
-        <v>12.77840783371735</v>
+        <v>12.77840880953892</v>
       </c>
       <c r="F902" t="n">
         <v>3444900</v>
@@ -18532,16 +18532,16 @@
         <v>44902</v>
       </c>
       <c r="B906" t="n">
-        <v>11.34589099884033</v>
+        <v>11.34589004516602</v>
       </c>
       <c r="C906" t="n">
-        <v>11.94350598202324</v>
+        <v>11.94350497811664</v>
       </c>
       <c r="D906" t="n">
-        <v>11.34589099884033</v>
+        <v>11.34589004516602</v>
       </c>
       <c r="E906" t="n">
-        <v>11.62712118474661</v>
+        <v>11.62712020743361</v>
       </c>
       <c r="F906" t="n">
         <v>4257100</v>
@@ -18832,16 +18832,16 @@
         <v>44923</v>
       </c>
       <c r="B921" t="n">
-        <v>11.22285270690918</v>
+        <v>11.2228536605835</v>
       </c>
       <c r="C921" t="n">
-        <v>11.53044799937938</v>
+        <v>11.53044897919194</v>
       </c>
       <c r="D921" t="n">
-        <v>10.97677546717459</v>
+        <v>10.97677639993822</v>
       </c>
       <c r="E921" t="n">
-        <v>11.12617920625201</v>
+        <v>11.12618015171139</v>
       </c>
       <c r="F921" t="n">
         <v>1106200</v>
@@ -18852,16 +18852,16 @@
         <v>44924</v>
       </c>
       <c r="B922" t="n">
-        <v>11.23164176940918</v>
+        <v>11.23164081573486</v>
       </c>
       <c r="C922" t="n">
-        <v>11.61833413874736</v>
+        <v>11.61833315223914</v>
       </c>
       <c r="D922" t="n">
-        <v>10.83616158477905</v>
+        <v>10.8361606646848</v>
       </c>
       <c r="E922" t="n">
-        <v>11.25800772968141</v>
+        <v>11.25800677376837</v>
       </c>
       <c r="F922" t="n">
         <v>1066700</v>
@@ -18892,16 +18892,16 @@
         <v>44929</v>
       </c>
       <c r="B924" t="n">
-        <v>9.957315444946289</v>
+        <v>9.957316398620605</v>
       </c>
       <c r="C924" t="n">
-        <v>10.59008418524001</v>
+        <v>10.59008519951854</v>
       </c>
       <c r="D924" t="n">
-        <v>9.922161672603973</v>
+        <v>9.922162622911394</v>
       </c>
       <c r="E924" t="n">
-        <v>10.44946909587075</v>
+        <v>10.44947009668169</v>
       </c>
       <c r="F924" t="n">
         <v>920100</v>
@@ -19032,16 +19032,16 @@
         <v>44938</v>
       </c>
       <c r="B931" t="n">
-        <v>9.667296409606934</v>
+        <v>9.66729736328125</v>
       </c>
       <c r="C931" t="n">
-        <v>10.12429627854627</v>
+        <v>10.12429727730341</v>
       </c>
       <c r="D931" t="n">
-        <v>9.412431355969849</v>
+        <v>9.412432284501847</v>
       </c>
       <c r="E931" t="n">
-        <v>10.06277654964627</v>
+        <v>10.06277754233452</v>
       </c>
       <c r="F931" t="n">
         <v>3972100</v>
@@ -19052,16 +19052,16 @@
         <v>44939</v>
       </c>
       <c r="B932" t="n">
-        <v>9.614564895629883</v>
+        <v>9.614565849304199</v>
       </c>
       <c r="C932" t="n">
-        <v>9.834276167668456</v>
+        <v>9.834277143136063</v>
       </c>
       <c r="D932" t="n">
-        <v>9.157565885618284</v>
+        <v>9.157566793962603</v>
       </c>
       <c r="E932" t="n">
-        <v>9.553046007661319</v>
+        <v>9.55304695523354</v>
       </c>
       <c r="F932" t="n">
         <v>4523900</v>
@@ -19192,16 +19192,16 @@
         <v>44950</v>
       </c>
       <c r="B939" t="n">
-        <v>9.614564895629883</v>
+        <v>9.614565849304199</v>
       </c>
       <c r="C939" t="n">
-        <v>9.640930851729543</v>
+        <v>9.640931808019115</v>
       </c>
       <c r="D939" t="n">
-        <v>9.342123387655965</v>
+        <v>9.34212431430665</v>
       </c>
       <c r="E939" t="n">
-        <v>9.447584697658643</v>
+        <v>9.447585634770096</v>
       </c>
       <c r="F939" t="n">
         <v>1892600</v>
@@ -19452,16 +19452,16 @@
         <v>44967</v>
       </c>
       <c r="B952" t="n">
-        <v>7.558068752288818</v>
+        <v>7.55806827545166</v>
       </c>
       <c r="C952" t="n">
-        <v>7.681106538952327</v>
+        <v>7.681106054352737</v>
       </c>
       <c r="D952" t="n">
-        <v>7.45260659496001</v>
+        <v>7.452606124776438</v>
       </c>
       <c r="E952" t="n">
-        <v>7.558068752288818</v>
+        <v>7.55806827545166</v>
       </c>
       <c r="F952" t="n">
         <v>1100200</v>
@@ -19472,16 +19472,16 @@
         <v>44970</v>
       </c>
       <c r="B953" t="n">
-        <v>7.522914886474609</v>
+        <v>7.522914409637451</v>
       </c>
       <c r="C953" t="n">
-        <v>7.645952671621207</v>
+        <v>7.645952186985345</v>
       </c>
       <c r="D953" t="n">
-        <v>7.232895214594074</v>
+        <v>7.232894756139705</v>
       </c>
       <c r="E953" t="n">
-        <v>7.566856473665793</v>
+        <v>7.566855994043414</v>
       </c>
       <c r="F953" t="n">
         <v>2712600</v>
@@ -19492,16 +19492,16 @@
         <v>44971</v>
       </c>
       <c r="B954" t="n">
-        <v>7.145011901855469</v>
+        <v>7.145011425018311</v>
       </c>
       <c r="C954" t="n">
-        <v>7.663530727562388</v>
+        <v>7.663530216120802</v>
       </c>
       <c r="D954" t="n">
-        <v>7.083493003257066</v>
+        <v>7.083492530525499</v>
       </c>
       <c r="E954" t="n">
-        <v>7.514126969710152</v>
+        <v>7.514126468239336</v>
       </c>
       <c r="F954" t="n">
         <v>2909100</v>
@@ -19532,16 +19532,16 @@
         <v>44973</v>
       </c>
       <c r="B956" t="n">
-        <v>7.979913234710693</v>
+        <v>7.97991418838501</v>
       </c>
       <c r="C956" t="n">
-        <v>8.111739661050875</v>
+        <v>8.111740630479682</v>
       </c>
       <c r="D956" t="n">
-        <v>7.566855813709092</v>
+        <v>7.566856718019181</v>
       </c>
       <c r="E956" t="n">
-        <v>7.663529308615072</v>
+        <v>7.663530224478548</v>
       </c>
       <c r="F956" t="n">
         <v>2076600</v>
@@ -19552,16 +19552,16 @@
         <v>44974</v>
       </c>
       <c r="B957" t="n">
-        <v>7.733837127685547</v>
+        <v>7.733837604522705</v>
       </c>
       <c r="C957" t="n">
-        <v>7.988702175798579</v>
+        <v>7.988702668349687</v>
       </c>
       <c r="D957" t="n">
-        <v>7.637163629280322</v>
+        <v>7.637164100156983</v>
       </c>
       <c r="E957" t="n">
-        <v>7.953548404959954</v>
+        <v>7.953548895343623</v>
       </c>
       <c r="F957" t="n">
         <v>1740900</v>
@@ -19592,16 +19592,16 @@
         <v>44980</v>
       </c>
       <c r="B959" t="n">
-        <v>7.558068752288818</v>
+        <v>7.55806827545166</v>
       </c>
       <c r="C959" t="n">
-        <v>7.628376298419984</v>
+        <v>7.628375817147136</v>
       </c>
       <c r="D959" t="n">
-        <v>7.311991502697679</v>
+        <v>7.311991041385489</v>
       </c>
       <c r="E959" t="n">
-        <v>7.44381878029266</v>
+        <v>7.443818310663511</v>
       </c>
       <c r="F959" t="n">
         <v>2884000</v>
@@ -19632,16 +19632,16 @@
         <v>44984</v>
       </c>
       <c r="B961" t="n">
-        <v>7.628376483917236</v>
+        <v>7.628376960754395</v>
       </c>
       <c r="C961" t="n">
-        <v>7.95354910221403</v>
+        <v>7.953549599377189</v>
       </c>
       <c r="D961" t="n">
-        <v>7.584434056983707</v>
+        <v>7.584434531074097</v>
       </c>
       <c r="E961" t="n">
-        <v>7.883241554373214</v>
+        <v>7.883242047141565</v>
       </c>
       <c r="F961" t="n">
         <v>1796000</v>
@@ -19652,16 +19652,16 @@
         <v>44985</v>
       </c>
       <c r="B962" t="n">
-        <v>7.206530094146729</v>
+        <v>7.206530570983887</v>
       </c>
       <c r="C962" t="n">
-        <v>7.689895096404264</v>
+        <v>7.689895605224415</v>
       </c>
       <c r="D962" t="n">
-        <v>7.18016497420746</v>
+        <v>7.180165449300108</v>
       </c>
       <c r="E962" t="n">
-        <v>7.628376203835287</v>
+        <v>7.628376708584893</v>
       </c>
       <c r="F962" t="n">
         <v>2084200</v>
@@ -19672,16 +19672,16 @@
         <v>44986</v>
       </c>
       <c r="B963" t="n">
-        <v>6.969241619110107</v>
+        <v>6.969242095947266</v>
       </c>
       <c r="C963" t="n">
-        <v>7.303203282836455</v>
+        <v>7.303203782523349</v>
       </c>
       <c r="D963" t="n">
-        <v>6.872568958076331</v>
+        <v>6.872569428299123</v>
       </c>
       <c r="E963" t="n">
-        <v>7.250472207097658</v>
+        <v>7.25047270317668</v>
       </c>
       <c r="F963" t="n">
         <v>3168200</v>
@@ -19752,16 +19752,16 @@
         <v>44992</v>
       </c>
       <c r="B967" t="n">
-        <v>7.487761974334717</v>
+        <v>7.487761497497559</v>
       </c>
       <c r="C967" t="n">
-        <v>7.645953550292841</v>
+        <v>7.645953063381696</v>
       </c>
       <c r="D967" t="n">
-        <v>7.276838476170305</v>
+        <v>7.27683801276522</v>
       </c>
       <c r="E967" t="n">
-        <v>7.329569560244445</v>
+        <v>7.329569093481328</v>
       </c>
       <c r="F967" t="n">
         <v>1239000</v>
@@ -19792,16 +19792,16 @@
         <v>44994</v>
       </c>
       <c r="B969" t="n">
-        <v>8.129318237304688</v>
+        <v>8.129317283630371</v>
       </c>
       <c r="C969" t="n">
-        <v>8.349029541015625</v>
+        <v>8.349028561566326</v>
       </c>
       <c r="D969" t="n">
-        <v>8.0677993404679</v>
+        <v>8.067798394010547</v>
       </c>
       <c r="E969" t="n">
-        <v>8.146895543904975</v>
+        <v>8.146894588168612</v>
       </c>
       <c r="F969" t="n">
         <v>3140600</v>
@@ -19832,16 +19832,16 @@
         <v>44998</v>
       </c>
       <c r="B971" t="n">
-        <v>7.716260433197021</v>
+        <v>7.716259479522705</v>
       </c>
       <c r="C971" t="n">
-        <v>7.839299059924837</v>
+        <v>7.839298091043831</v>
       </c>
       <c r="D971" t="n">
-        <v>7.478972670810896</v>
+        <v>7.478971746463641</v>
       </c>
       <c r="E971" t="n">
-        <v>7.716260433197021</v>
+        <v>7.716259479522705</v>
       </c>
       <c r="F971" t="n">
         <v>789800</v>
@@ -19872,16 +19872,16 @@
         <v>45000</v>
       </c>
       <c r="B973" t="n">
-        <v>7.637163639068604</v>
+        <v>7.637164115905762</v>
       </c>
       <c r="C973" t="n">
-        <v>7.86566356887853</v>
+        <v>7.865664059982405</v>
       </c>
       <c r="D973" t="n">
-        <v>7.153799498951003</v>
+        <v>7.153799945608635</v>
       </c>
       <c r="E973" t="n">
-        <v>7.505337207787805</v>
+        <v>7.505337676394193</v>
       </c>
       <c r="F973" t="n">
         <v>1097200</v>
@@ -19912,16 +19912,16 @@
         <v>45002</v>
       </c>
       <c r="B975" t="n">
-        <v>7.716260433197021</v>
+        <v>7.716259479522705</v>
       </c>
       <c r="C975" t="n">
-        <v>8.050221701630743</v>
+        <v>8.050220706681214</v>
       </c>
       <c r="D975" t="n">
-        <v>7.575645338726417</v>
+        <v>7.575644402431116</v>
       </c>
       <c r="E975" t="n">
-        <v>8.050221701630743</v>
+        <v>8.050220706681214</v>
       </c>
       <c r="F975" t="n">
         <v>1382600</v>
@@ -19952,16 +19952,16 @@
         <v>45006</v>
       </c>
       <c r="B977" t="n">
-        <v>7.338357448577881</v>
+        <v>7.338357925415039</v>
       </c>
       <c r="C977" t="n">
-        <v>7.514126313605961</v>
+        <v>7.514126801864357</v>
       </c>
       <c r="D977" t="n">
-        <v>7.180165050986578</v>
+        <v>7.180165517544595</v>
       </c>
       <c r="E977" t="n">
-        <v>7.188953703770998</v>
+        <v>7.188954170900089</v>
       </c>
       <c r="F977" t="n">
         <v>2520700</v>
@@ -19972,16 +19972,16 @@
         <v>45007</v>
       </c>
       <c r="B978" t="n">
-        <v>7.28562593460083</v>
+        <v>7.285626411437988</v>
       </c>
       <c r="C978" t="n">
-        <v>7.540490983193351</v>
+        <v>7.54049147671118</v>
       </c>
       <c r="D978" t="n">
-        <v>7.171375969627354</v>
+        <v>7.171376438986963</v>
       </c>
       <c r="E978" t="n">
-        <v>7.34714482415116</v>
+        <v>7.34714530501467</v>
       </c>
       <c r="F978" t="n">
         <v>921100</v>
@@ -20032,16 +20032,16 @@
         <v>45012</v>
       </c>
       <c r="B981" t="n">
-        <v>7.188953399658203</v>
+        <v>7.188953876495361</v>
       </c>
       <c r="C981" t="n">
-        <v>7.268049595107865</v>
+        <v>7.268050077191407</v>
       </c>
       <c r="D981" t="n">
-        <v>6.995607237240367</v>
+        <v>6.995607701253039</v>
       </c>
       <c r="E981" t="n">
-        <v>7.039549661171515</v>
+        <v>7.039550128098851</v>
       </c>
       <c r="F981" t="n">
         <v>840700</v>
@@ -20072,16 +20072,16 @@
         <v>45014</v>
       </c>
       <c r="B983" t="n">
-        <v>7.074704170227051</v>
+        <v>7.074703693389893</v>
       </c>
       <c r="C983" t="n">
-        <v>7.452607043914391</v>
+        <v>7.452606541606468</v>
       </c>
       <c r="D983" t="n">
-        <v>6.749531121182534</v>
+        <v>6.749530666262135</v>
       </c>
       <c r="E983" t="n">
-        <v>7.19774196430251</v>
+        <v>7.197741479172568</v>
       </c>
       <c r="F983" t="n">
         <v>1527300</v>
@@ -20092,16 +20092,16 @@
         <v>45015</v>
       </c>
       <c r="B984" t="n">
-        <v>7.628376483917236</v>
+        <v>7.628376960754395</v>
       </c>
       <c r="C984" t="n">
-        <v>7.68989537874493</v>
+        <v>7.689895859427532</v>
       </c>
       <c r="D984" t="n">
-        <v>7.180165237832975</v>
+        <v>7.180165686653192</v>
       </c>
       <c r="E984" t="n">
-        <v>7.268050091700036</v>
+        <v>7.268050546013789</v>
       </c>
       <c r="F984" t="n">
         <v>1854500</v>
@@ -20112,16 +20112,16 @@
         <v>45016</v>
       </c>
       <c r="B985" t="n">
-        <v>7.294415950775146</v>
+        <v>7.294415473937988</v>
       </c>
       <c r="C985" t="n">
-        <v>7.768992365792066</v>
+        <v>7.768991857931769</v>
       </c>
       <c r="D985" t="n">
-        <v>7.118647063385948</v>
+        <v>7.118646598038831</v>
       </c>
       <c r="E985" t="n">
-        <v>7.628377255880707</v>
+        <v>7.628376757212443</v>
       </c>
       <c r="F985" t="n">
         <v>3070300</v>
@@ -20192,16 +20192,16 @@
         <v>45022</v>
       </c>
       <c r="B989" t="n">
-        <v>6.731954097747803</v>
+        <v>6.731953620910645</v>
       </c>
       <c r="C989" t="n">
-        <v>6.784684759458694</v>
+        <v>6.784684278886522</v>
       </c>
       <c r="D989" t="n">
-        <v>6.564973459463624</v>
+        <v>6.564972994454023</v>
       </c>
       <c r="E989" t="n">
-        <v>6.564973459463624</v>
+        <v>6.564972994454023</v>
       </c>
       <c r="F989" t="n">
         <v>728000</v>
@@ -20372,16 +20372,16 @@
         <v>45036</v>
       </c>
       <c r="B998" t="n">
-        <v>6.48587703704834</v>
+        <v>6.485877513885498</v>
       </c>
       <c r="C998" t="n">
-        <v>6.600127002358792</v>
+        <v>6.600127487595527</v>
       </c>
       <c r="D998" t="n">
-        <v>6.292530877435881</v>
+        <v>6.292531340058365</v>
       </c>
       <c r="E998" t="n">
-        <v>6.424357728250556</v>
+        <v>6.424358200564858</v>
       </c>
       <c r="F998" t="n">
         <v>2265600</v>
@@ -37712,16 +37712,16 @@
         <v>46304</v>
       </c>
       <c r="B1865" t="n">
-        <v>11.39</v>
+        <v>11.39000034332275</v>
       </c>
       <c r="C1865" t="n">
-        <v>11.48</v>
+        <v>11.47999954223633</v>
       </c>
       <c r="D1865" t="n">
-        <v>10.37</v>
+        <v>10.36999988555908</v>
       </c>
       <c r="E1865" t="n">
-        <v>10.49</v>
+        <v>10.48999977111816</v>
       </c>
       <c r="F1865" t="n">
         <v>6829200</v>
